--- a/database/event/5209/event_5209_evp_summary.xlsx
+++ b/database/event/5209/event_5209_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.091200000000001</v>
+        <v>8.078200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2018</v>
+        <v>3.1967</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8473</v>
+        <v>2.7744</v>
       </c>
       <c r="E2" t="n">
-        <v>8.091200000000001</v>
+        <v>8.078200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7484</v>
+        <v>1.7353</v>
       </c>
       <c r="G2" t="n">
         <v>6.3428</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7484</v>
+        <v>1.7353</v>
       </c>
       <c r="I2" t="n">
         <v>1.7647</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.4598</v>
+        <v>4.4406</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7648</v>
+        <v>1.7572</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3803</v>
+        <v>1.3252</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4598</v>
+        <v>4.4406</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5672</v>
+        <v>2.548</v>
       </c>
       <c r="G3" t="n">
         <v>1.8926</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5672</v>
+        <v>2.548</v>
       </c>
       <c r="I3" t="n">
         <v>2.5911</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9818</v>
+        <v>3.9521</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5757</v>
+        <v>1.5639</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1872</v>
+        <v>1.1306</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9818</v>
+        <v>3.9521</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1345</v>
+        <v>4.1048</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1527</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1799</v>
+        <v>4.1333</v>
       </c>
       <c r="I4" t="n">
         <v>4.2386</v>
@@ -640,7 +640,7 @@
         <v>1.4792</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0887</v>
+        <v>1.0453</v>
       </c>
       <c r="E5" t="n">
         <v>3.738</v>
@@ -686,7 +686,7 @@
         <v>1.2276</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8319</v>
+        <v>0.792</v>
       </c>
       <c r="E6" t="n">
         <v>3.1022</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0416</v>
+        <v>2.9694</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2036</v>
+        <v>1.175</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8074</v>
+        <v>0.7391</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0416</v>
+        <v>2.9694</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9007</v>
+        <v>3.8285</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8591</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9007</v>
+        <v>3.8285</v>
       </c>
       <c r="I7" t="n">
         <v>3.9923</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.715</v>
+        <v>2.7064</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0744</v>
+        <v>1.071</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6754</v>
+        <v>0.6343</v>
       </c>
       <c r="E8" t="n">
-        <v>2.715</v>
+        <v>2.7064</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1644</v>
+        <v>1.1558</v>
       </c>
       <c r="G8" t="n">
         <v>1.5506</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1644</v>
+        <v>1.1558</v>
       </c>
       <c r="I8" t="n">
         <v>1.1753</v>
@@ -824,7 +824,7 @@
         <v>0.9957</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5952</v>
+        <v>0.5586</v>
       </c>
       <c r="E9" t="n">
         <v>2.5163</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4893</v>
+        <v>2.4894</v>
       </c>
       <c r="C10" t="n">
         <v>0.9851</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5843</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4893</v>
+        <v>2.4894</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.026</v>
+        <v>-0.0259</v>
       </c>
       <c r="G10" t="n">
         <v>2.5153</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.026</v>
+        <v>-0.0259</v>
       </c>
       <c r="I10" t="n">
         <v>-0.0261</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4784</v>
+        <v>2.4806</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9807</v>
+        <v>0.9816</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5799</v>
+        <v>0.5444</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4784</v>
+        <v>2.4806</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5875</v>
+        <v>-0.5853</v>
       </c>
       <c r="G11" t="n">
         <v>3.0659</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5875</v>
+        <v>-0.5853</v>
       </c>
       <c r="I11" t="n">
         <v>-0.5901999999999999</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5872</v>
+        <v>1.5852</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6281</v>
+        <v>0.6273</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2198</v>
+        <v>0.1876</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5872</v>
+        <v>1.5852</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2691</v>
+        <v>0.2671</v>
       </c>
       <c r="G12" t="n">
         <v>1.3181</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2691</v>
+        <v>0.2671</v>
       </c>
       <c r="I12" t="n">
         <v>0.2716</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5571</v>
+        <v>1.5511</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6162</v>
+        <v>0.6138</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2077</v>
+        <v>0.174</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5571</v>
+        <v>1.5511</v>
       </c>
       <c r="F13" t="n">
-        <v>1.625</v>
+        <v>1.619</v>
       </c>
       <c r="G13" t="n">
         <v>-0.0679</v>
       </c>
       <c r="H13" t="n">
-        <v>1.625</v>
+        <v>1.619</v>
       </c>
       <c r="I13" t="n">
         <v>1.6326</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4402</v>
+        <v>1.4437</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5699</v>
+        <v>0.5713</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1604</v>
+        <v>0.1313</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4402</v>
+        <v>1.4437</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4638</v>
+        <v>-0.4603</v>
       </c>
       <c r="G14" t="n">
         <v>1.904</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4638</v>
+        <v>-0.4603</v>
       </c>
       <c r="I14" t="n">
         <v>-0.4681</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4063</v>
+        <v>1.3964</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5565</v>
+        <v>0.5526</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1468</v>
+        <v>0.1124</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4063</v>
+        <v>1.3964</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3234</v>
+        <v>1.3135</v>
       </c>
       <c r="G15" t="n">
         <v>0.0829</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3234</v>
+        <v>1.3135</v>
       </c>
       <c r="I15" t="n">
         <v>1.3357</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1903</v>
+        <v>1.1871</v>
       </c>
       <c r="C16" t="n">
-        <v>0.471</v>
+        <v>0.4698</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0595</v>
+        <v>0.029</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1903</v>
+        <v>1.1871</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8557</v>
+        <v>0.8525</v>
       </c>
       <c r="G16" t="n">
         <v>0.3346</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8557</v>
+        <v>0.8525</v>
       </c>
       <c r="I16" t="n">
         <v>0.8597</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1562</v>
+        <v>1.1494</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4575</v>
+        <v>0.4548</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0457</v>
+        <v>0.014</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1562</v>
+        <v>1.1494</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9141</v>
+        <v>0.9073</v>
       </c>
       <c r="G17" t="n">
         <v>0.2421</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9141</v>
+        <v>0.9073</v>
       </c>
       <c r="I17" t="n">
         <v>0.9226</v>
@@ -1238,7 +1238,7 @@
         <v>0.4439</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0318</v>
+        <v>0.003</v>
       </c>
       <c r="E18" t="n">
         <v>1.1218</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0622</v>
+        <v>1.058</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4203</v>
+        <v>0.4187</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0077</v>
+        <v>-0.0224</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0622</v>
+        <v>1.058</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1339</v>
+        <v>1.1297</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0717</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1339</v>
+        <v>1.1297</v>
       </c>
       <c r="I19" t="n">
         <v>1.1392</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2426</v>
+        <v>0.2401</v>
       </c>
       <c r="C20" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3234</v>
+        <v>-0.3483</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2426</v>
+        <v>0.2401</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6822</v>
+        <v>0.6797</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4396</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6822</v>
+        <v>0.6797</v>
       </c>
       <c r="I20" t="n">
         <v>0.6854</v>
@@ -1376,7 +1376,7 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3371</v>
+        <v>-0.3608</v>
       </c>
       <c r="E21" t="n">
         <v>0.2087</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1599</v>
+        <v>0.1595</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0633</v>
+        <v>0.0631</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3568</v>
+        <v>-0.3804</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1599</v>
+        <v>0.1595</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0944</v>
+        <v>0.094</v>
       </c>
       <c r="G22" t="n">
         <v>0.0655</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0944</v>
+        <v>0.094</v>
       </c>
       <c r="I22" t="n">
         <v>0.0948</v>
@@ -1468,7 +1468,7 @@
         <v>0.0585</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3616</v>
+        <v>-0.385</v>
       </c>
       <c r="E23" t="n">
         <v>0.1479</v>
@@ -1514,7 +1514,7 @@
         <v>0.0497</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3706</v>
+        <v>-0.3938</v>
       </c>
       <c r="E24" t="n">
         <v>0.1257</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1018</v>
+        <v>0.1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0403</v>
+        <v>0.0396</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3802</v>
+        <v>-0.4041</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1018</v>
+        <v>0.1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4881</v>
+        <v>0.4863</v>
       </c>
       <c r="G25" t="n">
         <v>-0.3863</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4881</v>
+        <v>0.4863</v>
       </c>
       <c r="I25" t="n">
         <v>0.4904</v>
@@ -1606,7 +1606,7 @@
         <v>-0.08939999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5127</v>
+        <v>-0.5339</v>
       </c>
       <c r="E26" t="n">
         <v>-0.226</v>
@@ -1652,7 +1652,7 @@
         <v>-0.096</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5194</v>
+        <v>-0.5406</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2426</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.298</v>
+        <v>-0.2966</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1179</v>
+        <v>-0.1174</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5417</v>
+        <v>-0.5621</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.298</v>
+        <v>-0.2966</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3762</v>
+        <v>-0.3748</v>
       </c>
       <c r="G28" t="n">
         <v>0.07820000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3762</v>
+        <v>-0.3748</v>
       </c>
       <c r="I28" t="n">
         <v>-0.378</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6874</v>
+        <v>-0.6574</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.272</v>
+        <v>-0.2601</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.7058</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6874</v>
+        <v>-0.6574</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.6905</v>
+        <v>-2.6605</v>
       </c>
       <c r="G29" t="n">
         <v>2.0031</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.6905</v>
+        <v>-2.6605</v>
       </c>
       <c r="I29" t="n">
         <v>-2.7282</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7591</v>
+        <v>-0.7634</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3004</v>
+        <v>-0.3021</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.728</v>
+        <v>-0.748</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7591</v>
+        <v>-0.7634</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5762</v>
+        <v>0.5719</v>
       </c>
       <c r="G30" t="n">
         <v>-1.3353</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5762</v>
+        <v>0.5719</v>
       </c>
       <c r="I30" t="n">
         <v>0.5816</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7675</v>
+        <v>-0.7643</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3037</v>
+        <v>-0.3024</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-0.7484</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7675</v>
+        <v>-0.7643</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8701</v>
+        <v>-0.8669</v>
       </c>
       <c r="G31" t="n">
         <v>0.1026</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8701</v>
+        <v>-0.8669</v>
       </c>
       <c r="I31" t="n">
         <v>-0.8742</v>
@@ -1882,7 +1882,7 @@
         <v>-0.4013</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.831</v>
+        <v>-0.8479</v>
       </c>
       <c r="E32" t="n">
         <v>-1.0141</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.191</v>
+        <v>-1.1942</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4713</v>
+        <v>-0.4726</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9025</v>
+        <v>-0.9197</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.191</v>
+        <v>-1.1942</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4359</v>
+        <v>0.4327</v>
       </c>
       <c r="G33" t="n">
         <v>-1.6269</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4359</v>
+        <v>0.4327</v>
       </c>
       <c r="I33" t="n">
         <v>0.44</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.2317</v>
+        <v>-1.228</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4874</v>
+        <v>-0.4859</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.9331</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.2317</v>
+        <v>-1.228</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9954</v>
+        <v>-0.9917</v>
       </c>
       <c r="G34" t="n">
         <v>-0.2363</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9954</v>
+        <v>-0.9917</v>
       </c>
       <c r="I34" t="n">
         <v>-1</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.3514</v>
+        <v>-1.3477</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5333</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9673</v>
+        <v>-0.9808</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3514</v>
+        <v>-1.3477</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9954</v>
+        <v>-0.9917</v>
       </c>
       <c r="G35" t="n">
         <v>-0.356</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9954</v>
+        <v>-0.9917</v>
       </c>
       <c r="I35" t="n">
         <v>-1</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.5516</v>
+        <v>-1.5423</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.614</v>
+        <v>-0.6103</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0482</v>
+        <v>-1.0584</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.5516</v>
+        <v>-1.5423</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2532</v>
+        <v>-1.2439</v>
       </c>
       <c r="G36" t="n">
         <v>-0.2984</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2532</v>
+        <v>-1.2439</v>
       </c>
       <c r="I36" t="n">
         <v>-1.2649</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.561</v>
+        <v>-1.5499</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6177</v>
+        <v>-0.6133</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.052</v>
+        <v>-1.0614</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.561</v>
+        <v>-1.5499</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4906</v>
+        <v>-1.4795</v>
       </c>
       <c r="G37" t="n">
         <v>-0.0704</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4906</v>
+        <v>-1.4795</v>
       </c>
       <c r="I37" t="n">
         <v>-1.5045</v>
@@ -2158,7 +2158,7 @@
         <v>-0.6712</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1065</v>
+        <v>-1.1196</v>
       </c>
       <c r="E38" t="n">
         <v>-1.6961</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.2876</v>
+        <v>-2.2464</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.9052</v>
+        <v>-0.8889</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3455</v>
+        <v>-1.3389</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.2876</v>
+        <v>-2.2464</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.7757</v>
+        <v>-2.7345</v>
       </c>
       <c r="G39" t="n">
         <v>0.4881</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.7757</v>
+        <v>-2.7345</v>
       </c>
       <c r="I39" t="n">
         <v>-2.8277</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.4082</v>
+        <v>-2.403</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.953</v>
+        <v>-0.9509</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3942</v>
+        <v>-1.4013</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.4082</v>
+        <v>-2.403</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4082</v>
+        <v>-1.403</v>
       </c>
       <c r="G40" t="n">
         <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4082</v>
+        <v>-1.403</v>
       </c>
       <c r="I40" t="n">
         <v>-1.4148</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.9463</v>
+        <v>-2.9318</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.1659</v>
+        <v>-1.1602</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6116</v>
+        <v>-1.6119</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.9463</v>
+        <v>-2.9318</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9463</v>
+        <v>-1.9318</v>
       </c>
       <c r="G41" t="n">
         <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9463</v>
+        <v>-1.9318</v>
       </c>
       <c r="I41" t="n">
         <v>-1.9645</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-3.1573</v>
+        <v>-3.1399</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.2494</v>
+        <v>-1.2425</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.6968</v>
+        <v>-1.6948</v>
       </c>
       <c r="E42" t="n">
-        <v>-3.1573</v>
+        <v>-3.1399</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.3352</v>
+        <v>-2.3178</v>
       </c>
       <c r="G42" t="n">
         <v>-0.8221000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.3352</v>
+        <v>-2.3178</v>
       </c>
       <c r="I42" t="n">
         <v>-2.357</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-3.3128</v>
+        <v>-3.2478</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.3109</v>
+        <v>-1.2852</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.7597</v>
+        <v>-1.7378</v>
       </c>
       <c r="E43" t="n">
-        <v>-3.3128</v>
+        <v>-3.2478</v>
       </c>
       <c r="F43" t="n">
-        <v>-4.3822</v>
+        <v>-4.3172</v>
       </c>
       <c r="G43" t="n">
         <v>1.0694</v>
       </c>
       <c r="H43" t="n">
-        <v>-4.3822</v>
+        <v>-4.3172</v>
       </c>
       <c r="I43" t="n">
         <v>-4.4644</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-3.6683</v>
+        <v>-3.6428</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.4516</v>
+        <v>-1.4415</v>
       </c>
       <c r="D44" t="n">
-        <v>-1.9033</v>
+        <v>-1.8952</v>
       </c>
       <c r="E44" t="n">
-        <v>-3.6683</v>
+        <v>-3.6428</v>
       </c>
       <c r="F44" t="n">
-        <v>-3.4134</v>
+        <v>-3.3879</v>
       </c>
       <c r="G44" t="n">
         <v>-0.2549</v>
       </c>
       <c r="H44" t="n">
-        <v>-3.4134</v>
+        <v>-3.3879</v>
       </c>
       <c r="I44" t="n">
         <v>-3.4452</v>

--- a/database/event/5209/event_5209_evp_summary.xlsx
+++ b/database/event/5209/event_5209_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.078200000000001</v>
+        <v>8.5131</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1967</v>
+        <v>3.3688</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7744</v>
+        <v>3.2052</v>
       </c>
       <c r="E2" t="n">
-        <v>8.078200000000001</v>
+        <v>8.5131</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7353</v>
+        <v>3.0094</v>
       </c>
       <c r="G2" t="n">
-        <v>6.3428</v>
+        <v>5.5038</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7353</v>
+        <v>3.2483</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7647</v>
+        <v>3.521</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3428</v>
+        <v>5.5038</v>
       </c>
       <c r="K2" t="n">
         <v>78</v>
@@ -529,7 +529,7 @@
         <v>218</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1075</v>
+        <v>9.024799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>296</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.4406</v>
+        <v>4.285</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7572</v>
+        <v>1.6957</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3252</v>
+        <v>1.2964</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4406</v>
+        <v>4.285</v>
       </c>
       <c r="F3" t="n">
-        <v>2.548</v>
+        <v>2.8862</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8926</v>
+        <v>1.3988</v>
       </c>
       <c r="H3" t="n">
-        <v>2.548</v>
+        <v>2.9779</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5911</v>
+        <v>3.2279</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8926</v>
+        <v>1.3988</v>
       </c>
       <c r="K3" t="n">
         <v>116</v>
@@ -575,7 +575,7 @@
         <v>197</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4837</v>
+        <v>4.6267</v>
       </c>
       <c r="N3" t="n">
         <v>313</v>
@@ -584,139 +584,139 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9521</v>
+        <v>3.4865</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5639</v>
+        <v>1.3797</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1306</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9521</v>
+        <v>3.4865</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1048</v>
+        <v>0.9953</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1527</v>
+        <v>2.4912</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1333</v>
+        <v>0.9953</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2386</v>
+        <v>0.9953</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1527</v>
+        <v>2.4912</v>
       </c>
       <c r="K4" t="n">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="M4" t="n">
-        <v>4.0859</v>
+        <v>3.4865</v>
       </c>
       <c r="N4" t="n">
-        <v>346</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>Nivera</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.738</v>
+        <v>3.0519</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4792</v>
+        <v>1.2077</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0453</v>
+        <v>0.7398</v>
       </c>
       <c r="E5" t="n">
-        <v>3.738</v>
+        <v>3.0519</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6808</v>
+        <v>1.6448</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0572</v>
+        <v>1.4071</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6808</v>
+        <v>1.6448</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6808</v>
+        <v>1.6448</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0572</v>
+        <v>1.4071</v>
       </c>
       <c r="K5" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L5" t="n">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="M5" t="n">
-        <v>3.738</v>
+        <v>3.0519</v>
       </c>
       <c r="N5" t="n">
-        <v>256</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nivera</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.1022</v>
+        <v>2.9155</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2276</v>
+        <v>1.1537</v>
       </c>
       <c r="D6" t="n">
-        <v>0.792</v>
+        <v>0.6782</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1022</v>
+        <v>2.9155</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3278</v>
+        <v>-0.2722</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7744</v>
+        <v>3.1877</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3278</v>
+        <v>-0.2722</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3278</v>
+        <v>-0.2834</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7744</v>
+        <v>3.1877</v>
       </c>
       <c r="K6" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="L6" t="n">
-        <v>83</v>
+        <v>229</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1022</v>
+        <v>2.9043</v>
       </c>
       <c r="N6" t="n">
-        <v>118</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9694</v>
+        <v>2.6918</v>
       </c>
       <c r="C7" t="n">
-        <v>1.175</v>
+        <v>1.0652</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7391</v>
+        <v>0.5772</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9694</v>
+        <v>2.6918</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8285</v>
+        <v>3.6455</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8591</v>
+        <v>-0.9537</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8285</v>
+        <v>4.6451</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9923</v>
+        <v>5.6822</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8591</v>
+        <v>-0.9537</v>
       </c>
       <c r="K7" t="n">
         <v>151</v>
@@ -759,7 +759,7 @@
         <v>269</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1332</v>
+        <v>4.7285</v>
       </c>
       <c r="N7" t="n">
         <v>420</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7064</v>
+        <v>2.5767</v>
       </c>
       <c r="C8" t="n">
-        <v>1.071</v>
+        <v>1.0196</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6343</v>
+        <v>0.5252</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7064</v>
+        <v>2.5767</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1558</v>
+        <v>3.1285</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5506</v>
+        <v>-0.5518</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1558</v>
+        <v>3.5098</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1753</v>
+        <v>3.9609</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5506</v>
+        <v>-0.5518</v>
       </c>
       <c r="K8" t="n">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="L8" t="n">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7259</v>
+        <v>3.4091</v>
       </c>
       <c r="N8" t="n">
-        <v>166</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5163</v>
+        <v>2.4643</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9957</v>
+        <v>0.9752</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5586</v>
+        <v>0.4745</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5163</v>
+        <v>2.4643</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5585</v>
+        <v>0.6829</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9578</v>
+        <v>1.7814</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5585</v>
+        <v>0.6829</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5585</v>
+        <v>0.6829</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9578</v>
+        <v>1.7814</v>
       </c>
       <c r="K9" t="n">
         <v>17</v>
@@ -851,7 +851,7 @@
         <v>98</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5163</v>
+        <v>2.4643</v>
       </c>
       <c r="N9" t="n">
         <v>115</v>
@@ -860,185 +860,185 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4894</v>
+        <v>2.4017</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9851</v>
+        <v>0.9504</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.4462</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4894</v>
+        <v>2.4017</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0259</v>
+        <v>1.0704</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5153</v>
+        <v>1.3313</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0259</v>
+        <v>1.0704</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0261</v>
+        <v>1.1603</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5153</v>
+        <v>1.3313</v>
       </c>
       <c r="K10" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L10" t="n">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4892</v>
+        <v>2.4916</v>
       </c>
       <c r="N10" t="n">
-        <v>249</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4806</v>
+        <v>2.2082</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9816</v>
+        <v>0.8738</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5444</v>
+        <v>0.3589</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4806</v>
+        <v>2.2082</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5853</v>
+        <v>0.1325</v>
       </c>
       <c r="G11" t="n">
-        <v>3.0659</v>
+        <v>2.0757</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5853</v>
+        <v>0.1325</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5901999999999999</v>
+        <v>0.1379</v>
       </c>
       <c r="J11" t="n">
-        <v>3.0659</v>
+        <v>2.0757</v>
       </c>
       <c r="K11" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="L11" t="n">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4757</v>
+        <v>2.2136</v>
       </c>
       <c r="N11" t="n">
-        <v>314</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5852</v>
+        <v>1.741</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6273</v>
+        <v>0.6889</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1876</v>
+        <v>0.148</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5852</v>
+        <v>1.741</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2671</v>
+        <v>0.8452</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3181</v>
+        <v>0.8958</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2671</v>
+        <v>0.8452</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2716</v>
+        <v>0.9162</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3181</v>
+        <v>0.8958</v>
       </c>
       <c r="K12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L12" t="n">
-        <v>94</v>
+        <v>218</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5897</v>
+        <v>1.812</v>
       </c>
       <c r="N12" t="n">
-        <v>137</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5511</v>
+        <v>1.4958</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6138</v>
+        <v>0.5919</v>
       </c>
       <c r="D13" t="n">
-        <v>0.174</v>
+        <v>0.0373</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5511</v>
+        <v>1.4958</v>
       </c>
       <c r="F13" t="n">
-        <v>1.619</v>
+        <v>0.4353</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0679</v>
+        <v>1.0605</v>
       </c>
       <c r="H13" t="n">
-        <v>1.619</v>
+        <v>0.4353</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6326</v>
+        <v>0.4718</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0679</v>
+        <v>1.0605</v>
       </c>
       <c r="K13" t="n">
+        <v>43</v>
+      </c>
+      <c r="L13" t="n">
         <v>94</v>
       </c>
-      <c r="L13" t="n">
-        <v>195</v>
-      </c>
       <c r="M13" t="n">
-        <v>1.5647</v>
+        <v>1.5323</v>
       </c>
       <c r="N13" t="n">
-        <v>289</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4437</v>
+        <v>1.4219</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5713</v>
+        <v>0.5627</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1313</v>
+        <v>0.0039</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4437</v>
+        <v>1.4219</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4603</v>
+        <v>-0.1096</v>
       </c>
       <c r="G14" t="n">
-        <v>1.904</v>
+        <v>1.5315</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4603</v>
+        <v>-0.1096</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4681</v>
+        <v>-0.1188</v>
       </c>
       <c r="J14" t="n">
-        <v>1.904</v>
+        <v>1.5315</v>
       </c>
       <c r="K14" t="n">
         <v>104</v>
@@ -1081,7 +1081,7 @@
         <v>145</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4359</v>
+        <v>1.4127</v>
       </c>
       <c r="N14" t="n">
         <v>249</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3964</v>
+        <v>1.3331</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5526</v>
+        <v>0.5275</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1124</v>
+        <v>-0.0362</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3964</v>
+        <v>1.3331</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3135</v>
+        <v>1.3492</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0829</v>
+        <v>-0.0161</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3135</v>
+        <v>1.3492</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3357</v>
+        <v>1.4625</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0829</v>
+        <v>-0.0161</v>
       </c>
       <c r="K15" t="n">
         <v>82</v>
@@ -1127,7 +1127,7 @@
         <v>135</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4186</v>
+        <v>1.4464</v>
       </c>
       <c r="N15" t="n">
         <v>217</v>
@@ -1136,415 +1136,415 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1871</v>
+        <v>1.2875</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4698</v>
+        <v>0.5095</v>
       </c>
       <c r="D16" t="n">
-        <v>0.029</v>
+        <v>-0.0568</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1871</v>
+        <v>1.2875</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8525</v>
+        <v>1.7815</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3346</v>
+        <v>-0.494</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8525</v>
+        <v>1.7815</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8597</v>
+        <v>1.8548</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3346</v>
+        <v>-0.494</v>
       </c>
       <c r="K16" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L16" t="n">
-        <v>58</v>
+        <v>195</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1943</v>
+        <v>1.3608</v>
       </c>
       <c r="N16" t="n">
-        <v>140</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1494</v>
+        <v>1.1928</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4548</v>
+        <v>0.472</v>
       </c>
       <c r="D17" t="n">
-        <v>0.014</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1494</v>
+        <v>1.1928</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9073</v>
+        <v>0.803</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2421</v>
+        <v>0.3898</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9073</v>
+        <v>0.803</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9226</v>
+        <v>0.836</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2421</v>
+        <v>0.3898</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="L17" t="n">
-        <v>218</v>
+        <v>58</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1647</v>
+        <v>1.2258</v>
       </c>
       <c r="N17" t="n">
-        <v>260</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1218</v>
+        <v>1.1212</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4439</v>
+        <v>0.4437</v>
       </c>
       <c r="D18" t="n">
-        <v>0.003</v>
+        <v>-0.1318</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1218</v>
+        <v>1.1212</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.1192</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1218</v>
+        <v>0.002</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.1192</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1.1652</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1218</v>
+        <v>0.002</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="L18" t="n">
-        <v>230</v>
+        <v>58</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1218</v>
+        <v>1.1672</v>
       </c>
       <c r="N18" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.058</v>
+        <v>0.9025</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4187</v>
+        <v>0.3571</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0224</v>
+        <v>-0.2306</v>
       </c>
       <c r="E19" t="n">
-        <v>1.058</v>
+        <v>0.9025</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1297</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0717</v>
+        <v>0.9025</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1297</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1392</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0717</v>
+        <v>0.9025</v>
       </c>
       <c r="K19" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>58</v>
+        <v>230</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0675</v>
+        <v>0.9025</v>
       </c>
       <c r="N19" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Bubzkji</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2401</v>
+        <v>0.4637</v>
       </c>
       <c r="C20" t="n">
-        <v>0.095</v>
+        <v>0.1835</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3483</v>
+        <v>-0.4287</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2401</v>
+        <v>0.4637</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6797</v>
+        <v>0.4637</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4396</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6797</v>
+        <v>0.4637</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6854</v>
+        <v>0.4637</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4396</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="L20" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2458</v>
+        <v>0.4637</v>
       </c>
       <c r="N20" t="n">
-        <v>247</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2087</v>
+        <v>0.4203</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1663</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3608</v>
+        <v>-0.4483</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2087</v>
+        <v>0.4203</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.2258</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2087</v>
+        <v>0.1945</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.2258</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.2351</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2087</v>
+        <v>0.1945</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="L21" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2087</v>
+        <v>0.4296</v>
       </c>
       <c r="N21" t="n">
-        <v>57</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1595</v>
+        <v>0.3223</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0631</v>
+        <v>0.1275</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3804</v>
+        <v>-0.4925</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1595</v>
+        <v>0.3223</v>
       </c>
       <c r="F22" t="n">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0655</v>
+        <v>0.3223</v>
       </c>
       <c r="H22" t="n">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0948</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0655</v>
+        <v>0.3223</v>
       </c>
       <c r="K22" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1603</v>
+        <v>0.3223</v>
       </c>
       <c r="N22" t="n">
-        <v>140</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1479</v>
+        <v>0.1706</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0585</v>
+        <v>0.0675</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.385</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1479</v>
+        <v>0.1706</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.3945</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1479</v>
+        <v>-0.2239</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.3945</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.3945</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1479</v>
+        <v>-0.2239</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L23" t="n">
-        <v>230</v>
+        <v>47</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1479</v>
+        <v>0.1706</v>
       </c>
       <c r="N23" t="n">
-        <v>230</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bubzkji</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1257</v>
+        <v>0.1268</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0497</v>
+        <v>0.0502</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3938</v>
+        <v>-0.5808</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1257</v>
+        <v>0.1268</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1257</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
+        <v>0.1268</v>
+      </c>
+      <c r="H24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="n">
-        <v>0.1257</v>
-      </c>
       <c r="I24" t="n">
-        <v>0.1257</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
+        <v>0.1268</v>
+      </c>
+      <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="n">
-        <v>97</v>
-      </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1257</v>
+        <v>0.1268</v>
       </c>
       <c r="N24" t="n">
-        <v>97</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1</v>
+        <v>0.1124</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0396</v>
+        <v>0.0445</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4041</v>
+        <v>-0.5873</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1</v>
+        <v>0.1124</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4863</v>
+        <v>0.8141</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3863</v>
+        <v>-0.7017</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4863</v>
+        <v>0.8141</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4904</v>
+        <v>0.8476</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3863</v>
+        <v>-0.7017</v>
       </c>
       <c r="K25" t="n">
         <v>121</v>
@@ -1587,7 +1587,7 @@
         <v>239</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1041</v>
+        <v>0.1459</v>
       </c>
       <c r="N25" t="n">
         <v>360</v>
@@ -1596,185 +1596,185 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.226</v>
+        <v>0.0694</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.08939999999999999</v>
+        <v>0.0275</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5339</v>
+        <v>-0.6067</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.226</v>
+        <v>0.0694</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1908</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4168</v>
+        <v>0.0694</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1908</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1908</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4168</v>
+        <v>0.0694</v>
       </c>
       <c r="K26" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.226</v>
+        <v>0.0694</v>
       </c>
       <c r="N26" t="n">
-        <v>92</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2426</v>
+        <v>0.0083</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.096</v>
+        <v>0.0033</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5406</v>
+        <v>-0.6343</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2426</v>
+        <v>0.0083</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0.1707</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2426</v>
+        <v>0.179</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-0.1707</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-0.1777</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2426</v>
+        <v>0.179</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="L27" t="n">
-        <v>230</v>
+        <v>58</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2426</v>
+        <v>0.001299999999999996</v>
       </c>
       <c r="N27" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2966</v>
+        <v>-0.0728</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1174</v>
+        <v>-0.0288</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5621</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2966</v>
+        <v>-0.0728</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3748</v>
+        <v>0.5739</v>
       </c>
       <c r="G28" t="n">
-        <v>0.07820000000000001</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3748</v>
+        <v>0.5739</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.378</v>
+        <v>0.5975</v>
       </c>
       <c r="J28" t="n">
-        <v>0.07820000000000001</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="L28" t="n">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2998</v>
+        <v>-0.04920000000000002</v>
       </c>
       <c r="N28" t="n">
-        <v>140</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6574</v>
+        <v>-0.5812</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2601</v>
+        <v>-0.23</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7058</v>
+        <v>-0.9004</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6574</v>
+        <v>-0.5812</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.6605</v>
+        <v>-0.8267</v>
       </c>
       <c r="G29" t="n">
-        <v>2.0031</v>
+        <v>0.2455</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.6605</v>
+        <v>-0.8267</v>
       </c>
       <c r="I29" t="n">
-        <v>-2.7282</v>
+        <v>-0.8607</v>
       </c>
       <c r="J29" t="n">
-        <v>2.0031</v>
+        <v>0.2455</v>
       </c>
       <c r="K29" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="L29" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.7251000000000003</v>
+        <v>-0.6152</v>
       </c>
       <c r="N29" t="n">
-        <v>265</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7634</v>
+        <v>-0.5967</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3021</v>
+        <v>-0.2361</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.748</v>
+        <v>-0.9074</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7634</v>
+        <v>-0.5967</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5719</v>
+        <v>0.5836</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.3353</v>
+        <v>-1.1803</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5719</v>
+        <v>0.5836</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5816</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.3353</v>
+        <v>-1.1803</v>
       </c>
       <c r="K30" t="n">
         <v>82</v>
@@ -1817,7 +1817,7 @@
         <v>162</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7536999999999999</v>
+        <v>-0.5476999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>244</v>
@@ -1826,185 +1826,185 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7643</v>
+        <v>-0.8783</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3024</v>
+        <v>-0.3476</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7484</v>
+        <v>-1.0345</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7643</v>
+        <v>-0.8783</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8669</v>
+        <v>0.4347</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1026</v>
+        <v>-1.313</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8669</v>
+        <v>0.4347</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8742</v>
+        <v>0.4712</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1026</v>
+        <v>-1.313</v>
       </c>
       <c r="K31" t="n">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="L31" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7716</v>
+        <v>-0.8417999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>182</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.0141</v>
+        <v>-0.8957000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4013</v>
+        <v>-0.3544</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8479</v>
+        <v>-1.0424</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.0141</v>
+        <v>-0.8957000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-0.7817</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.0141</v>
+        <v>-0.114</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-0.7817</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>-0.8139</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.0141</v>
+        <v>-0.114</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="L32" t="n">
-        <v>230</v>
+        <v>58</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.0141</v>
+        <v>-0.9278999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.1942</v>
+        <v>-0.9939</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4726</v>
+        <v>-0.3933</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9197</v>
+        <v>-1.0867</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.1942</v>
+        <v>-0.9939</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4327</v>
+        <v>-0.8349</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.6269</v>
+        <v>-0.159</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4327</v>
+        <v>-0.8349</v>
       </c>
       <c r="I33" t="n">
-        <v>0.44</v>
+        <v>-0.905</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.6269</v>
+        <v>-0.159</v>
       </c>
       <c r="K33" t="n">
         <v>82</v>
       </c>
       <c r="L33" t="n">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.1869</v>
+        <v>-1.064</v>
       </c>
       <c r="N33" t="n">
-        <v>217</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.228</v>
+        <v>-1.0473</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4859</v>
+        <v>-0.4144</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9331</v>
+        <v>-1.1108</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.228</v>
+        <v>-1.0473</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9917</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2363</v>
+        <v>-1.0473</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9917</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.2363</v>
+        <v>-1.0473</v>
       </c>
       <c r="K34" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>58</v>
+        <v>230</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.2363</v>
+        <v>-1.0473</v>
       </c>
       <c r="N34" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.3477</v>
+        <v>-1.086</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.5333</v>
+        <v>-0.4298</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9808</v>
+        <v>-1.1283</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3477</v>
+        <v>-1.086</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9917</v>
+        <v>-0.9605</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.356</v>
+        <v>-0.1255</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9917</v>
+        <v>-0.9605</v>
       </c>
       <c r="I35" t="n">
         <v>-1</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.356</v>
+        <v>-0.1255</v>
       </c>
       <c r="K35" t="n">
         <v>45</v>
@@ -2047,7 +2047,7 @@
         <v>71</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.356</v>
+        <v>-1.1255</v>
       </c>
       <c r="N35" t="n">
         <v>116</v>
@@ -2056,47 +2056,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.5423</v>
+        <v>-1.1628</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6103</v>
+        <v>-0.4601</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0584</v>
+        <v>-1.163</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.5423</v>
+        <v>-1.1628</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2439</v>
+        <v>-2.6815</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.2984</v>
+        <v>1.5187</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2439</v>
+        <v>-2.6815</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2649</v>
+        <v>-3.0261</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.2984</v>
+        <v>1.5187</v>
       </c>
       <c r="K36" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="L36" t="n">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.5633</v>
+        <v>-1.5074</v>
       </c>
       <c r="N36" t="n">
-        <v>241</v>
+        <v>265</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.5499</v>
+        <v>-1.2138</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6133</v>
+        <v>-0.4803</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0614</v>
+        <v>-1.186</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.5499</v>
+        <v>-1.2138</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4795</v>
+        <v>-1.1953</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0704</v>
+        <v>-0.0185</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4795</v>
+        <v>-1.1953</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.5045</v>
+        <v>-1.2956</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.0704</v>
+        <v>-0.0185</v>
       </c>
       <c r="K37" t="n">
         <v>69</v>
@@ -2139,7 +2139,7 @@
         <v>23</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.5749</v>
+        <v>-1.3141</v>
       </c>
       <c r="N37" t="n">
         <v>92</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6961</v>
+        <v>-1.534</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6712</v>
+        <v>-0.607</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1196</v>
+        <v>-1.3305</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6961</v>
+        <v>-1.534</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.6961</v>
+        <v>-1.534</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.6961</v>
+        <v>-1.534</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>230</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6961</v>
+        <v>-1.534</v>
       </c>
       <c r="N38" t="n">
         <v>230</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.2464</v>
+        <v>-1.8668</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8889</v>
+        <v>-0.7387</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3389</v>
+        <v>-1.4808</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.2464</v>
+        <v>-1.8668</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.7345</v>
+        <v>-2.3112</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4881</v>
+        <v>0.4444</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.7345</v>
+        <v>-2.3112</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.8277</v>
+        <v>-2.7155</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4881</v>
+        <v>0.4444</v>
       </c>
       <c r="K39" t="n">
         <v>105</v>
@@ -2231,7 +2231,7 @@
         <v>145</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.3396</v>
+        <v>-2.2711</v>
       </c>
       <c r="N39" t="n">
         <v>250</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.403</v>
+        <v>-2.3931</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.9509</v>
+        <v>-0.947</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4013</v>
+        <v>-1.7184</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.403</v>
+        <v>-2.3931</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.403</v>
+        <v>-1.3931</v>
       </c>
       <c r="G40" t="n">
         <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.403</v>
+        <v>-1.3931</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4148</v>
+        <v>-1.4504</v>
       </c>
       <c r="J40" t="n">
         <v>-1</v>
@@ -2277,7 +2277,7 @@
         <v>47</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.4148</v>
+        <v>-2.4504</v>
       </c>
       <c r="N40" t="n">
         <v>68</v>
@@ -2286,93 +2286,93 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.9318</v>
+        <v>-2.605</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.1602</v>
+        <v>-1.0308</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6119</v>
+        <v>-1.814</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.9318</v>
+        <v>-2.605</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9318</v>
+        <v>-2.1788</v>
       </c>
       <c r="G41" t="n">
-        <v>-1</v>
+        <v>-0.4262</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9318</v>
+        <v>-2.1788</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9645</v>
+        <v>-2.3617</v>
       </c>
       <c r="J41" t="n">
-        <v>-1</v>
+        <v>-0.4262</v>
       </c>
       <c r="K41" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L41" t="n">
-        <v>47</v>
+        <v>151</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.9645</v>
+        <v>-2.7879</v>
       </c>
       <c r="N41" t="n">
-        <v>92</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-3.1399</v>
+        <v>-2.7674</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.2425</v>
+        <v>-1.0951</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.6948</v>
+        <v>-1.8874</v>
       </c>
       <c r="E42" t="n">
-        <v>-3.1399</v>
+        <v>-2.7674</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.3178</v>
+        <v>-1.7674</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.3178</v>
+        <v>-1.7674</v>
       </c>
       <c r="I42" t="n">
-        <v>-2.357</v>
+        <v>-1.9158</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-1</v>
       </c>
       <c r="K42" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L42" t="n">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="M42" t="n">
-        <v>-3.1791</v>
+        <v>-2.9158</v>
       </c>
       <c r="N42" t="n">
-        <v>201</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43">
@@ -2382,31 +2382,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-3.2478</v>
+        <v>-2.979</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.2852</v>
+        <v>-1.1788</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.7378</v>
+        <v>-1.9829</v>
       </c>
       <c r="E43" t="n">
-        <v>-3.2478</v>
+        <v>-2.979</v>
       </c>
       <c r="F43" t="n">
-        <v>-4.3172</v>
+        <v>-3.478</v>
       </c>
       <c r="G43" t="n">
-        <v>1.0694</v>
+        <v>0.499</v>
       </c>
       <c r="H43" t="n">
-        <v>-4.3172</v>
+        <v>-3.478</v>
       </c>
       <c r="I43" t="n">
-        <v>-4.4644</v>
+        <v>-4.0864</v>
       </c>
       <c r="J43" t="n">
-        <v>1.0694</v>
+        <v>0.499</v>
       </c>
       <c r="K43" t="n">
         <v>129</v>
@@ -2415,7 +2415,7 @@
         <v>145</v>
       </c>
       <c r="M43" t="n">
-        <v>-3.395</v>
+        <v>-3.5874</v>
       </c>
       <c r="N43" t="n">
         <v>274</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-3.6428</v>
+        <v>-3.0324</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.4415</v>
+        <v>-1.2</v>
       </c>
       <c r="D44" t="n">
-        <v>-1.8952</v>
+        <v>-2.007</v>
       </c>
       <c r="E44" t="n">
-        <v>-3.6428</v>
+        <v>-3.0324</v>
       </c>
       <c r="F44" t="n">
-        <v>-3.3879</v>
+        <v>-3.3465</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.2549</v>
+        <v>0.3141</v>
       </c>
       <c r="H44" t="n">
-        <v>-3.3879</v>
+        <v>-3.3465</v>
       </c>
       <c r="I44" t="n">
-        <v>-3.4452</v>
+        <v>-3.6274</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.2549</v>
+        <v>0.3141</v>
       </c>
       <c r="K44" t="n">
         <v>50</v>
@@ -2461,7 +2461,7 @@
         <v>300</v>
       </c>
       <c r="M44" t="n">
-        <v>-3.7001</v>
+        <v>-3.3133</v>
       </c>
       <c r="N44" t="n">
         <v>350</v>
@@ -2567,10 +2567,10 @@
         <v>0.7</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.92</v>
+        <v>-0.8879</v>
       </c>
       <c r="J2" t="n">
-        <v>-18.4</v>
+        <v>-17.758</v>
       </c>
     </row>
     <row r="3">
@@ -2607,10 +2607,10 @@
         <v>0.61</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1146</v>
+        <v>-1.1047</v>
       </c>
       <c r="J3" t="n">
-        <v>-22.292</v>
+        <v>-22.094</v>
       </c>
     </row>
     <row r="4">
@@ -2647,10 +2647,10 @@
         <v>0.42</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4932</v>
+        <v>-1.543</v>
       </c>
       <c r="J4" t="n">
-        <v>-29.864</v>
+        <v>-30.86</v>
       </c>
     </row>
     <row r="5">
@@ -2687,10 +2687,10 @@
         <v>2.12</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1966</v>
+        <v>1.8681</v>
       </c>
       <c r="J5" t="n">
-        <v>43.932</v>
+        <v>37.362</v>
       </c>
     </row>
     <row r="6">
@@ -2727,10 +2727,10 @@
         <v>1.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0953</v>
+        <v>1.0502</v>
       </c>
       <c r="J6" t="n">
-        <v>21.906</v>
+        <v>21.004</v>
       </c>
     </row>
     <row r="7">
@@ -2767,10 +2767,10 @@
         <v>1.36</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5745</v>
+        <v>0.6944</v>
       </c>
       <c r="J7" t="n">
-        <v>11.49</v>
+        <v>13.888</v>
       </c>
     </row>
     <row r="8">
@@ -2807,10 +2807,10 @@
         <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3151</v>
+        <v>0.3649</v>
       </c>
       <c r="J8" t="n">
-        <v>6.302</v>
+        <v>7.298</v>
       </c>
     </row>
     <row r="9">
@@ -2847,10 +2847,10 @@
         <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2468</v>
+        <v>-0.1417</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.936</v>
+        <v>-2.834</v>
       </c>
     </row>
     <row r="10">
@@ -2887,10 +2887,10 @@
         <v>1.15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2839</v>
+        <v>0.328</v>
       </c>
       <c r="J10" t="n">
-        <v>5.678</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="11">
@@ -2927,10 +2927,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4529</v>
+        <v>-0.2861</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.058</v>
+        <v>-5.722</v>
       </c>
     </row>
     <row r="12">
@@ -2967,10 +2967,10 @@
         <v>0.55</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6623</v>
+        <v>-0.4452</v>
       </c>
       <c r="J12" t="n">
-        <v>-19.869</v>
+        <v>-13.356</v>
       </c>
     </row>
     <row r="13">
@@ -3007,10 +3007,10 @@
         <v>0.4</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8478</v>
+        <v>-0.5839</v>
       </c>
       <c r="J13" t="n">
-        <v>-25.434</v>
+        <v>-17.517</v>
       </c>
     </row>
     <row r="14">
@@ -3047,10 +3047,10 @@
         <v>0.39</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8596</v>
+        <v>-0.5931</v>
       </c>
       <c r="J14" t="n">
-        <v>-25.788</v>
+        <v>-17.793</v>
       </c>
     </row>
     <row r="15">
@@ -3087,10 +3087,10 @@
         <v>1.39</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7287</v>
+        <v>0.7083</v>
       </c>
       <c r="J15" t="n">
-        <v>21.861</v>
+        <v>21.249</v>
       </c>
     </row>
     <row r="16">
@@ -3127,10 +3127,10 @@
         <v>1.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2539</v>
+        <v>0.1939</v>
       </c>
       <c r="J16" t="n">
-        <v>7.617</v>
+        <v>5.817</v>
       </c>
     </row>
     <row r="17">
@@ -3167,10 +3167,10 @@
         <v>0.62</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5817</v>
+        <v>-0.3863</v>
       </c>
       <c r="J17" t="n">
-        <v>-17.451</v>
+        <v>-11.589</v>
       </c>
     </row>
     <row r="18">
@@ -3207,10 +3207,10 @@
         <v>0.59</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6213</v>
+        <v>-0.4143</v>
       </c>
       <c r="J18" t="n">
-        <v>-18.639</v>
+        <v>-12.429</v>
       </c>
     </row>
     <row r="19">
@@ -3247,10 +3247,10 @@
         <v>0.41</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8427</v>
+        <v>-0.58</v>
       </c>
       <c r="J19" t="n">
-        <v>-25.281</v>
+        <v>-17.4</v>
       </c>
     </row>
     <row r="20">
@@ -3287,10 +3287,10 @@
         <v>1.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4582</v>
+        <v>0.3764</v>
       </c>
       <c r="J20" t="n">
-        <v>13.746</v>
+        <v>11.292</v>
       </c>
     </row>
     <row r="21">
@@ -3327,10 +3327,10 @@
         <v>1.19</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4438</v>
+        <v>0.3622</v>
       </c>
       <c r="J21" t="n">
-        <v>13.314</v>
+        <v>10.866</v>
       </c>
     </row>
     <row r="22">
@@ -3367,10 +3367,10 @@
         <v>0.75</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7742</v>
+        <v>-0.7369</v>
       </c>
       <c r="J22" t="n">
-        <v>-16.2582</v>
+        <v>-15.4749</v>
       </c>
     </row>
     <row r="23">
@@ -3407,10 +3407,10 @@
         <v>0.61</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0918</v>
+        <v>-1.0804</v>
       </c>
       <c r="J23" t="n">
-        <v>-22.9278</v>
+        <v>-22.6884</v>
       </c>
     </row>
     <row r="24">
@@ -3447,10 +3447,10 @@
         <v>0.34</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6322</v>
+        <v>-1.7068</v>
       </c>
       <c r="J24" t="n">
-        <v>-34.2762</v>
+        <v>-35.8428</v>
       </c>
     </row>
     <row r="25">
@@ -3487,10 +3487,10 @@
         <v>1.59</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5293</v>
+        <v>1.3468</v>
       </c>
       <c r="J25" t="n">
-        <v>32.1153</v>
+        <v>28.2828</v>
       </c>
     </row>
     <row r="26">
@@ -3527,10 +3527,10 @@
         <v>1.51</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3729</v>
+        <v>1.2374</v>
       </c>
       <c r="J26" t="n">
-        <v>28.8309</v>
+        <v>25.9854</v>
       </c>
     </row>
     <row r="27">
@@ -3567,10 +3567,10 @@
         <v>1.25</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4689</v>
+        <v>0.5458</v>
       </c>
       <c r="J27" t="n">
-        <v>9.8469</v>
+        <v>11.4618</v>
       </c>
     </row>
     <row r="28">
@@ -3607,10 +3607,10 @@
         <v>0.95</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1123</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.3583</v>
+        <v>-1.512</v>
       </c>
     </row>
     <row r="29">
@@ -3647,10 +3647,10 @@
         <v>0.88</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.247</v>
+        <v>-0.1511</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.187</v>
+        <v>-3.1731</v>
       </c>
     </row>
     <row r="30">
@@ -3687,10 +3687,10 @@
         <v>0.85</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2962</v>
+        <v>-0.1828</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.2202</v>
+        <v>-3.8388</v>
       </c>
     </row>
     <row r="31">
@@ -3727,10 +3727,10 @@
         <v>0.85</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2962</v>
+        <v>-0.1828</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.2202</v>
+        <v>-3.8388</v>
       </c>
     </row>
     <row r="32">
@@ -3767,10 +3767,10 @@
         <v>1.01</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0218</v>
+        <v>0.0356</v>
       </c>
       <c r="J32" t="n">
-        <v>0.654</v>
+        <v>1.068</v>
       </c>
     </row>
     <row r="33">
@@ -3807,10 +3807,10 @@
         <v>0.86</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2988</v>
+        <v>-0.1797</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.964</v>
+        <v>-5.391</v>
       </c>
     </row>
     <row r="34">
@@ -3847,10 +3847,10 @@
         <v>0.82</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3592</v>
+        <v>-0.2212</v>
       </c>
       <c r="J34" t="n">
-        <v>-10.776</v>
+        <v>-6.636</v>
       </c>
     </row>
     <row r="35">
@@ -3887,10 +3887,10 @@
         <v>1.35</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5775</v>
+        <v>0.6952</v>
       </c>
       <c r="J35" t="n">
-        <v>17.325</v>
+        <v>20.856</v>
       </c>
     </row>
     <row r="36">
@@ -3927,10 +3927,10 @@
         <v>1.06</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1463</v>
+        <v>0.1578</v>
       </c>
       <c r="J36" t="n">
-        <v>4.389</v>
+        <v>4.734</v>
       </c>
     </row>
     <row r="37">
@@ -3967,10 +3967,10 @@
         <v>0.54</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1974</v>
+        <v>-1.2024</v>
       </c>
       <c r="J37" t="n">
-        <v>-35.922</v>
+        <v>-36.072</v>
       </c>
     </row>
     <row r="38">
@@ -4007,10 +4007,10 @@
         <v>0.48</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3255</v>
+        <v>-1.3457</v>
       </c>
       <c r="J38" t="n">
-        <v>-39.765</v>
+        <v>-40.371</v>
       </c>
     </row>
     <row r="39">
@@ -4047,10 +4047,10 @@
         <v>0.36</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5697</v>
+        <v>-1.629</v>
       </c>
       <c r="J39" t="n">
-        <v>-47.091</v>
+        <v>-48.87</v>
       </c>
     </row>
     <row r="40">
@@ -4087,10 +4087,10 @@
         <v>1.4</v>
       </c>
       <c r="I40" t="n">
-        <v>1.244</v>
+        <v>1.158</v>
       </c>
       <c r="J40" t="n">
-        <v>37.32</v>
+        <v>34.74</v>
       </c>
     </row>
     <row r="41">
@@ -4127,10 +4127,10 @@
         <v>1.3</v>
       </c>
       <c r="I41" t="n">
-        <v>1.0243</v>
+        <v>0.9961</v>
       </c>
       <c r="J41" t="n">
-        <v>30.729</v>
+        <v>29.883</v>
       </c>
     </row>
     <row r="42">
@@ -4167,10 +4167,10 @@
         <v>0.98</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0097</v>
+        <v>-0.0196</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2134</v>
+        <v>-0.4312</v>
       </c>
     </row>
     <row r="43">
@@ -4207,10 +4207,10 @@
         <v>0.86</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2309</v>
+        <v>-0.1624</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.0798</v>
+        <v>-3.5728</v>
       </c>
     </row>
     <row r="44">
@@ -4247,10 +4247,10 @@
         <v>0.63</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5829</v>
+        <v>-0.385</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.8238</v>
+        <v>-8.470000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -4287,10 +4287,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.094</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.068</v>
+        <v>-1.892</v>
       </c>
     </row>
     <row r="46">
@@ -4327,10 +4327,10 @@
         <v>0.9</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1505</v>
+        <v>-0.1205</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.311</v>
+        <v>-2.651</v>
       </c>
     </row>
     <row r="47">
@@ -4367,10 +4367,10 @@
         <v>0.82</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.6233</v>
+        <v>-0.5735</v>
       </c>
       <c r="J47" t="n">
-        <v>-13.7126</v>
+        <v>-12.617</v>
       </c>
     </row>
     <row r="48">
@@ -4407,10 +4407,10 @@
         <v>0.67</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9771</v>
+        <v>-0.9517</v>
       </c>
       <c r="J48" t="n">
-        <v>-21.4962</v>
+        <v>-20.9374</v>
       </c>
     </row>
     <row r="49">
@@ -4447,10 +4447,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.2107</v>
+        <v>-1.2139</v>
       </c>
       <c r="J49" t="n">
-        <v>-26.6354</v>
+        <v>-26.7058</v>
       </c>
     </row>
     <row r="50">
@@ -4487,10 +4487,10 @@
         <v>1.59</v>
       </c>
       <c r="I50" t="n">
-        <v>1.4956</v>
+        <v>1.3203</v>
       </c>
       <c r="J50" t="n">
-        <v>32.9032</v>
+        <v>29.0466</v>
       </c>
     </row>
     <row r="51">
@@ -4527,10 +4527,10 @@
         <v>1.44</v>
       </c>
       <c r="I51" t="n">
-        <v>1.1979</v>
+        <v>1.1176</v>
       </c>
       <c r="J51" t="n">
-        <v>26.3538</v>
+        <v>24.5872</v>
       </c>
     </row>
     <row r="52">
@@ -4567,10 +4567,10 @@
         <v>0.68</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.8742</v>
+        <v>-0.8607</v>
       </c>
       <c r="J52" t="n">
-        <v>-23.6034</v>
+        <v>-23.2389</v>
       </c>
     </row>
     <row r="53">
@@ -4607,10 +4607,10 @@
         <v>0.57</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.13</v>
+        <v>-1.1287</v>
       </c>
       <c r="J53" t="n">
-        <v>-30.51</v>
+        <v>-30.4749</v>
       </c>
     </row>
     <row r="54">
@@ -4647,10 +4647,10 @@
         <v>0.26</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.763</v>
+        <v>-1.8615</v>
       </c>
       <c r="J54" t="n">
-        <v>-47.601</v>
+        <v>-50.2605</v>
       </c>
     </row>
     <row r="55">
@@ -4687,10 +4687,10 @@
         <v>1.37</v>
       </c>
       <c r="I55" t="n">
-        <v>1.1826</v>
+        <v>1.115</v>
       </c>
       <c r="J55" t="n">
-        <v>31.9302</v>
+        <v>30.105</v>
       </c>
     </row>
     <row r="56">
@@ -4727,10 +4727,10 @@
         <v>1.18</v>
       </c>
       <c r="I56" t="n">
-        <v>0.7396</v>
+        <v>0.6835</v>
       </c>
       <c r="J56" t="n">
-        <v>19.9692</v>
+        <v>18.4545</v>
       </c>
     </row>
     <row r="57">
@@ -4767,10 +4767,10 @@
         <v>0.92</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.215</v>
+        <v>-0.1199</v>
       </c>
       <c r="J57" t="n">
-        <v>-5.805</v>
+        <v>-3.2373</v>
       </c>
     </row>
     <row r="58">
@@ -4807,10 +4807,10 @@
         <v>0.89</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.265</v>
+        <v>-0.1537</v>
       </c>
       <c r="J58" t="n">
-        <v>-7.155</v>
+        <v>-4.1499</v>
       </c>
     </row>
     <row r="59">
@@ -4847,10 +4847,10 @@
         <v>0.5</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.7716</v>
+        <v>-0.5259</v>
       </c>
       <c r="J59" t="n">
-        <v>-20.8332</v>
+        <v>-14.1993</v>
       </c>
     </row>
     <row r="60">
@@ -4887,10 +4887,10 @@
         <v>1.82</v>
       </c>
       <c r="I60" t="n">
-        <v>1.0821</v>
+        <v>1.2439</v>
       </c>
       <c r="J60" t="n">
-        <v>29.2167</v>
+        <v>33.5853</v>
       </c>
     </row>
     <row r="61">
@@ -4927,10 +4927,10 @@
         <v>1.25</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4281</v>
+        <v>0.5054</v>
       </c>
       <c r="J61" t="n">
-        <v>11.5587</v>
+        <v>13.6458</v>
       </c>
     </row>
     <row r="62">
@@ -4967,10 +4967,10 @@
         <v>0.74</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.7779</v>
+        <v>-0.7466</v>
       </c>
       <c r="J62" t="n">
-        <v>-17.8917</v>
+        <v>-17.1718</v>
       </c>
     </row>
     <row r="63">
@@ -5007,10 +5007,10 @@
         <v>0.54</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.227</v>
+        <v>-1.233</v>
       </c>
       <c r="J63" t="n">
-        <v>-28.221</v>
+        <v>-28.359</v>
       </c>
     </row>
     <row r="64">
@@ -5047,10 +5047,10 @@
         <v>0.31</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.6822</v>
+        <v>-1.7659</v>
       </c>
       <c r="J64" t="n">
-        <v>-38.6906</v>
+        <v>-40.6157</v>
       </c>
     </row>
     <row r="65">
@@ -5087,10 +5087,10 @@
         <v>1.63</v>
       </c>
       <c r="I65" t="n">
-        <v>1.6369</v>
+        <v>1.4284</v>
       </c>
       <c r="J65" t="n">
-        <v>37.6487</v>
+        <v>32.8532</v>
       </c>
     </row>
     <row r="66">
@@ -5127,10 +5127,10 @@
         <v>1.34</v>
       </c>
       <c r="I66" t="n">
-        <v>1.0482</v>
+        <v>1.0123</v>
       </c>
       <c r="J66" t="n">
-        <v>24.1086</v>
+        <v>23.2829</v>
       </c>
     </row>
     <row r="67">
@@ -5167,10 +5167,10 @@
         <v>1.21</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3682</v>
+        <v>0.4327</v>
       </c>
       <c r="J67" t="n">
-        <v>8.4686</v>
+        <v>9.9521</v>
       </c>
     </row>
     <row r="68">
@@ -5207,10 +5207,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3237</v>
+        <v>0.3791</v>
       </c>
       <c r="J68" t="n">
-        <v>7.4451</v>
+        <v>8.7193</v>
       </c>
     </row>
     <row r="69">
@@ -5247,10 +5247,10 @@
         <v>1.06</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1037</v>
+        <v>0.149</v>
       </c>
       <c r="J69" t="n">
-        <v>2.3851</v>
+        <v>3.427</v>
       </c>
     </row>
     <row r="70">
@@ -5287,10 +5287,10 @@
         <v>1.18</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3237</v>
+        <v>0.3791</v>
       </c>
       <c r="J70" t="n">
-        <v>7.4451</v>
+        <v>8.7193</v>
       </c>
     </row>
     <row r="71">
@@ -5327,10 +5327,10 @@
         <v>0.8</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4013</v>
+        <v>-0.2486</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.229900000000001</v>
+        <v>-5.7178</v>
       </c>
     </row>
     <row r="72">
@@ -5367,10 +5367,10 @@
         <v>1.02</v>
       </c>
       <c r="I72" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0575</v>
       </c>
       <c r="J72" t="n">
-        <v>2.2575</v>
+        <v>1.4375</v>
       </c>
     </row>
     <row r="73">
@@ -5407,10 +5407,10 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.029</v>
+        <v>0.0056</v>
       </c>
       <c r="J73" t="n">
-        <v>0.725</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="74">
@@ -5447,10 +5447,10 @@
         <v>0.71</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.498</v>
+        <v>-0.3214</v>
       </c>
       <c r="J74" t="n">
-        <v>-12.45</v>
+        <v>-8.035</v>
       </c>
     </row>
     <row r="75">
@@ -5487,10 +5487,10 @@
         <v>1.14</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3102</v>
+        <v>0.26</v>
       </c>
       <c r="J75" t="n">
-        <v>7.755</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="76">
@@ -5527,10 +5527,10 @@
         <v>0.9</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2114</v>
+        <v>-0.1292</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.285</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="77">
@@ -5567,10 +5567,10 @@
         <v>0.72</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.4648</v>
+        <v>-0.3016</v>
       </c>
       <c r="J77" t="n">
-        <v>-11.62</v>
+        <v>-7.54</v>
       </c>
     </row>
     <row r="78">
@@ -5607,10 +5607,10 @@
         <v>0.36</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.9085</v>
+        <v>-0.6323</v>
       </c>
       <c r="J78" t="n">
-        <v>-22.7125</v>
+        <v>-15.8075</v>
       </c>
     </row>
     <row r="79">
@@ -5647,10 +5647,10 @@
         <v>0.35</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.9196</v>
+        <v>-0.6412</v>
       </c>
       <c r="J79" t="n">
-        <v>-22.99</v>
+        <v>-16.03</v>
       </c>
     </row>
     <row r="80">
@@ -5687,10 +5687,10 @@
         <v>1.61</v>
       </c>
       <c r="I80" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.8655</v>
       </c>
       <c r="J80" t="n">
-        <v>23.35</v>
+        <v>21.6375</v>
       </c>
     </row>
     <row r="81">
@@ -5727,10 +5727,10 @@
         <v>1.33</v>
       </c>
       <c r="I81" t="n">
-        <v>0.6041</v>
+        <v>0.5201</v>
       </c>
       <c r="J81" t="n">
-        <v>15.1025</v>
+        <v>13.0025</v>
       </c>
     </row>
     <row r="82">
@@ -5767,10 +5767,10 @@
         <v>0.96</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.3097</v>
+        <v>-0.2279</v>
       </c>
       <c r="J82" t="n">
-        <v>-5.2649</v>
+        <v>-3.8743</v>
       </c>
     </row>
     <row r="83">
@@ -5807,10 +5807,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.3734</v>
+        <v>-0.2935</v>
       </c>
       <c r="J83" t="n">
-        <v>-6.3478</v>
+        <v>-4.9895</v>
       </c>
     </row>
     <row r="84">
@@ -5847,10 +5847,10 @@
         <v>0.92</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.4326</v>
+        <v>-0.3552</v>
       </c>
       <c r="J84" t="n">
-        <v>-7.3542</v>
+        <v>-6.0384</v>
       </c>
     </row>
     <row r="85">
@@ -5887,10 +5887,10 @@
         <v>1.84</v>
       </c>
       <c r="I85" t="n">
-        <v>1.8311</v>
+        <v>1.5485</v>
       </c>
       <c r="J85" t="n">
-        <v>31.1287</v>
+        <v>26.3245</v>
       </c>
     </row>
     <row r="86">
@@ -5927,10 +5927,10 @@
         <v>1.56</v>
       </c>
       <c r="I86" t="n">
-        <v>1.3192</v>
+        <v>1.2067</v>
       </c>
       <c r="J86" t="n">
-        <v>22.4264</v>
+        <v>20.5139</v>
       </c>
     </row>
     <row r="87">
@@ -5967,10 +5967,10 @@
         <v>1.53</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7481</v>
+        <v>0.9331</v>
       </c>
       <c r="J87" t="n">
-        <v>12.7177</v>
+        <v>15.8627</v>
       </c>
     </row>
     <row r="88">
@@ -6007,10 +6007,10 @@
         <v>1.37</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5585</v>
+        <v>0.6829</v>
       </c>
       <c r="J88" t="n">
-        <v>9.4945</v>
+        <v>11.6093</v>
       </c>
     </row>
     <row r="89">
@@ -6047,10 +6047,10 @@
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0619</v>
+        <v>-0.0148</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.0523</v>
+        <v>-0.2516</v>
       </c>
     </row>
     <row r="90">
@@ -6087,10 +6087,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0183</v>
+        <v>0.0667</v>
       </c>
       <c r="J90" t="n">
-        <v>0.3111</v>
+        <v>1.1339</v>
       </c>
     </row>
     <row r="91">
@@ -6127,10 +6127,10 @@
         <v>0.87</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3131</v>
+        <v>-0.1841</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.3227</v>
+        <v>-3.1297</v>
       </c>
     </row>
     <row r="92">
@@ -6167,10 +6167,10 @@
         <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>0.014</v>
+        <v>0.0011</v>
       </c>
       <c r="J92" t="n">
-        <v>0.252</v>
+        <v>0.0198</v>
       </c>
     </row>
     <row r="93">
@@ -6207,10 +6207,10 @@
         <v>0.4</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.5229</v>
+        <v>-1.5771</v>
       </c>
       <c r="J93" t="n">
-        <v>-27.4122</v>
+        <v>-28.3878</v>
       </c>
     </row>
     <row r="94">
@@ -6247,10 +6247,10 @@
         <v>0.12</v>
       </c>
       <c r="I94" t="n">
-        <v>-2.0323</v>
+        <v>-2.1996</v>
       </c>
       <c r="J94" t="n">
-        <v>-36.5814</v>
+        <v>-39.5928</v>
       </c>
     </row>
     <row r="95">
@@ -6287,10 +6287,10 @@
         <v>2.01</v>
       </c>
       <c r="I95" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J95" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="96">
@@ -6327,10 +6327,10 @@
         <v>1.43</v>
       </c>
       <c r="I96" t="n">
-        <v>1.1912</v>
+        <v>1.113</v>
       </c>
       <c r="J96" t="n">
-        <v>21.4416</v>
+        <v>20.034</v>
       </c>
     </row>
     <row r="97">
@@ -6367,10 +6367,10 @@
         <v>1.39</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5797</v>
+        <v>0.7117</v>
       </c>
       <c r="J97" t="n">
-        <v>10.4346</v>
+        <v>12.8106</v>
       </c>
     </row>
     <row r="98">
@@ -6407,10 +6407,10 @@
         <v>1.37</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.6798</v>
       </c>
       <c r="J98" t="n">
-        <v>9.988200000000001</v>
+        <v>12.2364</v>
       </c>
     </row>
     <row r="99">
@@ -6447,10 +6447,10 @@
         <v>0.83</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3737</v>
+        <v>-0.227</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.7266</v>
+        <v>-4.086</v>
       </c>
     </row>
     <row r="100">
@@ -6487,10 +6487,10 @@
         <v>1.18</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2866</v>
+        <v>0.3645</v>
       </c>
       <c r="J100" t="n">
-        <v>5.1588</v>
+        <v>6.561</v>
       </c>
     </row>
     <row r="101">
@@ -6527,10 +6527,10 @@
         <v>1.09</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1271</v>
+        <v>0.1982</v>
       </c>
       <c r="J101" t="n">
-        <v>2.2878</v>
+        <v>3.5676</v>
       </c>
     </row>
     <row r="102">
@@ -6567,10 +6567,10 @@
         <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0555</v>
+        <v>0.0225</v>
       </c>
       <c r="J102" t="n">
-        <v>1.332</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="103">
@@ -6607,10 +6607,10 @@
         <v>0.92</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1307</v>
+        <v>-0.102</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.1368</v>
+        <v>-2.448</v>
       </c>
     </row>
     <row r="104">
@@ -6647,10 +6647,10 @@
         <v>0.66</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.5513</v>
+        <v>-0.3613</v>
       </c>
       <c r="J104" t="n">
-        <v>-13.2312</v>
+        <v>-8.671200000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6687,10 +6687,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0497</v>
+        <v>-0.0532</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.1928</v>
+        <v>-1.2768</v>
       </c>
     </row>
     <row r="106">
@@ -6727,10 +6727,10 @@
         <v>0.93</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1108</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="J106" t="n">
-        <v>-2.6592</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="107">
@@ -6767,10 +6767,10 @@
         <v>0.61</v>
       </c>
       <c r="I107" t="n">
-        <v>-1.1061</v>
+        <v>-1.0954</v>
       </c>
       <c r="J107" t="n">
-        <v>-26.5464</v>
+        <v>-26.2896</v>
       </c>
     </row>
     <row r="108">
@@ -6807,10 +6807,10 @@
         <v>0.59</v>
       </c>
       <c r="I108" t="n">
-        <v>-1.1481</v>
+        <v>-1.1428</v>
       </c>
       <c r="J108" t="n">
-        <v>-27.5544</v>
+        <v>-27.4272</v>
       </c>
     </row>
     <row r="109">
@@ -6847,10 +6847,10 @@
         <v>0.52</v>
       </c>
       <c r="I109" t="n">
-        <v>-1.2916</v>
+        <v>-1.3067</v>
       </c>
       <c r="J109" t="n">
-        <v>-30.9984</v>
+        <v>-31.3608</v>
       </c>
     </row>
     <row r="110">
@@ -6887,10 +6887,10 @@
         <v>1.73</v>
       </c>
       <c r="I110" t="n">
-        <v>1.7373</v>
+        <v>1.2316</v>
       </c>
       <c r="J110" t="n">
-        <v>41.6952</v>
+        <v>29.5584</v>
       </c>
     </row>
     <row r="111">
@@ -6927,10 +6927,10 @@
         <v>1.62</v>
       </c>
       <c r="I111" t="n">
-        <v>1.5539</v>
+        <v>1.0873</v>
       </c>
       <c r="J111" t="n">
-        <v>37.2936</v>
+        <v>26.0952</v>
       </c>
     </row>
     <row r="112">
@@ -6967,10 +6967,10 @@
         <v>1.41</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6454</v>
+        <v>0.6017</v>
       </c>
       <c r="J112" t="n">
-        <v>17.4258</v>
+        <v>16.2459</v>
       </c>
     </row>
     <row r="113">
@@ -7007,10 +7007,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.3777</v>
+        <v>-0.2333</v>
       </c>
       <c r="J113" t="n">
-        <v>-10.1979</v>
+        <v>-6.2991</v>
       </c>
     </row>
     <row r="114">
@@ -7047,10 +7047,10 @@
         <v>0.62</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.6269</v>
+        <v>-0.4148</v>
       </c>
       <c r="J114" t="n">
-        <v>-16.9263</v>
+        <v>-11.1996</v>
       </c>
     </row>
     <row r="115">
@@ -7087,10 +7087,10 @@
         <v>1.36</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5841</v>
+        <v>0.5527</v>
       </c>
       <c r="J115" t="n">
-        <v>15.7707</v>
+        <v>14.9229</v>
       </c>
     </row>
     <row r="116">
@@ -7127,10 +7127,10 @@
         <v>0.99</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0593</v>
+        <v>-0.0238</v>
       </c>
       <c r="J116" t="n">
-        <v>-1.6011</v>
+        <v>-0.6425999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7167,10 +7167,10 @@
         <v>0.8</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.6166</v>
+        <v>-0.5883</v>
       </c>
       <c r="J117" t="n">
-        <v>-16.6482</v>
+        <v>-15.8841</v>
       </c>
     </row>
     <row r="118">
@@ -7207,10 +7207,10 @@
         <v>0.71</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.8163</v>
       </c>
       <c r="J118" t="n">
-        <v>-22.7664</v>
+        <v>-22.0401</v>
       </c>
     </row>
     <row r="119">
@@ -7247,10 +7247,10 @@
         <v>0.63</v>
       </c>
       <c r="I119" t="n">
-        <v>-1.0277</v>
+        <v>-1.0125</v>
       </c>
       <c r="J119" t="n">
-        <v>-27.7479</v>
+        <v>-27.3375</v>
       </c>
     </row>
     <row r="120">
@@ -7287,10 +7287,10 @@
         <v>1.25</v>
       </c>
       <c r="I120" t="n">
-        <v>0.8537</v>
+        <v>0.6148</v>
       </c>
       <c r="J120" t="n">
-        <v>23.0499</v>
+        <v>16.5996</v>
       </c>
     </row>
     <row r="121">
@@ -7327,10 +7327,10 @@
         <v>1.09</v>
       </c>
       <c r="I121" t="n">
-        <v>0.436</v>
+        <v>0.3518</v>
       </c>
       <c r="J121" t="n">
-        <v>11.772</v>
+        <v>9.4986</v>
       </c>
     </row>
     <row r="122">
@@ -7367,10 +7367,10 @@
         <v>1.4</v>
       </c>
       <c r="I122" t="n">
-        <v>1.0342</v>
+        <v>0.746</v>
       </c>
       <c r="J122" t="n">
-        <v>42.4022</v>
+        <v>30.586</v>
       </c>
     </row>
     <row r="123">
@@ -7407,10 +7407,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3445</v>
+        <v>0.3684</v>
       </c>
       <c r="J123" t="n">
-        <v>14.1245</v>
+        <v>15.1044</v>
       </c>
     </row>
     <row r="124">
@@ -7447,10 +7447,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2853</v>
+        <v>0.3342</v>
       </c>
       <c r="J124" t="n">
-        <v>11.6973</v>
+        <v>13.7022</v>
       </c>
     </row>
     <row r="125">
@@ -7487,10 +7487,10 @@
         <v>1.09</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2255</v>
+        <v>0.2824</v>
       </c>
       <c r="J125" t="n">
-        <v>9.2455</v>
+        <v>11.5784</v>
       </c>
     </row>
     <row r="126">
@@ -7527,10 +7527,10 @@
         <v>1.09</v>
       </c>
       <c r="I126" t="n">
-        <v>0.2255</v>
+        <v>0.2824</v>
       </c>
       <c r="J126" t="n">
-        <v>9.2455</v>
+        <v>11.5784</v>
       </c>
     </row>
     <row r="127">
@@ -7567,10 +7567,10 @@
         <v>1.07</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1905</v>
+        <v>0.1935</v>
       </c>
       <c r="J127" t="n">
-        <v>7.8105</v>
+        <v>7.9335</v>
       </c>
     </row>
     <row r="128">
@@ -7607,10 +7607,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1718</v>
+        <v>0.1713</v>
       </c>
       <c r="J128" t="n">
-        <v>7.0438</v>
+        <v>7.0233</v>
       </c>
     </row>
     <row r="129">
@@ -7647,10 +7647,10 @@
         <v>1.02</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0876</v>
+        <v>0.0737</v>
       </c>
       <c r="J129" t="n">
-        <v>3.5916</v>
+        <v>3.0217</v>
       </c>
     </row>
     <row r="130">
@@ -7687,10 +7687,10 @@
         <v>0.88</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2484</v>
+        <v>-0.1516</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.1844</v>
+        <v>-6.2156</v>
       </c>
     </row>
     <row r="131">
@@ -7727,10 +7727,10 @@
         <v>0.77</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4169</v>
+        <v>-0.264</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.0929</v>
+        <v>-10.824</v>
       </c>
     </row>
     <row r="132">
@@ -7767,10 +7767,10 @@
         <v>1.82</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6468</v>
+        <v>1.1718</v>
       </c>
       <c r="J132" t="n">
-        <v>29.6424</v>
+        <v>21.0924</v>
       </c>
     </row>
     <row r="133">
@@ -7807,10 +7807,10 @@
         <v>1.68</v>
       </c>
       <c r="I133" t="n">
-        <v>1.3882</v>
+        <v>1.0159</v>
       </c>
       <c r="J133" t="n">
-        <v>24.9876</v>
+        <v>18.2862</v>
       </c>
     </row>
     <row r="134">
@@ -7847,10 +7847,10 @@
         <v>1.62</v>
       </c>
       <c r="I134" t="n">
-        <v>1.2654</v>
+        <v>0.9489</v>
       </c>
       <c r="J134" t="n">
-        <v>22.7772</v>
+        <v>17.0802</v>
       </c>
     </row>
     <row r="135">
@@ -7887,10 +7887,10 @@
         <v>1.46</v>
       </c>
       <c r="I135" t="n">
-        <v>0.9154</v>
+        <v>0.7639</v>
       </c>
       <c r="J135" t="n">
-        <v>16.4772</v>
+        <v>13.7502</v>
       </c>
     </row>
     <row r="136">
@@ -7927,10 +7927,10 @@
         <v>1.41</v>
       </c>
       <c r="I136" t="n">
-        <v>0.8131</v>
+        <v>0.7022</v>
       </c>
       <c r="J136" t="n">
-        <v>14.6358</v>
+        <v>12.6396</v>
       </c>
     </row>
     <row r="137">
@@ -7967,10 +7967,10 @@
         <v>0.79</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1363</v>
+        <v>-0.1325</v>
       </c>
       <c r="J137" t="n">
-        <v>-2.4534</v>
+        <v>-2.385</v>
       </c>
     </row>
     <row r="138">
@@ -8007,10 +8007,10 @@
         <v>0.68</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.3054</v>
+        <v>-0.2616</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.4972</v>
+        <v>-4.7088</v>
       </c>
     </row>
     <row r="139">
@@ -8047,10 +8047,10 @@
         <v>0.39</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.7905</v>
+        <v>-0.5476</v>
       </c>
       <c r="J139" t="n">
-        <v>-14.229</v>
+        <v>-9.8568</v>
       </c>
     </row>
     <row r="140">
@@ -8087,10 +8087,10 @@
         <v>0.32</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.8889</v>
+        <v>-0.617</v>
       </c>
       <c r="J140" t="n">
-        <v>-16.0002</v>
+        <v>-11.106</v>
       </c>
     </row>
     <row r="141">
@@ -8127,10 +8127,10 @@
         <v>0.29</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.9292</v>
+        <v>-0.6472</v>
       </c>
       <c r="J141" t="n">
-        <v>-16.7256</v>
+        <v>-11.6496</v>
       </c>
     </row>
     <row r="142">
@@ -8167,10 +8167,10 @@
         <v>1.34</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6107</v>
+        <v>0.5727</v>
       </c>
       <c r="J142" t="n">
-        <v>17.0996</v>
+        <v>16.0356</v>
       </c>
     </row>
     <row r="143">
@@ -8207,10 +8207,10 @@
         <v>0.99</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0223</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>0.6244</v>
+        <v>-0.238</v>
       </c>
     </row>
     <row r="144">
@@ -8247,10 +8247,10 @@
         <v>0.82</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3208</v>
+        <v>-0.2056</v>
       </c>
       <c r="J144" t="n">
-        <v>-8.9824</v>
+        <v>-5.7568</v>
       </c>
     </row>
     <row r="145">
@@ -8287,10 +8287,10 @@
         <v>0.74</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4411</v>
+        <v>-0.2845</v>
       </c>
       <c r="J145" t="n">
-        <v>-12.3508</v>
+        <v>-7.966</v>
       </c>
     </row>
     <row r="146">
@@ -8327,10 +8327,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6773</v>
+        <v>-0.4536</v>
       </c>
       <c r="J146" t="n">
-        <v>-18.9644</v>
+        <v>-12.7008</v>
       </c>
     </row>
     <row r="147">
@@ -8367,10 +8367,10 @@
         <v>1.64</v>
       </c>
       <c r="I147" t="n">
-        <v>1.5055</v>
+        <v>1.0523</v>
       </c>
       <c r="J147" t="n">
-        <v>42.154</v>
+        <v>29.4644</v>
       </c>
     </row>
     <row r="148">
@@ -8407,10 +8407,10 @@
         <v>1.33</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8756</v>
+        <v>0.65</v>
       </c>
       <c r="J148" t="n">
-        <v>24.5168</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="149">
@@ -8447,10 +8447,10 @@
         <v>1.05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0949</v>
+        <v>0.1587</v>
       </c>
       <c r="J149" t="n">
-        <v>2.6572</v>
+        <v>4.4436</v>
       </c>
     </row>
     <row r="150">
@@ -8487,10 +8487,10 @@
         <v>0.93</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3818</v>
+        <v>-0.3073</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.6904</v>
+        <v>-8.6044</v>
       </c>
     </row>
     <row r="151">
@@ -8527,10 +8527,10 @@
         <v>0.92</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4114</v>
+        <v>-0.3378</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.5192</v>
+        <v>-9.458399999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8567,10 +8567,10 @@
         <v>1.38</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5764</v>
+        <v>0.4326</v>
       </c>
       <c r="J152" t="n">
-        <v>17.292</v>
+        <v>12.978</v>
       </c>
     </row>
     <row r="153">
@@ -8607,10 +8607,10 @@
         <v>1.29</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4607</v>
+        <v>0.3707</v>
       </c>
       <c r="J153" t="n">
-        <v>13.821</v>
+        <v>11.121</v>
       </c>
     </row>
     <row r="154">
@@ -8647,10 +8647,10 @@
         <v>1.18</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3017</v>
+        <v>0.2624</v>
       </c>
       <c r="J154" t="n">
-        <v>9.051</v>
+        <v>7.872</v>
       </c>
     </row>
     <row r="155">
@@ -8687,10 +8687,10 @@
         <v>0.95</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1769</v>
+        <v>-0.0906</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.307</v>
+        <v>-2.718</v>
       </c>
     </row>
     <row r="156">
@@ -8727,10 +8727,10 @@
         <v>0.91</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2468</v>
+        <v>-0.1383</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.404</v>
+        <v>-4.149</v>
       </c>
     </row>
     <row r="157">
@@ -8767,10 +8767,10 @@
         <v>1.16</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3475</v>
+        <v>0.2947</v>
       </c>
       <c r="J157" t="n">
-        <v>10.425</v>
+        <v>8.840999999999999</v>
       </c>
     </row>
     <row r="158">
@@ -8807,10 +8807,10 @@
         <v>1.04</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1421</v>
+        <v>0.1002</v>
       </c>
       <c r="J158" t="n">
-        <v>4.263</v>
+        <v>3.006</v>
       </c>
     </row>
     <row r="159">
@@ -8847,10 +8847,10 @@
         <v>0.91</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1846</v>
+        <v>-0.1164</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.538</v>
+        <v>-3.492</v>
       </c>
     </row>
     <row r="160">
@@ -8887,10 +8887,10 @@
         <v>0.79</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3818</v>
+        <v>-0.2413</v>
       </c>
       <c r="J160" t="n">
-        <v>-11.454</v>
+        <v>-7.239</v>
       </c>
     </row>
     <row r="161">
@@ -8927,10 +8927,10 @@
         <v>0.78</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3964</v>
+        <v>-0.2512</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.892</v>
+        <v>-7.536</v>
       </c>
     </row>
     <row r="162">
@@ -8967,10 +8967,10 @@
         <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2101</v>
+        <v>0.2163</v>
       </c>
       <c r="J162" t="n">
-        <v>6.0929</v>
+        <v>6.2727</v>
       </c>
     </row>
     <row r="163">
@@ -9007,10 +9007,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0593</v>
+        <v>-0.0469</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.7197</v>
+        <v>-1.3601</v>
       </c>
     </row>
     <row r="164">
@@ -9047,10 +9047,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0599</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.4389</v>
+        <v>-1.7371</v>
       </c>
     </row>
     <row r="165">
@@ -9087,10 +9087,10 @@
         <v>0.91</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.194</v>
+        <v>-0.1183</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.626</v>
+        <v>-3.4307</v>
       </c>
     </row>
     <row r="166">
@@ -9127,10 +9127,10 @@
         <v>0.86</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2801</v>
+        <v>-0.1724</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.1229</v>
+        <v>-4.9996</v>
       </c>
     </row>
     <row r="167">
@@ -9167,10 +9167,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0679</v>
+        <v>0.7651</v>
       </c>
       <c r="J167" t="n">
-        <v>30.9691</v>
+        <v>22.1879</v>
       </c>
     </row>
     <row r="168">
@@ -9207,10 +9207,10 @@
         <v>1.36</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9606</v>
+        <v>0.6979</v>
       </c>
       <c r="J168" t="n">
-        <v>27.8574</v>
+        <v>20.2391</v>
       </c>
     </row>
     <row r="169">
@@ -9247,10 +9247,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.003</v>
+        <v>0.0625</v>
       </c>
       <c r="J169" t="n">
-        <v>0.08699999999999999</v>
+        <v>1.8125</v>
       </c>
     </row>
     <row r="170">
@@ -9287,10 +9287,10 @@
         <v>0.99</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1581</v>
+        <v>-0.0882</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.5849</v>
+        <v>-2.5578</v>
       </c>
     </row>
     <row r="171">
@@ -9327,10 +9327,10 @@
         <v>0.92</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3996</v>
+        <v>-0.3289</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.5884</v>
+        <v>-9.5381</v>
       </c>
     </row>
     <row r="172">
@@ -9367,10 +9367,10 @@
         <v>1.13</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4403</v>
+        <v>0.3801</v>
       </c>
       <c r="J172" t="n">
-        <v>14.9702</v>
+        <v>12.9234</v>
       </c>
     </row>
     <row r="173">
@@ -9407,10 +9407,10 @@
         <v>1.07</v>
       </c>
       <c r="I173" t="n">
-        <v>0.248</v>
+        <v>0.2441</v>
       </c>
       <c r="J173" t="n">
-        <v>8.432</v>
+        <v>8.2994</v>
       </c>
     </row>
     <row r="174">
@@ -9447,10 +9447,10 @@
         <v>0.96</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2391</v>
+        <v>-0.1811</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.1294</v>
+        <v>-6.1574</v>
       </c>
     </row>
     <row r="175">
@@ -9487,10 +9487,10 @@
         <v>1.15</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4967</v>
+        <v>0.4116</v>
       </c>
       <c r="J175" t="n">
-        <v>16.8878</v>
+        <v>13.9944</v>
       </c>
     </row>
     <row r="176">
@@ -9527,10 +9527,10 @@
         <v>1.01</v>
       </c>
       <c r="I176" t="n">
-        <v>0.0016</v>
+        <v>0.0408</v>
       </c>
       <c r="J176" t="n">
-        <v>0.0544</v>
+        <v>1.3872</v>
       </c>
     </row>
     <row r="177">
@@ -9567,10 +9567,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.371</v>
+        <v>-0.2299</v>
       </c>
       <c r="J177" t="n">
-        <v>-12.614</v>
+        <v>-7.8166</v>
       </c>
     </row>
     <row r="178">
@@ -9607,10 +9607,10 @@
         <v>0.8</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.3854</v>
+        <v>-0.2399</v>
       </c>
       <c r="J178" t="n">
-        <v>-13.1036</v>
+        <v>-8.156599999999999</v>
       </c>
     </row>
     <row r="179">
@@ -9647,10 +9647,10 @@
         <v>0.74</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.4688</v>
+        <v>-0.2989</v>
       </c>
       <c r="J179" t="n">
-        <v>-15.9392</v>
+        <v>-10.1626</v>
       </c>
     </row>
     <row r="180">
@@ -9687,10 +9687,10 @@
         <v>1.46</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7147</v>
+        <v>0.6579</v>
       </c>
       <c r="J180" t="n">
-        <v>24.2998</v>
+        <v>22.3686</v>
       </c>
     </row>
     <row r="181">
@@ -9727,10 +9727,10 @@
         <v>1.23</v>
       </c>
       <c r="I181" t="n">
-        <v>0.4233</v>
+        <v>0.4263</v>
       </c>
       <c r="J181" t="n">
-        <v>14.3922</v>
+        <v>14.4942</v>
       </c>
     </row>
     <row r="182">
@@ -9767,10 +9767,10 @@
         <v>1.09</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2159</v>
+        <v>0.2782</v>
       </c>
       <c r="J182" t="n">
-        <v>7.7724</v>
+        <v>10.0152</v>
       </c>
     </row>
     <row r="183">
@@ -9807,10 +9807,10 @@
         <v>1.09</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2159</v>
+        <v>0.2782</v>
       </c>
       <c r="J183" t="n">
-        <v>7.7724</v>
+        <v>10.0152</v>
       </c>
     </row>
     <row r="184">
@@ -9847,10 +9847,10 @@
         <v>1</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1165</v>
+        <v>-0.0441</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.194</v>
+        <v>-1.5876</v>
       </c>
     </row>
     <row r="185">
@@ -9887,10 +9887,10 @@
         <v>1.66</v>
       </c>
       <c r="I185" t="n">
-        <v>1.5388</v>
+        <v>1.0748</v>
       </c>
       <c r="J185" t="n">
-        <v>55.3968</v>
+        <v>38.6928</v>
       </c>
     </row>
     <row r="186">
@@ -9927,10 +9927,10 @@
         <v>1.07</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1551</v>
+        <v>0.2193</v>
       </c>
       <c r="J186" t="n">
-        <v>5.5836</v>
+        <v>7.8948</v>
       </c>
     </row>
     <row r="187">
@@ -9967,10 +9967,10 @@
         <v>0.95</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1423</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>-5.1228</v>
+        <v>-2.7972</v>
       </c>
     </row>
     <row r="188">
@@ -10007,10 +10007,10 @@
         <v>0.78</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.416</v>
+        <v>-0.261</v>
       </c>
       <c r="J188" t="n">
-        <v>-14.976</v>
+        <v>-9.396000000000001</v>
       </c>
     </row>
     <row r="189">
@@ -10047,10 +10047,10 @@
         <v>0.6</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.6484</v>
+        <v>-0.4311</v>
       </c>
       <c r="J189" t="n">
-        <v>-23.3424</v>
+        <v>-15.5196</v>
       </c>
     </row>
     <row r="190">
@@ -10087,10 +10087,10 @@
         <v>1.46</v>
       </c>
       <c r="I190" t="n">
-        <v>0.7114</v>
+        <v>0.6552</v>
       </c>
       <c r="J190" t="n">
-        <v>25.6104</v>
+        <v>23.5872</v>
       </c>
     </row>
     <row r="191">
@@ -10127,10 +10127,10 @@
         <v>1.3</v>
       </c>
       <c r="I191" t="n">
-        <v>0.5142</v>
+        <v>0.4969</v>
       </c>
       <c r="J191" t="n">
-        <v>18.5112</v>
+        <v>17.8884</v>
       </c>
     </row>
     <row r="192">
@@ -10167,10 +10167,10 @@
         <v>1.44</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1601</v>
+        <v>1.0946</v>
       </c>
       <c r="J192" t="n">
-        <v>29.0025</v>
+        <v>27.365</v>
       </c>
     </row>
     <row r="193">
@@ -10207,10 +10207,10 @@
         <v>1.08</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2546</v>
+        <v>0.2702</v>
       </c>
       <c r="J193" t="n">
-        <v>6.365</v>
+        <v>6.755</v>
       </c>
     </row>
     <row r="194">
@@ -10247,10 +10247,10 @@
         <v>1.01</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0108</v>
+        <v>0.0359</v>
       </c>
       <c r="J194" t="n">
-        <v>-0.27</v>
+        <v>0.8975</v>
       </c>
     </row>
     <row r="195">
@@ -10287,10 +10287,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2832</v>
+        <v>-0.2199</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.08</v>
+        <v>-5.4975</v>
       </c>
     </row>
     <row r="196">
@@ -10327,10 +10327,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3158</v>
+        <v>-0.252</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.895</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="197">
@@ -10367,10 +10367,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.54</v>
+        <v>0.6425</v>
       </c>
       <c r="J197" t="n">
-        <v>13.5</v>
+        <v>16.0625</v>
       </c>
     </row>
     <row r="198">
@@ -10407,10 +10407,10 @@
         <v>1.11</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2524</v>
+        <v>0.272</v>
       </c>
       <c r="J198" t="n">
-        <v>6.31</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="199">
@@ -10447,10 +10447,10 @@
         <v>1.1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2356</v>
+        <v>0.2516</v>
       </c>
       <c r="J199" t="n">
-        <v>5.89</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="200">
@@ -10487,10 +10487,10 @@
         <v>0.72</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4901</v>
+        <v>-0.3149</v>
       </c>
       <c r="J200" t="n">
-        <v>-12.2525</v>
+        <v>-7.8725</v>
       </c>
     </row>
     <row r="201">
@@ -10527,10 +10527,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5682</v>
+        <v>-0.3716</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.205</v>
+        <v>-9.289999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10567,10 +10567,10 @@
         <v>1.25</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4854</v>
+        <v>0.433</v>
       </c>
       <c r="J202" t="n">
-        <v>14.0766</v>
+        <v>12.557</v>
       </c>
     </row>
     <row r="203">
@@ -10607,10 +10607,10 @@
         <v>1.06</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1916</v>
+        <v>0.1423</v>
       </c>
       <c r="J203" t="n">
-        <v>5.5564</v>
+        <v>4.1267</v>
       </c>
     </row>
     <row r="204">
@@ -10647,10 +10647,10 @@
         <v>1.04</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1526</v>
+        <v>0.106</v>
       </c>
       <c r="J204" t="n">
-        <v>4.4254</v>
+        <v>3.074</v>
       </c>
     </row>
     <row r="205">
@@ -10687,10 +10687,10 @@
         <v>0.63</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5934</v>
+        <v>-0.3914</v>
       </c>
       <c r="J205" t="n">
-        <v>-17.2086</v>
+        <v>-11.3506</v>
       </c>
     </row>
     <row r="206">
@@ -10727,10 +10727,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6684</v>
+        <v>-0.4468</v>
       </c>
       <c r="J206" t="n">
-        <v>-19.3836</v>
+        <v>-12.9572</v>
       </c>
     </row>
     <row r="207">
@@ -10767,10 +10767,10 @@
         <v>1.28</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4466</v>
+        <v>0.3841</v>
       </c>
       <c r="J207" t="n">
-        <v>12.9514</v>
+        <v>11.1389</v>
       </c>
     </row>
     <row r="208">
@@ -10807,10 +10807,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3621</v>
+        <v>0.3117</v>
       </c>
       <c r="J208" t="n">
-        <v>10.5009</v>
+        <v>9.039300000000001</v>
       </c>
     </row>
     <row r="209">
@@ -10847,10 +10847,10 @@
         <v>1.21</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3473</v>
+        <v>0.2994</v>
       </c>
       <c r="J209" t="n">
-        <v>10.0717</v>
+        <v>8.682600000000001</v>
       </c>
     </row>
     <row r="210">
@@ -10887,10 +10887,10 @@
         <v>1.18</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3009</v>
+        <v>0.2622</v>
       </c>
       <c r="J210" t="n">
-        <v>8.726100000000001</v>
+        <v>7.6038</v>
       </c>
     </row>
     <row r="211">
@@ -10927,10 +10927,10 @@
         <v>0.83</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3691</v>
+        <v>-0.2242</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.7039</v>
+        <v>-6.5018</v>
       </c>
     </row>
     <row r="212">
@@ -10967,10 +10967,10 @@
         <v>1.38</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9821</v>
       </c>
       <c r="J212" t="n">
-        <v>27.846</v>
+        <v>27.4988</v>
       </c>
     </row>
     <row r="213">
@@ -11007,10 +11007,10 @@
         <v>1.28</v>
       </c>
       <c r="I213" t="n">
-        <v>0.769</v>
+        <v>0.7593</v>
       </c>
       <c r="J213" t="n">
-        <v>21.532</v>
+        <v>21.2604</v>
       </c>
     </row>
     <row r="214">
@@ -11047,10 +11047,10 @@
         <v>1.14</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3794</v>
+        <v>0.4195</v>
       </c>
       <c r="J214" t="n">
-        <v>10.6232</v>
+        <v>11.746</v>
       </c>
     </row>
     <row r="215">
@@ -11087,10 +11087,10 @@
         <v>1.03</v>
       </c>
       <c r="I215" t="n">
-        <v>0.0328</v>
+        <v>0.095</v>
       </c>
       <c r="J215" t="n">
-        <v>0.9184</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="216">
@@ -11127,10 +11127,10 @@
         <v>0.96</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2807</v>
+        <v>-0.2062</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.8596</v>
+        <v>-5.7736</v>
       </c>
     </row>
     <row r="217">
@@ -11167,10 +11167,10 @@
         <v>1.09</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2452</v>
+        <v>0.2523</v>
       </c>
       <c r="J217" t="n">
-        <v>6.8656</v>
+        <v>7.0644</v>
       </c>
     </row>
     <row r="218">
@@ -11207,10 +11207,10 @@
         <v>1.04</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1526</v>
+        <v>0.1386</v>
       </c>
       <c r="J218" t="n">
-        <v>4.2728</v>
+        <v>3.8808</v>
       </c>
     </row>
     <row r="219">
@@ -11247,10 +11247,10 @@
         <v>0.9</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1888</v>
+        <v>-0.125</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.2864</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="220">
@@ -11287,10 +11287,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3437</v>
+        <v>-0.2181</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.6236</v>
+        <v>-6.1068</v>
       </c>
     </row>
     <row r="221">
@@ -11327,10 +11327,10 @@
         <v>0.71</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4881</v>
+        <v>-0.3159</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.6668</v>
+        <v>-8.8452</v>
       </c>
     </row>
     <row r="222">
@@ -11367,10 +11367,10 @@
         <v>1.28</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4312</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="J222" t="n">
-        <v>9.055199999999999</v>
+        <v>11.1237</v>
       </c>
     </row>
     <row r="223">
@@ -11407,10 +11407,10 @@
         <v>1.25</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3888</v>
+        <v>0.4801</v>
       </c>
       <c r="J223" t="n">
-        <v>8.1648</v>
+        <v>10.0821</v>
       </c>
     </row>
     <row r="224">
@@ -11447,10 +11447,10 @@
         <v>1.2</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3111</v>
+        <v>0.3965</v>
       </c>
       <c r="J224" t="n">
-        <v>6.5331</v>
+        <v>8.326499999999999</v>
       </c>
     </row>
     <row r="225">
@@ -11487,10 +11487,10 @@
         <v>1.28</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4312</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="J225" t="n">
-        <v>9.055199999999999</v>
+        <v>11.1237</v>
       </c>
     </row>
     <row r="226">
@@ -11527,10 +11527,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.205</v>
+        <v>-0.1078</v>
       </c>
       <c r="J226" t="n">
-        <v>-4.305</v>
+        <v>-2.2638</v>
       </c>
     </row>
     <row r="227">
@@ -11567,10 +11567,10 @@
         <v>0.74</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.786</v>
       </c>
       <c r="J227" t="n">
-        <v>-17.3481</v>
+        <v>-16.506</v>
       </c>
     </row>
     <row r="228">
@@ -11607,10 +11607,10 @@
         <v>0.61</v>
       </c>
       <c r="I228" t="n">
-        <v>-1.1123</v>
+        <v>-1.1021</v>
       </c>
       <c r="J228" t="n">
-        <v>-23.3583</v>
+        <v>-23.1441</v>
       </c>
     </row>
     <row r="229">
@@ -11647,10 +11647,10 @@
         <v>0.46</v>
       </c>
       <c r="I229" t="n">
-        <v>-1.4148</v>
+        <v>-1.4504</v>
       </c>
       <c r="J229" t="n">
-        <v>-29.7108</v>
+        <v>-30.4584</v>
       </c>
     </row>
     <row r="230">
@@ -11687,10 +11687,10 @@
         <v>2.03</v>
       </c>
       <c r="I230" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J230" t="n">
-        <v>43.2453</v>
+        <v>38.5098</v>
       </c>
     </row>
     <row r="231">
@@ -11727,10 +11727,10 @@
         <v>1.36</v>
       </c>
       <c r="I231" t="n">
-        <v>1.0152</v>
+        <v>0.9878</v>
       </c>
       <c r="J231" t="n">
-        <v>21.3192</v>
+        <v>20.7438</v>
       </c>
     </row>
     <row r="232">
@@ -11767,10 +11767,10 @@
         <v>1.47</v>
       </c>
       <c r="I232" t="n">
-        <v>0.6935</v>
+        <v>0.8575</v>
       </c>
       <c r="J232" t="n">
-        <v>16.644</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="233">
@@ -11807,10 +11807,10 @@
         <v>1.2</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3443</v>
+        <v>0.4093</v>
       </c>
       <c r="J233" t="n">
-        <v>8.263199999999999</v>
+        <v>9.8232</v>
       </c>
     </row>
     <row r="234">
@@ -11847,10 +11847,10 @@
         <v>1.08</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1309</v>
+        <v>0.1872</v>
       </c>
       <c r="J234" t="n">
-        <v>3.1416</v>
+        <v>4.4928</v>
       </c>
     </row>
     <row r="235">
@@ -11887,10 +11887,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2404</v>
+        <v>-0.1352</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.7696</v>
+        <v>-3.2448</v>
       </c>
     </row>
     <row r="236">
@@ -11927,10 +11927,10 @@
         <v>0.9</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2569</v>
+        <v>-0.1464</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.1656</v>
+        <v>-3.5136</v>
       </c>
     </row>
     <row r="237">
@@ -11967,10 +11967,10 @@
         <v>0.9</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.4215</v>
+        <v>-0.3632</v>
       </c>
       <c r="J237" t="n">
-        <v>-10.116</v>
+        <v>-8.716799999999999</v>
       </c>
     </row>
     <row r="238">
@@ -12007,10 +12007,10 @@
         <v>0.73</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.8522</v>
+        <v>-0.8137</v>
       </c>
       <c r="J238" t="n">
-        <v>-20.4528</v>
+        <v>-19.5288</v>
       </c>
     </row>
     <row r="239">
@@ -12047,10 +12047,10 @@
         <v>0.67</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.9863</v>
+        <v>-0.961</v>
       </c>
       <c r="J239" t="n">
-        <v>-23.6712</v>
+        <v>-23.064</v>
       </c>
     </row>
     <row r="240">
@@ -12087,10 +12087,10 @@
         <v>1.58</v>
       </c>
       <c r="I240" t="n">
-        <v>1.457</v>
+        <v>1.2928</v>
       </c>
       <c r="J240" t="n">
-        <v>34.968</v>
+        <v>31.0272</v>
       </c>
     </row>
     <row r="241">
@@ -12127,10 +12127,10 @@
         <v>1.37</v>
       </c>
       <c r="I241" t="n">
-        <v>1.0313</v>
+        <v>1.0022</v>
       </c>
       <c r="J241" t="n">
-        <v>24.7512</v>
+        <v>24.0528</v>
       </c>
     </row>
     <row r="242">
@@ -12167,10 +12167,10 @@
         <v>1.11</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2554</v>
+        <v>0.2743</v>
       </c>
       <c r="J242" t="n">
-        <v>7.1512</v>
+        <v>7.6804</v>
       </c>
     </row>
     <row r="243">
@@ -12207,10 +12207,10 @@
         <v>1.03</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1055</v>
+        <v>0.0973</v>
       </c>
       <c r="J243" t="n">
-        <v>2.954</v>
+        <v>2.7244</v>
       </c>
     </row>
     <row r="244">
@@ -12247,10 +12247,10 @@
         <v>0.93</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1632</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J244" t="n">
-        <v>-4.5696</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="245">
@@ -12287,10 +12287,10 @@
         <v>0.9</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2184</v>
+        <v>-0.1312</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.1152</v>
+        <v>-3.6736</v>
       </c>
     </row>
     <row r="246">
@@ -12327,10 +12327,10 @@
         <v>0.89</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2357</v>
+        <v>-0.1421</v>
       </c>
       <c r="J246" t="n">
-        <v>-6.5996</v>
+        <v>-3.9788</v>
       </c>
     </row>
     <row r="247">
@@ -12367,10 +12367,10 @@
         <v>1.28</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.592</v>
       </c>
       <c r="J247" t="n">
-        <v>22.1424</v>
+        <v>16.576</v>
       </c>
     </row>
     <row r="248">
@@ -12407,10 +12407,10 @@
         <v>1.27</v>
       </c>
       <c r="I248" t="n">
-        <v>0.7672</v>
+        <v>0.5779</v>
       </c>
       <c r="J248" t="n">
-        <v>21.4816</v>
+        <v>16.1812</v>
       </c>
     </row>
     <row r="249">
@@ -12447,10 +12447,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.5676</v>
+        <v>0.4626</v>
       </c>
       <c r="J249" t="n">
-        <v>15.8928</v>
+        <v>12.9528</v>
       </c>
     </row>
     <row r="250">
@@ -12487,10 +12487,10 @@
         <v>1.12</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3574</v>
+        <v>0.3573</v>
       </c>
       <c r="J250" t="n">
-        <v>10.0072</v>
+        <v>10.0044</v>
       </c>
     </row>
     <row r="251">
@@ -12527,10 +12527,10 @@
         <v>0.74</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.8488</v>
+        <v>-0.8074</v>
       </c>
       <c r="J251" t="n">
-        <v>-23.7664</v>
+        <v>-22.6072</v>
       </c>
     </row>
     <row r="252">
@@ -12567,10 +12567,10 @@
         <v>1.3</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4978</v>
+        <v>0.487</v>
       </c>
       <c r="J252" t="n">
-        <v>14.934</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="253">
@@ -12607,10 +12607,10 @@
         <v>1.15</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2839</v>
+        <v>0.3257</v>
       </c>
       <c r="J253" t="n">
-        <v>8.516999999999999</v>
+        <v>9.771000000000001</v>
       </c>
     </row>
     <row r="254">
@@ -12647,10 +12647,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0281</v>
       </c>
       <c r="J254" t="n">
-        <v>-0.018</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="255">
@@ -12687,10 +12687,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1772</v>
+        <v>-0.0953</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.316</v>
+        <v>-2.859</v>
       </c>
     </row>
     <row r="256">
@@ -12727,10 +12727,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1772</v>
+        <v>-0.0953</v>
       </c>
       <c r="J256" t="n">
-        <v>-5.316</v>
+        <v>-2.859</v>
       </c>
     </row>
     <row r="257">
@@ -12767,10 +12767,10 @@
         <v>1.46</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2672</v>
+        <v>0.8909</v>
       </c>
       <c r="J257" t="n">
-        <v>38.016</v>
+        <v>26.727</v>
       </c>
     </row>
     <row r="258">
@@ -12807,10 +12807,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.5122</v>
       </c>
       <c r="J258" t="n">
-        <v>20.61</v>
+        <v>15.366</v>
       </c>
     </row>
     <row r="259">
@@ -12847,10 +12847,10 @@
         <v>1.03</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1866</v>
+        <v>0.139</v>
       </c>
       <c r="J259" t="n">
-        <v>5.598</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="260">
@@ -12887,10 +12887,10 @@
         <v>0.63</v>
       </c>
       <c r="I260" t="n">
-        <v>-1.0508</v>
+        <v>-1.0348</v>
       </c>
       <c r="J260" t="n">
-        <v>-31.524</v>
+        <v>-31.044</v>
       </c>
     </row>
     <row r="261">
@@ -12927,10 +12927,10 @@
         <v>0.52</v>
       </c>
       <c r="I261" t="n">
-        <v>-1.2819</v>
+        <v>-1.2953</v>
       </c>
       <c r="J261" t="n">
-        <v>-38.457</v>
+        <v>-38.859</v>
       </c>
     </row>
     <row r="262">
@@ -12967,10 +12967,10 @@
         <v>1.02</v>
       </c>
       <c r="I262" t="n">
-        <v>0.1859</v>
+        <v>0.1268</v>
       </c>
       <c r="J262" t="n">
-        <v>3.9039</v>
+        <v>2.6628</v>
       </c>
     </row>
     <row r="263">
@@ -13007,10 +13007,10 @@
         <v>0.84</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1887</v>
+        <v>-0.1636</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.9627</v>
+        <v>-3.4356</v>
       </c>
     </row>
     <row r="264">
@@ -13047,10 +13047,10 @@
         <v>0.77</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3037</v>
+        <v>-0.2359</v>
       </c>
       <c r="J264" t="n">
-        <v>-6.3777</v>
+        <v>-4.9539</v>
       </c>
     </row>
     <row r="265">
@@ -13087,10 +13087,10 @@
         <v>0.52</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.6934</v>
+        <v>-0.4685</v>
       </c>
       <c r="J265" t="n">
-        <v>-14.5614</v>
+        <v>-9.8385</v>
       </c>
     </row>
     <row r="266">
@@ -13127,10 +13127,10 @@
         <v>0.49</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7318</v>
+        <v>-0.4965</v>
       </c>
       <c r="J266" t="n">
-        <v>-15.3678</v>
+        <v>-10.4265</v>
       </c>
     </row>
     <row r="267">
@@ -13167,10 +13167,10 @@
         <v>1.66</v>
       </c>
       <c r="I267" t="n">
-        <v>0.8355</v>
+        <v>0.5853</v>
       </c>
       <c r="J267" t="n">
-        <v>17.5455</v>
+        <v>12.2913</v>
       </c>
     </row>
     <row r="268">
@@ -13207,10 +13207,10 @@
         <v>1.61</v>
       </c>
       <c r="I268" t="n">
-        <v>0.7812</v>
+        <v>0.5553</v>
       </c>
       <c r="J268" t="n">
-        <v>16.4052</v>
+        <v>11.6613</v>
       </c>
     </row>
     <row r="269">
@@ -13247,10 +13247,10 @@
         <v>1.36</v>
       </c>
       <c r="I269" t="n">
-        <v>0.4681</v>
+        <v>0.4018</v>
       </c>
       <c r="J269" t="n">
-        <v>9.8301</v>
+        <v>8.437799999999999</v>
       </c>
     </row>
     <row r="270">
@@ -13287,10 +13287,10 @@
         <v>1.2</v>
       </c>
       <c r="I270" t="n">
-        <v>0.2463</v>
+        <v>0.2652</v>
       </c>
       <c r="J270" t="n">
-        <v>5.1723</v>
+        <v>5.5692</v>
       </c>
     </row>
     <row r="271">
@@ -13327,10 +13327,10 @@
         <v>1</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.0997</v>
+        <v>-0.0337</v>
       </c>
       <c r="J271" t="n">
-        <v>-2.0937</v>
+        <v>-0.7077</v>
       </c>
     </row>
     <row r="272">
@@ -13367,10 +13367,10 @@
         <v>1.54</v>
       </c>
       <c r="I272" t="n">
-        <v>1.4069</v>
+        <v>0.9857</v>
       </c>
       <c r="J272" t="n">
-        <v>50.6484</v>
+        <v>35.4852</v>
       </c>
     </row>
     <row r="273">
@@ -13407,10 +13407,10 @@
         <v>1.13</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4816</v>
+        <v>0.3923</v>
       </c>
       <c r="J273" t="n">
-        <v>17.3376</v>
+        <v>14.1228</v>
       </c>
     </row>
     <row r="274">
@@ -13447,10 +13447,10 @@
         <v>0.93</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3046</v>
+        <v>-0.2605</v>
       </c>
       <c r="J274" t="n">
-        <v>-10.9656</v>
+        <v>-9.378</v>
       </c>
     </row>
     <row r="275">
@@ -13487,10 +13487,10 @@
         <v>0.77</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.7421</v>
+        <v>-0.699</v>
       </c>
       <c r="J275" t="n">
-        <v>-26.7156</v>
+        <v>-25.164</v>
       </c>
     </row>
     <row r="276">
@@ -13527,10 +13527,10 @@
         <v>0.64</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.0387</v>
+        <v>-1.0204</v>
       </c>
       <c r="J276" t="n">
-        <v>-37.3932</v>
+        <v>-36.7344</v>
       </c>
     </row>
     <row r="277">
@@ -13567,10 +13567,10 @@
         <v>1.36</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5707</v>
+        <v>0.544</v>
       </c>
       <c r="J277" t="n">
-        <v>20.5452</v>
+        <v>19.584</v>
       </c>
     </row>
     <row r="278">
@@ -13607,10 +13607,10 @@
         <v>1.29</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4808</v>
+        <v>0.4748</v>
       </c>
       <c r="J278" t="n">
-        <v>17.3088</v>
+        <v>17.0928</v>
       </c>
     </row>
     <row r="279">
@@ -13647,10 +13647,10 @@
         <v>1.1</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1934</v>
+        <v>0.2304</v>
       </c>
       <c r="J279" t="n">
-        <v>6.9624</v>
+        <v>8.2944</v>
       </c>
     </row>
     <row r="280">
@@ -13687,10 +13687,10 @@
         <v>0.86</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3128</v>
+        <v>-0.1864</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.2608</v>
+        <v>-6.7104</v>
       </c>
     </row>
     <row r="281">
@@ -13727,10 +13727,10 @@
         <v>0.79</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4141</v>
+        <v>-0.2579</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.9076</v>
+        <v>-9.2844</v>
       </c>
     </row>
     <row r="282">
@@ -13767,10 +13767,10 @@
         <v>1.78</v>
       </c>
       <c r="I282" t="n">
-        <v>1.7052</v>
+        <v>1.1949</v>
       </c>
       <c r="J282" t="n">
-        <v>46.0404</v>
+        <v>32.2623</v>
       </c>
     </row>
     <row r="283">
@@ -13807,10 +13807,10 @@
         <v>1.52</v>
       </c>
       <c r="I283" t="n">
-        <v>1.2281</v>
+        <v>0.8772</v>
       </c>
       <c r="J283" t="n">
-        <v>33.1587</v>
+        <v>23.6844</v>
       </c>
     </row>
     <row r="284">
@@ -13847,10 +13847,10 @@
         <v>1.19</v>
       </c>
       <c r="I284" t="n">
-        <v>0.4455</v>
+        <v>0.4456</v>
       </c>
       <c r="J284" t="n">
-        <v>12.0285</v>
+        <v>12.0312</v>
       </c>
     </row>
     <row r="285">
@@ -13887,10 +13887,10 @@
         <v>1.01</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.0108</v>
       </c>
       <c r="J285" t="n">
-        <v>-2.4003</v>
+        <v>-0.2916</v>
       </c>
     </row>
     <row r="286">
@@ -13927,10 +13927,10 @@
         <v>0.85</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6253</v>
+        <v>-0.5596</v>
       </c>
       <c r="J286" t="n">
-        <v>-16.8831</v>
+        <v>-15.1092</v>
       </c>
     </row>
     <row r="287">
@@ -13967,10 +13967,10 @@
         <v>1.1</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2886</v>
+        <v>0.3012</v>
       </c>
       <c r="J287" t="n">
-        <v>7.7922</v>
+        <v>8.132400000000001</v>
       </c>
     </row>
     <row r="288">
@@ -14007,10 +14007,10 @@
         <v>1</v>
       </c>
       <c r="I288" t="n">
-        <v>0.0772</v>
+        <v>0.0398</v>
       </c>
       <c r="J288" t="n">
-        <v>2.0844</v>
+        <v>1.0746</v>
       </c>
     </row>
     <row r="289">
@@ -14047,10 +14047,10 @@
         <v>0.83</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2797</v>
+        <v>-0.1903</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.5519</v>
+        <v>-5.1381</v>
       </c>
     </row>
     <row r="290">
@@ -14087,10 +14087,10 @@
         <v>0.73</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4406</v>
+        <v>-0.2877</v>
       </c>
       <c r="J290" t="n">
-        <v>-11.8962</v>
+        <v>-7.7679</v>
       </c>
     </row>
     <row r="291">
@@ -14127,10 +14127,10 @@
         <v>0.55</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.4569</v>
       </c>
       <c r="J291" t="n">
-        <v>-18.3843</v>
+        <v>-12.3363</v>
       </c>
     </row>
     <row r="292">
@@ -14167,10 +14167,10 @@
         <v>0.96</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.017</v>
+        <v>-0.0408</v>
       </c>
       <c r="J292" t="n">
-        <v>-0.51</v>
+        <v>-1.224</v>
       </c>
     </row>
     <row r="293">
@@ -14207,10 +14207,10 @@
         <v>0.95</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.0372</v>
+        <v>-0.0541</v>
       </c>
       <c r="J293" t="n">
-        <v>-1.116</v>
+        <v>-1.623</v>
       </c>
     </row>
     <row r="294">
@@ -14247,10 +14247,10 @@
         <v>0.85</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2195</v>
+        <v>-0.1687</v>
       </c>
       <c r="J294" t="n">
-        <v>-6.585</v>
+        <v>-5.061</v>
       </c>
     </row>
     <row r="295">
@@ -14287,10 +14287,10 @@
         <v>0.68</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.5049</v>
+        <v>-0.3324</v>
       </c>
       <c r="J295" t="n">
-        <v>-15.147</v>
+        <v>-9.972</v>
       </c>
     </row>
     <row r="296">
@@ -14327,10 +14327,10 @@
         <v>0.66</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5326</v>
+        <v>-0.3513</v>
       </c>
       <c r="J296" t="n">
-        <v>-15.978</v>
+        <v>-10.539</v>
       </c>
     </row>
     <row r="297">
@@ -14367,10 +14367,10 @@
         <v>0.75</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.4367</v>
+        <v>-0.2794</v>
       </c>
       <c r="J297" t="n">
-        <v>-13.101</v>
+        <v>-8.382</v>
       </c>
     </row>
     <row r="298">
@@ -14407,10 +14407,10 @@
         <v>1.32</v>
       </c>
       <c r="I298" t="n">
-        <v>0.5719</v>
+        <v>0.4244</v>
       </c>
       <c r="J298" t="n">
-        <v>17.157</v>
+        <v>12.732</v>
       </c>
     </row>
     <row r="299">
@@ -14447,10 +14447,10 @@
         <v>1.1</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2561</v>
+        <v>0.1908</v>
       </c>
       <c r="J299" t="n">
-        <v>7.683</v>
+        <v>5.724</v>
       </c>
     </row>
     <row r="300">
@@ -14487,10 +14487,10 @@
         <v>0.74</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4507</v>
+        <v>-0.2891</v>
       </c>
       <c r="J300" t="n">
-        <v>-13.521</v>
+        <v>-8.673</v>
       </c>
     </row>
     <row r="301">
@@ -14527,10 +14527,10 @@
         <v>0.72</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4783</v>
+        <v>-0.3084</v>
       </c>
       <c r="J301" t="n">
-        <v>-14.349</v>
+        <v>-9.252000000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14567,10 +14567,10 @@
         <v>0.85</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.4747</v>
+        <v>-0.4565</v>
       </c>
       <c r="J302" t="n">
-        <v>-13.2916</v>
+        <v>-12.782</v>
       </c>
     </row>
     <row r="303">
@@ -14607,10 +14607,10 @@
         <v>1.13</v>
       </c>
       <c r="I303" t="n">
-        <v>0.5514</v>
+        <v>0.4224</v>
       </c>
       <c r="J303" t="n">
-        <v>15.4392</v>
+        <v>11.8272</v>
       </c>
     </row>
     <row r="304">
@@ -14647,10 +14647,10 @@
         <v>0.9</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2989</v>
+        <v>-0.3222</v>
       </c>
       <c r="J304" t="n">
-        <v>-8.369199999999999</v>
+        <v>-9.021599999999999</v>
       </c>
     </row>
     <row r="305">
@@ -14687,10 +14687,10 @@
         <v>0.86</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4444</v>
+        <v>-0.4298</v>
       </c>
       <c r="J305" t="n">
-        <v>-12.4432</v>
+        <v>-12.0344</v>
       </c>
     </row>
     <row r="306">
@@ -14727,10 +14727,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.794</v>
+        <v>-0.7657</v>
       </c>
       <c r="J306" t="n">
-        <v>-22.232</v>
+        <v>-21.4396</v>
       </c>
     </row>
     <row r="307">
@@ -14767,10 +14767,10 @@
         <v>0.82</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.3097</v>
+        <v>-0.2026</v>
       </c>
       <c r="J307" t="n">
-        <v>-8.6716</v>
+        <v>-5.6728</v>
       </c>
     </row>
     <row r="308">
@@ -14807,10 +14807,10 @@
         <v>1.2</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4332</v>
+        <v>0.4283</v>
       </c>
       <c r="J308" t="n">
-        <v>12.1296</v>
+        <v>11.9924</v>
       </c>
     </row>
     <row r="309">
@@ -14847,10 +14847,10 @@
         <v>0.83</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2927</v>
+        <v>-0.1926</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.195600000000001</v>
+        <v>-5.3928</v>
       </c>
     </row>
     <row r="310">
@@ -14887,10 +14887,10 @@
         <v>0.82</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3097</v>
+        <v>-0.2026</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.6716</v>
+        <v>-5.6728</v>
       </c>
     </row>
     <row r="311">
@@ -14927,10 +14927,10 @@
         <v>0.65</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5575</v>
+        <v>-0.3668</v>
       </c>
       <c r="J311" t="n">
-        <v>-15.61</v>
+        <v>-10.2704</v>
       </c>
     </row>
     <row r="312">
@@ -14967,10 +14967,10 @@
         <v>0.71</v>
       </c>
       <c r="I312" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="J312" t="n">
-        <v>-19.401</v>
+        <v>-22.242</v>
       </c>
     </row>
     <row r="313">
@@ -15007,10 +15007,10 @@
         <v>0.92</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.0476</v>
+        <v>-0.1438</v>
       </c>
       <c r="J313" t="n">
-        <v>-1.428</v>
+        <v>-4.314</v>
       </c>
     </row>
     <row r="314">
@@ -15047,10 +15047,10 @@
         <v>0.61</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-0.977</v>
       </c>
       <c r="J314" t="n">
-        <v>-28.776</v>
+        <v>-29.31</v>
       </c>
     </row>
     <row r="315">
@@ -15087,10 +15087,10 @@
         <v>0.58</v>
       </c>
       <c r="I315" t="n">
-        <v>-1.0358</v>
+        <v>-1.0495</v>
       </c>
       <c r="J315" t="n">
-        <v>-31.074</v>
+        <v>-31.485</v>
       </c>
     </row>
     <row r="316">
@@ -15127,10 +15127,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I316" t="n">
-        <v>-1.0852</v>
+        <v>-1.0981</v>
       </c>
       <c r="J316" t="n">
-        <v>-32.556</v>
+        <v>-32.943</v>
       </c>
     </row>
     <row r="317">
@@ -15167,10 +15167,10 @@
         <v>0.89</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.2267</v>
+        <v>-0.1395</v>
       </c>
       <c r="J317" t="n">
-        <v>-6.801</v>
+        <v>-4.185</v>
       </c>
     </row>
     <row r="318">
@@ -15207,10 +15207,10 @@
         <v>1.19</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3875</v>
+        <v>0.3954</v>
       </c>
       <c r="J318" t="n">
-        <v>11.625</v>
+        <v>11.862</v>
       </c>
     </row>
     <row r="319">
@@ -15247,10 +15247,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1296</v>
+        <v>-0.0833</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.888</v>
+        <v>-2.499</v>
       </c>
     </row>
     <row r="320">
@@ -15287,10 +15287,10 @@
         <v>0.89</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2267</v>
+        <v>-0.1395</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.801</v>
+        <v>-4.185</v>
       </c>
     </row>
     <row r="321">
@@ -15327,10 +15327,10 @@
         <v>0.83</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3251</v>
+        <v>-0.2025</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.753</v>
+        <v>-6.075</v>
       </c>
     </row>
     <row r="322">
@@ -15367,10 +15367,10 @@
         <v>1.04</v>
       </c>
       <c r="I322" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1332</v>
       </c>
       <c r="J322" t="n">
-        <v>1.7319</v>
+        <v>3.0636</v>
       </c>
     </row>
     <row r="323">
@@ -15407,10 +15407,10 @@
         <v>0.63</v>
       </c>
       <c r="I323" t="n">
-        <v>-1.0926</v>
+        <v>-1.0795</v>
       </c>
       <c r="J323" t="n">
-        <v>-25.1298</v>
+        <v>-24.8285</v>
       </c>
     </row>
     <row r="324">
@@ -15447,10 +15447,10 @@
         <v>0.53</v>
       </c>
       <c r="I324" t="n">
-        <v>-1.2946</v>
+        <v>-1.3116</v>
       </c>
       <c r="J324" t="n">
-        <v>-29.7758</v>
+        <v>-30.1668</v>
       </c>
     </row>
     <row r="325">
@@ -15487,10 +15487,10 @@
         <v>1.94</v>
       </c>
       <c r="I325" t="n">
-        <v>1.9039</v>
+        <v>1.4336</v>
       </c>
       <c r="J325" t="n">
-        <v>43.7897</v>
+        <v>32.9728</v>
       </c>
     </row>
     <row r="326">
@@ -15527,10 +15527,10 @@
         <v>1.58</v>
       </c>
       <c r="I326" t="n">
-        <v>1.4069</v>
+        <v>0.9857</v>
       </c>
       <c r="J326" t="n">
-        <v>32.3587</v>
+        <v>22.6711</v>
       </c>
     </row>
     <row r="327">
@@ -15567,10 +15567,10 @@
         <v>1.74</v>
       </c>
       <c r="I327" t="n">
-        <v>0.9638</v>
+        <v>0.8658</v>
       </c>
       <c r="J327" t="n">
-        <v>22.1674</v>
+        <v>19.9134</v>
       </c>
     </row>
     <row r="328">
@@ -15607,10 +15607,10 @@
         <v>1.29</v>
       </c>
       <c r="I328" t="n">
-        <v>0.4422</v>
+        <v>0.4581</v>
       </c>
       <c r="J328" t="n">
-        <v>10.1706</v>
+        <v>10.5363</v>
       </c>
     </row>
     <row r="329">
@@ -15647,10 +15647,10 @@
         <v>0.98</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1281</v>
+        <v>-0.0555</v>
       </c>
       <c r="J329" t="n">
-        <v>-2.9463</v>
+        <v>-1.2765</v>
       </c>
     </row>
     <row r="330">
@@ -15687,10 +15687,10 @@
         <v>1</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.0704</v>
+        <v>-0.0185</v>
       </c>
       <c r="J330" t="n">
-        <v>-1.6192</v>
+        <v>-0.4255</v>
       </c>
     </row>
     <row r="331">
@@ -15727,10 +15727,10 @@
         <v>0.98</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.1281</v>
+        <v>-0.0555</v>
       </c>
       <c r="J331" t="n">
-        <v>-2.9463</v>
+        <v>-1.2765</v>
       </c>
     </row>
     <row r="332">
@@ -15767,10 +15767,10 @@
         <v>0.98</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.1909</v>
+        <v>-0.1235</v>
       </c>
       <c r="J332" t="n">
-        <v>-4.5816</v>
+        <v>-2.964</v>
       </c>
     </row>
     <row r="333">
@@ -15807,10 +15807,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I333" t="n">
-        <v>-1.2307</v>
+        <v>-1.2374</v>
       </c>
       <c r="J333" t="n">
-        <v>-29.5368</v>
+        <v>-29.6976</v>
       </c>
     </row>
     <row r="334">
@@ -15847,10 +15847,10 @@
         <v>0.54</v>
       </c>
       <c r="I334" t="n">
-        <v>-1.2706</v>
+        <v>-1.2835</v>
       </c>
       <c r="J334" t="n">
-        <v>-30.4944</v>
+        <v>-30.804</v>
       </c>
     </row>
     <row r="335">
@@ -15887,10 +15887,10 @@
         <v>1.87</v>
       </c>
       <c r="I335" t="n">
-        <v>1.8457</v>
+        <v>1.3595</v>
       </c>
       <c r="J335" t="n">
-        <v>44.2968</v>
+        <v>32.628</v>
       </c>
     </row>
     <row r="336">
@@ -15927,10 +15927,10 @@
         <v>1.64</v>
       </c>
       <c r="I336" t="n">
-        <v>1.534</v>
+        <v>1.0711</v>
       </c>
       <c r="J336" t="n">
-        <v>36.816</v>
+        <v>25.7064</v>
       </c>
     </row>
     <row r="337">
@@ -15967,10 +15967,10 @@
         <v>1.32</v>
       </c>
       <c r="I337" t="n">
-        <v>0.5098</v>
+        <v>0.4991</v>
       </c>
       <c r="J337" t="n">
-        <v>12.2352</v>
+        <v>11.9784</v>
       </c>
     </row>
     <row r="338">
@@ -16007,10 +16007,10 @@
         <v>1.29</v>
       </c>
       <c r="I338" t="n">
-        <v>0.4704</v>
+        <v>0.4696</v>
       </c>
       <c r="J338" t="n">
-        <v>11.2896</v>
+        <v>11.2704</v>
       </c>
     </row>
     <row r="339">
@@ -16047,10 +16047,10 @@
         <v>1.16</v>
       </c>
       <c r="I339" t="n">
-        <v>0.2824</v>
+        <v>0.3336</v>
       </c>
       <c r="J339" t="n">
-        <v>6.7776</v>
+        <v>8.006399999999999</v>
       </c>
     </row>
     <row r="340">
@@ -16087,10 +16087,10 @@
         <v>0.91</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2404</v>
+        <v>-0.1352</v>
       </c>
       <c r="J340" t="n">
-        <v>-5.7696</v>
+        <v>-3.2448</v>
       </c>
     </row>
     <row r="341">
@@ -16127,10 +16127,10 @@
         <v>0.88</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2887</v>
+        <v>-0.1684</v>
       </c>
       <c r="J341" t="n">
-        <v>-6.9288</v>
+        <v>-4.0416</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5209/event_5209_evp_summary.xlsx
+++ b/database/event/5209/event_5209_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.5131</v>
+        <v>8.666700000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3688</v>
+        <v>3.4296</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2052</v>
+        <v>3.3211</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5131</v>
+        <v>8.666700000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0094</v>
+        <v>2.7904</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5038</v>
+        <v>5.8763</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2483</v>
+        <v>3.3823</v>
       </c>
       <c r="I2" t="n">
-        <v>3.521</v>
+        <v>3.5589</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5038</v>
+        <v>5.8763</v>
       </c>
       <c r="K2" t="n">
         <v>78</v>
@@ -529,7 +529,7 @@
         <v>218</v>
       </c>
       <c r="M2" t="n">
-        <v>9.024799999999999</v>
+        <v>9.4352</v>
       </c>
       <c r="N2" t="n">
         <v>296</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.285</v>
+        <v>4.1864</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6957</v>
+        <v>1.6566</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2964</v>
+        <v>1.2815</v>
       </c>
       <c r="E3" t="n">
-        <v>4.285</v>
+        <v>4.1864</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8862</v>
+        <v>2.5833</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3988</v>
+        <v>1.6031</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9779</v>
+        <v>2.929</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2279</v>
+        <v>3.0819</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3988</v>
+        <v>1.6031</v>
       </c>
       <c r="K3" t="n">
         <v>116</v>
@@ -575,7 +575,7 @@
         <v>197</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6267</v>
+        <v>4.685</v>
       </c>
       <c r="N3" t="n">
         <v>313</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4865</v>
+        <v>3.7004</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3797</v>
+        <v>1.4643</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9360000000000001</v>
+        <v>1.0603</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4865</v>
+        <v>3.7004</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9953</v>
+        <v>0.9683</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4912</v>
+        <v>2.7321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9953</v>
+        <v>0.9683</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9953</v>
+        <v>0.9683</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4912</v>
+        <v>2.7321</v>
       </c>
       <c r="K4" t="n">
         <v>50</v>
@@ -621,7 +621,7 @@
         <v>206</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4865</v>
+        <v>3.7004</v>
       </c>
       <c r="N4" t="n">
         <v>256</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.0519</v>
+        <v>3.1358</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2077</v>
+        <v>1.2409</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7398</v>
+        <v>0.8033</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0519</v>
+        <v>3.1358</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6448</v>
+        <v>1.5844</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4071</v>
+        <v>1.5514</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6448</v>
+        <v>1.5844</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6448</v>
+        <v>1.5844</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4071</v>
+        <v>1.5514</v>
       </c>
       <c r="K5" t="n">
         <v>35</v>
@@ -667,7 +667,7 @@
         <v>83</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0519</v>
+        <v>3.1358</v>
       </c>
       <c r="N5" t="n">
         <v>118</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.9155</v>
+        <v>2.9511</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1537</v>
+        <v>1.1678</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6782</v>
+        <v>0.7192</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9155</v>
+        <v>2.9511</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2722</v>
+        <v>-0.2925</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1877</v>
+        <v>3.2436</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2722</v>
+        <v>-0.2925</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2834</v>
+        <v>-0.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1877</v>
+        <v>3.2436</v>
       </c>
       <c r="K6" t="n">
         <v>85</v>
@@ -713,7 +713,7 @@
         <v>229</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9043</v>
+        <v>2.9436</v>
       </c>
       <c r="N6" t="n">
         <v>314</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.6918</v>
+        <v>2.5798</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0652</v>
+        <v>1.0209</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5772</v>
+        <v>0.5502</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6918</v>
+        <v>2.5798</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6455</v>
+        <v>3.4339</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9537</v>
+        <v>-0.8541</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6451</v>
+        <v>4.7907</v>
       </c>
       <c r="I7" t="n">
-        <v>5.6822</v>
+        <v>5.4406</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9537</v>
+        <v>-0.8541</v>
       </c>
       <c r="K7" t="n">
         <v>151</v>
@@ -759,7 +759,7 @@
         <v>269</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7285</v>
+        <v>4.5865</v>
       </c>
       <c r="N7" t="n">
         <v>420</v>
@@ -768,185 +768,185 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5767</v>
+        <v>2.5222</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0196</v>
+        <v>0.9981</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5252</v>
+        <v>0.524</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5767</v>
+        <v>2.5222</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1285</v>
+        <v>1.0603</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5518</v>
+        <v>1.4619</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5098</v>
+        <v>1.0603</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9609</v>
+        <v>1.1156</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5518</v>
+        <v>1.4619</v>
       </c>
       <c r="K8" t="n">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="L8" t="n">
-        <v>190</v>
+        <v>84</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4091</v>
+        <v>2.5775</v>
       </c>
       <c r="N8" t="n">
-        <v>346</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4643</v>
+        <v>2.4631</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9752</v>
+        <v>0.9747</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4745</v>
+        <v>0.4971</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4643</v>
+        <v>2.4631</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6829</v>
+        <v>2.8504</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7814</v>
+        <v>-0.3873</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6829</v>
+        <v>3.5138</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6829</v>
+        <v>3.7925</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7814</v>
+        <v>-0.3873</v>
       </c>
       <c r="K9" t="n">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="L9" t="n">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4643</v>
+        <v>3.4052</v>
       </c>
       <c r="N9" t="n">
-        <v>115</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4017</v>
+        <v>2.4343</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9504</v>
+        <v>0.9633</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4462</v>
+        <v>0.4839</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4017</v>
+        <v>2.4343</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0704</v>
+        <v>0.1752</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3313</v>
+        <v>2.2591</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0704</v>
+        <v>0.1752</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1603</v>
+        <v>0.1797</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3313</v>
+        <v>2.2591</v>
       </c>
       <c r="K10" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L10" t="n">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4916</v>
+        <v>2.4388</v>
       </c>
       <c r="N10" t="n">
-        <v>166</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2082</v>
+        <v>2.4205</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8738</v>
+        <v>0.9578</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3589</v>
+        <v>0.4777</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2082</v>
+        <v>2.4205</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1325</v>
+        <v>0.6659</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0757</v>
+        <v>1.7546</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1325</v>
+        <v>0.6659</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1379</v>
+        <v>0.6659</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0757</v>
+        <v>1.7546</v>
       </c>
       <c r="K11" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>176</v>
+        <v>98</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2136</v>
+        <v>2.4205</v>
       </c>
       <c r="N11" t="n">
-        <v>249</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.741</v>
+        <v>1.7678</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6889</v>
+        <v>0.6996</v>
       </c>
       <c r="D12" t="n">
-        <v>0.148</v>
+        <v>0.1805</v>
       </c>
       <c r="E12" t="n">
-        <v>1.741</v>
+        <v>1.7678</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8452</v>
+        <v>0.8619</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8958</v>
+        <v>0.9059</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8452</v>
+        <v>0.8619</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9162</v>
+        <v>0.9069</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8958</v>
+        <v>0.9059</v>
       </c>
       <c r="K12" t="n">
         <v>42</v>
@@ -989,7 +989,7 @@
         <v>218</v>
       </c>
       <c r="M12" t="n">
-        <v>1.812</v>
+        <v>1.8128</v>
       </c>
       <c r="N12" t="n">
         <v>260</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4958</v>
+        <v>1.6454</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5919</v>
+        <v>0.6511</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0373</v>
+        <v>0.1248</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4958</v>
+        <v>1.6454</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4353</v>
+        <v>-0.0261</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0605</v>
+        <v>1.6715</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4353</v>
+        <v>-0.0261</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4718</v>
+        <v>-0.0275</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0605</v>
+        <v>1.6715</v>
       </c>
       <c r="K13" t="n">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="L13" t="n">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5323</v>
+        <v>1.644</v>
       </c>
       <c r="N13" t="n">
-        <v>137</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4219</v>
+        <v>1.5588</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5627</v>
+        <v>0.6168</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0039</v>
+        <v>0.0854</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4219</v>
+        <v>1.5588</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1096</v>
+        <v>0.4013</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5315</v>
+        <v>1.1575</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1096</v>
+        <v>0.4013</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1188</v>
+        <v>0.4223</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5315</v>
+        <v>1.1575</v>
       </c>
       <c r="K14" t="n">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="L14" t="n">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4127</v>
+        <v>1.5798</v>
       </c>
       <c r="N14" t="n">
-        <v>249</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3331</v>
+        <v>1.3747</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5275</v>
+        <v>0.544</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0362</v>
+        <v>0.0016</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3331</v>
+        <v>1.3747</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3492</v>
+        <v>1.2968</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0161</v>
+        <v>0.0779</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3492</v>
+        <v>1.2968</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4625</v>
+        <v>1.3645</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0161</v>
+        <v>0.0779</v>
       </c>
       <c r="K15" t="n">
         <v>82</v>
@@ -1127,7 +1127,7 @@
         <v>135</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4464</v>
+        <v>1.4424</v>
       </c>
       <c r="N15" t="n">
         <v>217</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2875</v>
+        <v>1.3567</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5095</v>
+        <v>0.5369</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0568</v>
+        <v>-0.0066</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2875</v>
+        <v>1.3567</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7815</v>
+        <v>1.7199</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.494</v>
+        <v>-0.3632</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7815</v>
+        <v>1.7199</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8548</v>
+        <v>1.7642</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.494</v>
+        <v>-0.3632</v>
       </c>
       <c r="K16" t="n">
         <v>94</v>
@@ -1173,7 +1173,7 @@
         <v>195</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3608</v>
+        <v>1.401</v>
       </c>
       <c r="N16" t="n">
         <v>289</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1928</v>
+        <v>1.2673</v>
       </c>
       <c r="C17" t="n">
-        <v>0.472</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0473</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1928</v>
+        <v>1.2673</v>
       </c>
       <c r="F17" t="n">
-        <v>0.803</v>
+        <v>0.8334</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3898</v>
+        <v>0.4339</v>
       </c>
       <c r="H17" t="n">
-        <v>0.803</v>
+        <v>0.8334</v>
       </c>
       <c r="I17" t="n">
-        <v>0.836</v>
+        <v>0.8549</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3898</v>
+        <v>0.4339</v>
       </c>
       <c r="K17" t="n">
         <v>82</v>
@@ -1219,7 +1219,7 @@
         <v>58</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2258</v>
+        <v>1.2888</v>
       </c>
       <c r="N17" t="n">
         <v>140</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1212</v>
+        <v>1.1273</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4437</v>
+        <v>0.4461</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1318</v>
+        <v>-0.111</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1212</v>
+        <v>1.1273</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1192</v>
+        <v>1.1279</v>
       </c>
       <c r="G18" t="n">
-        <v>0.002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1192</v>
+        <v>1.1279</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1652</v>
+        <v>1.157</v>
       </c>
       <c r="J18" t="n">
-        <v>0.002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K18" t="n">
         <v>82</v>
@@ -1265,7 +1265,7 @@
         <v>58</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1672</v>
+        <v>1.1564</v>
       </c>
       <c r="N18" t="n">
         <v>140</v>
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9025</v>
+        <v>0.955</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3571</v>
+        <v>0.3779</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2306</v>
+        <v>-0.1895</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9025</v>
+        <v>0.955</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9025</v>
+        <v>0.955</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9025</v>
+        <v>0.955</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>230</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9025</v>
+        <v>0.955</v>
       </c>
       <c r="N19" t="n">
         <v>230</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4637</v>
+        <v>0.4435</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1835</v>
+        <v>0.1755</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4287</v>
+        <v>-0.4223</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4637</v>
+        <v>0.4435</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4637</v>
+        <v>0.4435</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4637</v>
+        <v>0.4435</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4637</v>
+        <v>0.4435</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4637</v>
+        <v>0.4435</v>
       </c>
       <c r="N20" t="n">
         <v>97</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4203</v>
+        <v>0.4245</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1663</v>
+        <v>0.168</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4483</v>
+        <v>-0.431</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4203</v>
+        <v>0.4245</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2258</v>
+        <v>0.2353</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1945</v>
+        <v>0.1892</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2258</v>
+        <v>0.2353</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2351</v>
+        <v>0.2414</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1945</v>
+        <v>0.1892</v>
       </c>
       <c r="K21" t="n">
         <v>82</v>
@@ -1403,7 +1403,7 @@
         <v>58</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4296</v>
+        <v>0.4306</v>
       </c>
       <c r="N21" t="n">
         <v>140</v>
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3223</v>
+        <v>0.378</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1275</v>
+        <v>0.1496</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4925</v>
+        <v>-0.4521</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3223</v>
+        <v>0.378</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3223</v>
+        <v>0.378</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3223</v>
+        <v>0.378</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>57</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3223</v>
+        <v>0.378</v>
       </c>
       <c r="N22" t="n">
         <v>57</v>
@@ -1458,277 +1458,277 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1706</v>
+        <v>0.2071</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0675</v>
+        <v>0.082</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5299</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1706</v>
+        <v>0.2071</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3945</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2239</v>
+        <v>0.2071</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3945</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3945</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2239</v>
+        <v>0.2071</v>
       </c>
       <c r="K23" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1706</v>
+        <v>0.2071</v>
       </c>
       <c r="N23" t="n">
-        <v>92</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1268</v>
+        <v>0.1957</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0502</v>
+        <v>0.0774</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5808</v>
+        <v>-0.5351</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1268</v>
+        <v>0.1957</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.777</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1268</v>
+        <v>-0.5813</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.777</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.797</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1268</v>
+        <v>-0.5813</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="L24" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1268</v>
+        <v>0.2157</v>
       </c>
       <c r="N24" t="n">
-        <v>230</v>
+        <v>360</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1124</v>
+        <v>0.1722</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0445</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5873</v>
+        <v>-0.5458</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1124</v>
+        <v>0.1722</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8141</v>
+        <v>0.5685</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7017</v>
+        <v>-0.3963</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8141</v>
+        <v>0.5685</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8476</v>
+        <v>0.5831</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7017</v>
+        <v>-0.3963</v>
       </c>
       <c r="K25" t="n">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="L25" t="n">
-        <v>239</v>
+        <v>145</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1459</v>
+        <v>0.1868</v>
       </c>
       <c r="N25" t="n">
-        <v>360</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0694</v>
+        <v>0.1458</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0275</v>
+        <v>0.0577</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6067</v>
+        <v>-0.5578</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0694</v>
+        <v>0.1458</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.3825</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0694</v>
+        <v>-0.2367</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.3825</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.3825</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0694</v>
+        <v>-0.2367</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L26" t="n">
-        <v>230</v>
+        <v>47</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0694</v>
+        <v>0.1458</v>
       </c>
       <c r="N26" t="n">
-        <v>230</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0083</v>
+        <v>0.144</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0033</v>
+        <v>0.057</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6343</v>
+        <v>-0.5587</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0083</v>
+        <v>0.144</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1707</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.179</v>
+        <v>0.144</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1707</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1777</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.179</v>
+        <v>0.144</v>
       </c>
       <c r="K27" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>58</v>
+        <v>230</v>
       </c>
       <c r="M27" t="n">
-        <v>0.001299999999999996</v>
+        <v>0.144</v>
       </c>
       <c r="N27" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0728</v>
+        <v>-0.0109</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0288</v>
+        <v>-0.0043</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.6292</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0728</v>
+        <v>-0.0109</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5739</v>
+        <v>-0.1838</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.1729</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5739</v>
+        <v>-0.1838</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5975</v>
+        <v>-0.1885</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.1729</v>
       </c>
       <c r="K28" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="L28" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.04920000000000002</v>
+        <v>-0.0156</v>
       </c>
       <c r="N28" t="n">
-        <v>247</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5812</v>
+        <v>-0.5028</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.23</v>
+        <v>-0.199</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.9004</v>
+        <v>-0.8531</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5812</v>
+        <v>-0.5028</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.8267</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2455</v>
+        <v>0.285</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.8267</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.8607</v>
+        <v>-0.8081</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2455</v>
+        <v>0.285</v>
       </c>
       <c r="K29" t="n">
         <v>27</v>
@@ -1771,7 +1771,7 @@
         <v>155</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6152</v>
+        <v>-0.5231000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>182</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5967</v>
+        <v>-0.6005</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2361</v>
+        <v>-0.2376</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.9074</v>
+        <v>-0.8976</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5967</v>
+        <v>-0.6005</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5836</v>
+        <v>0.5948</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.1803</v>
+        <v>-1.1953</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5836</v>
+        <v>0.5948</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6259</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.1803</v>
+        <v>-1.1953</v>
       </c>
       <c r="K30" t="n">
         <v>82</v>
@@ -1817,7 +1817,7 @@
         <v>162</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5476999999999999</v>
+        <v>-0.5694</v>
       </c>
       <c r="N30" t="n">
         <v>244</v>
@@ -1826,277 +1826,277 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8783</v>
+        <v>-0.7447</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3476</v>
+        <v>-0.2947</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.0345</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8783</v>
+        <v>-0.7447</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4347</v>
+        <v>-2.4334</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.313</v>
+        <v>1.6887</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4347</v>
+        <v>-2.4334</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4712</v>
+        <v>-2.6264</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.313</v>
+        <v>1.6887</v>
       </c>
       <c r="K31" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="L31" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8417999999999999</v>
+        <v>-0.9376999999999998</v>
       </c>
       <c r="N31" t="n">
-        <v>217</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.792</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3544</v>
+        <v>-0.3134</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.0424</v>
+        <v>-0.9847</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.792</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7817</v>
+        <v>-0.8552</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.114</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7817</v>
+        <v>-0.8552</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8139</v>
+        <v>-0.8998</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.114</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="K32" t="n">
         <v>82</v>
       </c>
       <c r="L32" t="n">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.9278999999999999</v>
+        <v>-0.8366</v>
       </c>
       <c r="N32" t="n">
-        <v>140</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9939</v>
+        <v>-0.8072</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3933</v>
+        <v>-0.3194</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0867</v>
+        <v>-0.9917</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9939</v>
+        <v>-0.8072</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8349</v>
+        <v>0.4714</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.159</v>
+        <v>-1.2786</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8349</v>
+        <v>0.4714</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.905</v>
+        <v>0.496</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.159</v>
+        <v>-1.2786</v>
       </c>
       <c r="K33" t="n">
         <v>82</v>
       </c>
       <c r="L33" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.064</v>
+        <v>-0.7826</v>
       </c>
       <c r="N33" t="n">
-        <v>241</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0473</v>
+        <v>-0.9485</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4144</v>
+        <v>-0.3753</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.1108</v>
+        <v>-1.056</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0473</v>
+        <v>-0.9485</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-0.8293</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.0473</v>
+        <v>-0.1192</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>-0.8293</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>-0.8507</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.0473</v>
+        <v>-0.1192</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="L34" t="n">
-        <v>230</v>
+        <v>58</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0473</v>
+        <v>-0.9699</v>
       </c>
       <c r="N34" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bymas</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.086</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4298</v>
+        <v>-0.3756</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1283</v>
+        <v>-1.0563</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.086</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9605</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1255</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9605</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1255</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>71</v>
+        <v>230</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1255</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>116</v>
+        <v>230</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Bymas</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1628</v>
+        <v>-1.0892</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4601</v>
+        <v>-0.431</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.163</v>
+        <v>-1.12</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1628</v>
+        <v>-1.0892</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.6815</v>
+        <v>-0.9718</v>
       </c>
       <c r="G36" t="n">
-        <v>1.5187</v>
+        <v>-0.1174</v>
       </c>
       <c r="H36" t="n">
-        <v>-2.6815</v>
+        <v>-0.9718</v>
       </c>
       <c r="I36" t="n">
-        <v>-3.0261</v>
+        <v>-0.9968</v>
       </c>
       <c r="J36" t="n">
-        <v>1.5187</v>
+        <v>-0.1174</v>
       </c>
       <c r="K36" t="n">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="L36" t="n">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.5074</v>
+        <v>-1.1142</v>
       </c>
       <c r="N36" t="n">
-        <v>265</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2138</v>
+        <v>-1.1917</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4803</v>
+        <v>-0.4716</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.186</v>
+        <v>-1.1667</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2138</v>
+        <v>-1.1917</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1953</v>
+        <v>-1.1774</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0185</v>
+        <v>-0.0143</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1953</v>
+        <v>-1.1774</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2956</v>
+        <v>-1.2389</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.0185</v>
+        <v>-0.0143</v>
       </c>
       <c r="K37" t="n">
         <v>69</v>
@@ -2139,7 +2139,7 @@
         <v>23</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3141</v>
+        <v>-1.2532</v>
       </c>
       <c r="N37" t="n">
         <v>92</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.534</v>
+        <v>-1.4282</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.607</v>
+        <v>-0.5652</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.3305</v>
+        <v>-1.2743</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.534</v>
+        <v>-1.4282</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.534</v>
+        <v>-1.4282</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.534</v>
+        <v>-1.4282</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>230</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.534</v>
+        <v>-1.4282</v>
       </c>
       <c r="N38" t="n">
         <v>230</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8668</v>
+        <v>-1.6806</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.7387</v>
+        <v>-0.665</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4808</v>
+        <v>-1.3892</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8668</v>
+        <v>-1.6806</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.3112</v>
+        <v>-2.2047</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4444</v>
+        <v>0.5241</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.3112</v>
+        <v>-2.2047</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.7155</v>
+        <v>-2.4409</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4444</v>
+        <v>0.5241</v>
       </c>
       <c r="K39" t="n">
         <v>105</v>
@@ -2231,7 +2231,7 @@
         <v>145</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.2711</v>
+        <v>-1.9168</v>
       </c>
       <c r="N39" t="n">
         <v>250</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3931</v>
+        <v>-2.2682</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.947</v>
+        <v>-0.8976</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7184</v>
+        <v>-1.6567</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3931</v>
+        <v>-2.2682</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3931</v>
+        <v>-1.2682</v>
       </c>
       <c r="G40" t="n">
         <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3931</v>
+        <v>-1.2682</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4504</v>
+        <v>-1.3009</v>
       </c>
       <c r="J40" t="n">
         <v>-1</v>
@@ -2277,7 +2277,7 @@
         <v>47</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.4504</v>
+        <v>-2.3009</v>
       </c>
       <c r="N40" t="n">
         <v>68</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.605</v>
+        <v>-2.4795</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0308</v>
+        <v>-0.9812</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.814</v>
+        <v>-1.7529</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.605</v>
+        <v>-2.4795</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.1788</v>
+        <v>-2.0515</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.4262</v>
+        <v>-0.428</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.1788</v>
+        <v>-2.0515</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.3617</v>
+        <v>-2.1586</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4262</v>
+        <v>-0.428</v>
       </c>
       <c r="K41" t="n">
         <v>50</v>
@@ -2323,7 +2323,7 @@
         <v>151</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.7879</v>
+        <v>-2.5866</v>
       </c>
       <c r="N41" t="n">
         <v>201</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.7674</v>
+        <v>-2.6716</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.0951</v>
+        <v>-1.0572</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.8874</v>
+        <v>-1.8404</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.7674</v>
+        <v>-2.6716</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.7674</v>
+        <v>-1.6716</v>
       </c>
       <c r="G42" t="n">
         <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.7674</v>
+        <v>-1.6716</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.9158</v>
+        <v>-1.7589</v>
       </c>
       <c r="J42" t="n">
         <v>-1</v>
@@ -2369,7 +2369,7 @@
         <v>47</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.9158</v>
+        <v>-2.7589</v>
       </c>
       <c r="N42" t="n">
         <v>92</v>
@@ -2378,93 +2378,93 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-2.979</v>
+        <v>-2.7363</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.1788</v>
+        <v>-1.0828</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.9829</v>
+        <v>-1.8698</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.979</v>
+        <v>-2.7363</v>
       </c>
       <c r="F43" t="n">
-        <v>-3.478</v>
+        <v>-3.0587</v>
       </c>
       <c r="G43" t="n">
-        <v>0.499</v>
+        <v>0.3224</v>
       </c>
       <c r="H43" t="n">
-        <v>-3.478</v>
+        <v>-3.0587</v>
       </c>
       <c r="I43" t="n">
-        <v>-4.0864</v>
+        <v>-3.2184</v>
       </c>
       <c r="J43" t="n">
-        <v>0.499</v>
+        <v>0.3224</v>
       </c>
       <c r="K43" t="n">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="L43" t="n">
-        <v>145</v>
+        <v>300</v>
       </c>
       <c r="M43" t="n">
-        <v>-3.5874</v>
+        <v>-2.896</v>
       </c>
       <c r="N43" t="n">
-        <v>274</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-3.0324</v>
+        <v>-2.7696</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.2</v>
+        <v>-1.096</v>
       </c>
       <c r="D44" t="n">
-        <v>-2.007</v>
+        <v>-1.885</v>
       </c>
       <c r="E44" t="n">
-        <v>-3.0324</v>
+        <v>-2.7696</v>
       </c>
       <c r="F44" t="n">
-        <v>-3.3465</v>
+        <v>-3.4263</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3141</v>
+        <v>0.6567</v>
       </c>
       <c r="H44" t="n">
-        <v>-3.3465</v>
+        <v>-3.4263</v>
       </c>
       <c r="I44" t="n">
-        <v>-3.6274</v>
+        <v>-3.7934</v>
       </c>
       <c r="J44" t="n">
-        <v>0.3141</v>
+        <v>0.6567</v>
       </c>
       <c r="K44" t="n">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="L44" t="n">
-        <v>300</v>
+        <v>145</v>
       </c>
       <c r="M44" t="n">
-        <v>-3.3133</v>
+        <v>-3.1367</v>
       </c>
       <c r="N44" t="n">
-        <v>350</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -2567,10 +2567,10 @@
         <v>0.7</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8879</v>
+        <v>-0.819</v>
       </c>
       <c r="J2" t="n">
-        <v>-17.758</v>
+        <v>-16.38</v>
       </c>
     </row>
     <row r="3">
@@ -2607,10 +2607,10 @@
         <v>0.61</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1047</v>
+        <v>-1.0063</v>
       </c>
       <c r="J3" t="n">
-        <v>-22.094</v>
+        <v>-20.126</v>
       </c>
     </row>
     <row r="4">
@@ -2647,10 +2647,10 @@
         <v>0.42</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.543</v>
+        <v>-1.3788</v>
       </c>
       <c r="J4" t="n">
-        <v>-30.86</v>
+        <v>-27.576</v>
       </c>
     </row>
     <row r="5">
@@ -2687,10 +2687,10 @@
         <v>2.12</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J5" t="n">
-        <v>37.362</v>
+        <v>36.906</v>
       </c>
     </row>
     <row r="6">
@@ -2727,10 +2727,10 @@
         <v>1.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0502</v>
+        <v>0.9969</v>
       </c>
       <c r="J6" t="n">
-        <v>21.004</v>
+        <v>19.938</v>
       </c>
     </row>
     <row r="7">
@@ -2767,10 +2767,10 @@
         <v>1.36</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6944</v>
+        <v>0.6716</v>
       </c>
       <c r="J7" t="n">
-        <v>13.888</v>
+        <v>13.432</v>
       </c>
     </row>
     <row r="8">
@@ -2807,10 +2807,10 @@
         <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3649</v>
+        <v>0.3687</v>
       </c>
       <c r="J8" t="n">
-        <v>7.298</v>
+        <v>7.374</v>
       </c>
     </row>
     <row r="9">
@@ -2847,10 +2847,10 @@
         <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1417</v>
+        <v>-0.1528</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.834</v>
+        <v>-3.056</v>
       </c>
     </row>
     <row r="10">
@@ -2887,10 +2887,10 @@
         <v>1.15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.328</v>
+        <v>0.3338</v>
       </c>
       <c r="J10" t="n">
-        <v>6.56</v>
+        <v>6.676</v>
       </c>
     </row>
     <row r="11">
@@ -2927,10 +2927,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2861</v>
+        <v>-0.2973</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.722</v>
+        <v>-5.946</v>
       </c>
     </row>
     <row r="12">
@@ -2967,10 +2967,10 @@
         <v>0.55</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4452</v>
+        <v>-0.4573</v>
       </c>
       <c r="J12" t="n">
-        <v>-13.356</v>
+        <v>-13.719</v>
       </c>
     </row>
     <row r="13">
@@ -3007,10 +3007,10 @@
         <v>0.4</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5839</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-17.517</v>
+        <v>-17.616</v>
       </c>
     </row>
     <row r="14">
@@ -3047,10 +3047,10 @@
         <v>0.39</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5931</v>
+        <v>-0.5957</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.793</v>
+        <v>-17.871</v>
       </c>
     </row>
     <row r="15">
@@ -3087,10 +3087,10 @@
         <v>1.39</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7083</v>
+        <v>0.6667</v>
       </c>
       <c r="J15" t="n">
-        <v>21.249</v>
+        <v>20.001</v>
       </c>
     </row>
     <row r="16">
@@ -3127,10 +3127,10 @@
         <v>1.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1939</v>
+        <v>0.1858</v>
       </c>
       <c r="J16" t="n">
-        <v>5.817</v>
+        <v>5.574</v>
       </c>
     </row>
     <row r="17">
@@ -3167,10 +3167,10 @@
         <v>0.62</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3863</v>
+        <v>-0.4003</v>
       </c>
       <c r="J17" t="n">
-        <v>-11.589</v>
+        <v>-12.009</v>
       </c>
     </row>
     <row r="18">
@@ -3207,10 +3207,10 @@
         <v>0.59</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4143</v>
+        <v>-0.427</v>
       </c>
       <c r="J18" t="n">
-        <v>-12.429</v>
+        <v>-12.81</v>
       </c>
     </row>
     <row r="19">
@@ -3247,10 +3247,10 @@
         <v>0.41</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.58</v>
+        <v>-0.5828</v>
       </c>
       <c r="J19" t="n">
-        <v>-17.4</v>
+        <v>-17.484</v>
       </c>
     </row>
     <row r="20">
@@ -3287,10 +3287,10 @@
         <v>1.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3764</v>
+        <v>0.3716</v>
       </c>
       <c r="J20" t="n">
-        <v>11.292</v>
+        <v>11.148</v>
       </c>
     </row>
     <row r="21">
@@ -3327,10 +3327,10 @@
         <v>1.19</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3622</v>
+        <v>0.358</v>
       </c>
       <c r="J21" t="n">
-        <v>10.866</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="22">
@@ -3367,10 +3367,10 @@
         <v>0.75</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7369</v>
+        <v>-0.6917</v>
       </c>
       <c r="J22" t="n">
-        <v>-15.4749</v>
+        <v>-14.5257</v>
       </c>
     </row>
     <row r="23">
@@ -3407,10 +3407,10 @@
         <v>0.61</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0804</v>
+        <v>-0.9892</v>
       </c>
       <c r="J23" t="n">
-        <v>-22.6884</v>
+        <v>-20.7732</v>
       </c>
     </row>
     <row r="24">
@@ -3447,10 +3447,10 @@
         <v>0.34</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7068</v>
+        <v>-1.5182</v>
       </c>
       <c r="J24" t="n">
-        <v>-35.8428</v>
+        <v>-31.8822</v>
       </c>
     </row>
     <row r="25">
@@ -3487,10 +3487,10 @@
         <v>1.59</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3468</v>
+        <v>1.4138</v>
       </c>
       <c r="J25" t="n">
-        <v>28.2828</v>
+        <v>29.6898</v>
       </c>
     </row>
     <row r="26">
@@ -3527,10 +3527,10 @@
         <v>1.51</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2374</v>
+        <v>1.258</v>
       </c>
       <c r="J26" t="n">
-        <v>25.9854</v>
+        <v>26.418</v>
       </c>
     </row>
     <row r="27">
@@ -3567,10 +3567,10 @@
         <v>1.25</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5458</v>
+        <v>0.5293</v>
       </c>
       <c r="J27" t="n">
-        <v>11.4618</v>
+        <v>11.1153</v>
       </c>
     </row>
     <row r="28">
@@ -3607,10 +3607,10 @@
         <v>0.95</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.512</v>
+        <v>-1.7451</v>
       </c>
     </row>
     <row r="29">
@@ -3647,10 +3647,10 @@
         <v>0.88</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1511</v>
+        <v>-0.1654</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.1731</v>
+        <v>-3.4734</v>
       </c>
     </row>
     <row r="30">
@@ -3687,10 +3687,10 @@
         <v>0.85</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1828</v>
+        <v>-0.1975</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.8388</v>
+        <v>-4.1475</v>
       </c>
     </row>
     <row r="31">
@@ -3727,10 +3727,10 @@
         <v>0.85</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1828</v>
+        <v>-0.1975</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.8388</v>
+        <v>-4.1475</v>
       </c>
     </row>
     <row r="32">
@@ -3767,10 +3767,10 @@
         <v>1.01</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0356</v>
+        <v>0.0419</v>
       </c>
       <c r="J32" t="n">
-        <v>1.068</v>
+        <v>1.257</v>
       </c>
     </row>
     <row r="33">
@@ -3807,10 +3807,10 @@
         <v>0.86</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1797</v>
+        <v>-0.1927</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.391</v>
+        <v>-5.781</v>
       </c>
     </row>
     <row r="34">
@@ -3847,10 +3847,10 @@
         <v>0.82</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2212</v>
+        <v>-0.2342</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.636</v>
+        <v>-7.026</v>
       </c>
     </row>
     <row r="35">
@@ -3887,10 +3887,10 @@
         <v>1.35</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6952</v>
+        <v>0.6694</v>
       </c>
       <c r="J35" t="n">
-        <v>20.856</v>
+        <v>20.082</v>
       </c>
     </row>
     <row r="36">
@@ -3927,10 +3927,10 @@
         <v>1.06</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1578</v>
+        <v>0.1673</v>
       </c>
       <c r="J36" t="n">
-        <v>4.734</v>
+        <v>5.019</v>
       </c>
     </row>
     <row r="37">
@@ -3967,10 +3967,10 @@
         <v>0.54</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2024</v>
+        <v>-1.0996</v>
       </c>
       <c r="J37" t="n">
-        <v>-36.072</v>
+        <v>-32.988</v>
       </c>
     </row>
     <row r="38">
@@ -4007,10 +4007,10 @@
         <v>0.48</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3457</v>
+        <v>-1.2204</v>
       </c>
       <c r="J38" t="n">
-        <v>-40.371</v>
+        <v>-36.612</v>
       </c>
     </row>
     <row r="39">
@@ -4047,10 +4047,10 @@
         <v>0.36</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.629</v>
+        <v>-1.4572</v>
       </c>
       <c r="J39" t="n">
-        <v>-48.87</v>
+        <v>-43.716</v>
       </c>
     </row>
     <row r="40">
@@ -4087,10 +4087,10 @@
         <v>1.4</v>
       </c>
       <c r="I40" t="n">
-        <v>1.158</v>
+        <v>1.0941</v>
       </c>
       <c r="J40" t="n">
-        <v>34.74</v>
+        <v>32.823</v>
       </c>
     </row>
     <row r="41">
@@ -4127,10 +4127,10 @@
         <v>1.3</v>
       </c>
       <c r="I41" t="n">
-        <v>0.9961</v>
+        <v>0.904</v>
       </c>
       <c r="J41" t="n">
-        <v>29.883</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="42">
@@ -4167,10 +4167,10 @@
         <v>0.98</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0196</v>
+        <v>-0.0302</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.4312</v>
+        <v>-0.6644</v>
       </c>
     </row>
     <row r="43">
@@ -4207,10 +4207,10 @@
         <v>0.86</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1624</v>
+        <v>-0.1793</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.5728</v>
+        <v>-3.9446</v>
       </c>
     </row>
     <row r="44">
@@ -4247,10 +4247,10 @@
         <v>0.63</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.385</v>
+        <v>-0.3977</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.7494</v>
       </c>
     </row>
     <row r="45">
@@ -4287,10 +4287,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.1008</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.892</v>
+        <v>-2.2176</v>
       </c>
     </row>
     <row r="46">
@@ -4327,10 +4327,10 @@
         <v>0.9</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1205</v>
+        <v>-0.1364</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.651</v>
+        <v>-3.0008</v>
       </c>
     </row>
     <row r="47">
@@ -4367,10 +4367,10 @@
         <v>0.82</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.5735</v>
+        <v>-0.5442</v>
       </c>
       <c r="J47" t="n">
-        <v>-12.617</v>
+        <v>-11.9724</v>
       </c>
     </row>
     <row r="48">
@@ -4407,10 +4407,10 @@
         <v>0.67</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9517</v>
+        <v>-0.8759</v>
       </c>
       <c r="J48" t="n">
-        <v>-20.9374</v>
+        <v>-19.2698</v>
       </c>
     </row>
     <row r="49">
@@ -4447,10 +4447,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.2139</v>
+        <v>-1.101</v>
       </c>
       <c r="J49" t="n">
-        <v>-26.7058</v>
+        <v>-24.222</v>
       </c>
     </row>
     <row r="50">
@@ -4487,10 +4487,10 @@
         <v>1.59</v>
       </c>
       <c r="I50" t="n">
-        <v>1.3203</v>
+        <v>1.2837</v>
       </c>
       <c r="J50" t="n">
-        <v>29.0466</v>
+        <v>28.2414</v>
       </c>
     </row>
     <row r="51">
@@ -4527,10 +4527,10 @@
         <v>1.44</v>
       </c>
       <c r="I51" t="n">
-        <v>1.1176</v>
+        <v>1.068</v>
       </c>
       <c r="J51" t="n">
-        <v>24.5872</v>
+        <v>23.496</v>
       </c>
     </row>
     <row r="52">
@@ -4567,10 +4567,10 @@
         <v>0.68</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.8607</v>
+        <v>-0.8081</v>
       </c>
       <c r="J52" t="n">
-        <v>-23.2389</v>
+        <v>-21.8187</v>
       </c>
     </row>
     <row r="53">
@@ -4607,10 +4607,10 @@
         <v>0.57</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.1287</v>
+        <v>-1.0374</v>
       </c>
       <c r="J53" t="n">
-        <v>-30.4749</v>
+        <v>-28.0098</v>
       </c>
     </row>
     <row r="54">
@@ -4647,10 +4647,10 @@
         <v>0.26</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.8615</v>
+        <v>-1.6499</v>
       </c>
       <c r="J54" t="n">
-        <v>-50.2605</v>
+        <v>-44.5473</v>
       </c>
     </row>
     <row r="55">
@@ -4687,10 +4687,10 @@
         <v>1.37</v>
       </c>
       <c r="I55" t="n">
-        <v>1.115</v>
+        <v>1.0468</v>
       </c>
       <c r="J55" t="n">
-        <v>30.105</v>
+        <v>28.2636</v>
       </c>
     </row>
     <row r="56">
@@ -4727,10 +4727,10 @@
         <v>1.18</v>
       </c>
       <c r="I56" t="n">
-        <v>0.6835</v>
+        <v>0.6217</v>
       </c>
       <c r="J56" t="n">
-        <v>18.4545</v>
+        <v>16.7859</v>
       </c>
     </row>
     <row r="57">
@@ -4767,10 +4767,10 @@
         <v>0.92</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.1199</v>
+        <v>-0.13</v>
       </c>
       <c r="J57" t="n">
-        <v>-3.2373</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="58">
@@ -4807,10 +4807,10 @@
         <v>0.89</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1537</v>
+        <v>-0.1648</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.1499</v>
+        <v>-4.4496</v>
       </c>
     </row>
     <row r="59">
@@ -4847,10 +4847,10 @@
         <v>0.5</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5259</v>
+        <v>-0.5281</v>
       </c>
       <c r="J59" t="n">
-        <v>-14.1993</v>
+        <v>-14.2587</v>
       </c>
     </row>
     <row r="60">
@@ -4887,10 +4887,10 @@
         <v>1.82</v>
       </c>
       <c r="I60" t="n">
-        <v>1.2439</v>
+        <v>1.2282</v>
       </c>
       <c r="J60" t="n">
-        <v>33.5853</v>
+        <v>33.1614</v>
       </c>
     </row>
     <row r="61">
@@ -4927,10 +4927,10 @@
         <v>1.25</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5054</v>
+        <v>0.4997</v>
       </c>
       <c r="J61" t="n">
-        <v>13.6458</v>
+        <v>13.4919</v>
       </c>
     </row>
     <row r="62">
@@ -4967,10 +4967,10 @@
         <v>0.74</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.7466</v>
+        <v>-0.7029</v>
       </c>
       <c r="J62" t="n">
-        <v>-17.1718</v>
+        <v>-16.1667</v>
       </c>
     </row>
     <row r="63">
@@ -5007,10 +5007,10 @@
         <v>0.54</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.233</v>
+        <v>-1.1212</v>
       </c>
       <c r="J63" t="n">
-        <v>-28.359</v>
+        <v>-25.7876</v>
       </c>
     </row>
     <row r="64">
@@ -5047,10 +5047,10 @@
         <v>0.31</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.7659</v>
+        <v>-1.5685</v>
       </c>
       <c r="J64" t="n">
-        <v>-40.6157</v>
+        <v>-36.0755</v>
       </c>
     </row>
     <row r="65">
@@ -5087,10 +5087,10 @@
         <v>1.63</v>
       </c>
       <c r="I65" t="n">
-        <v>1.4284</v>
+        <v>1.3889</v>
       </c>
       <c r="J65" t="n">
-        <v>32.8532</v>
+        <v>31.9447</v>
       </c>
     </row>
     <row r="66">
@@ -5127,10 +5127,10 @@
         <v>1.34</v>
       </c>
       <c r="I66" t="n">
-        <v>1.0123</v>
+        <v>0.9339</v>
       </c>
       <c r="J66" t="n">
-        <v>23.2829</v>
+        <v>21.4797</v>
       </c>
     </row>
     <row r="67">
@@ -5167,10 +5167,10 @@
         <v>1.21</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4327</v>
+        <v>0.433</v>
       </c>
       <c r="J67" t="n">
-        <v>9.9521</v>
+        <v>9.959</v>
       </c>
     </row>
     <row r="68">
@@ -5207,10 +5207,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3791</v>
+        <v>0.3829</v>
       </c>
       <c r="J68" t="n">
-        <v>8.7193</v>
+        <v>8.806699999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5247,10 +5247,10 @@
         <v>1.06</v>
       </c>
       <c r="I69" t="n">
-        <v>0.149</v>
+        <v>0.1611</v>
       </c>
       <c r="J69" t="n">
-        <v>3.427</v>
+        <v>3.7053</v>
       </c>
     </row>
     <row r="70">
@@ -5287,10 +5287,10 @@
         <v>1.18</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3791</v>
+        <v>0.3829</v>
       </c>
       <c r="J70" t="n">
-        <v>8.7193</v>
+        <v>8.806699999999999</v>
       </c>
     </row>
     <row r="71">
@@ -5327,10 +5327,10 @@
         <v>0.8</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2486</v>
+        <v>-0.2599</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.7178</v>
+        <v>-5.9777</v>
       </c>
     </row>
     <row r="72">
@@ -5367,10 +5367,10 @@
         <v>1.02</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0575</v>
+        <v>0.0626</v>
       </c>
       <c r="J72" t="n">
-        <v>1.4375</v>
+        <v>1.565</v>
       </c>
     </row>
     <row r="73">
@@ -5407,10 +5407,10 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0056</v>
+        <v>0.0041</v>
       </c>
       <c r="J73" t="n">
-        <v>0.14</v>
+        <v>0.1025</v>
       </c>
     </row>
     <row r="74">
@@ -5447,10 +5447,10 @@
         <v>0.71</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3214</v>
+        <v>-0.3342</v>
       </c>
       <c r="J74" t="n">
-        <v>-8.035</v>
+        <v>-8.355</v>
       </c>
     </row>
     <row r="75">
@@ -5487,10 +5487,10 @@
         <v>1.14</v>
       </c>
       <c r="I75" t="n">
-        <v>0.26</v>
+        <v>0.265</v>
       </c>
       <c r="J75" t="n">
-        <v>6.5</v>
+        <v>6.625</v>
       </c>
     </row>
     <row r="76">
@@ -5527,10 +5527,10 @@
         <v>0.9</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1292</v>
+        <v>-0.1431</v>
       </c>
       <c r="J76" t="n">
-        <v>-3.23</v>
+        <v>-3.5775</v>
       </c>
     </row>
     <row r="77">
@@ -5567,10 +5567,10 @@
         <v>0.72</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.3016</v>
+        <v>-0.317</v>
       </c>
       <c r="J77" t="n">
-        <v>-7.54</v>
+        <v>-7.925</v>
       </c>
     </row>
     <row r="78">
@@ -5607,10 +5607,10 @@
         <v>0.36</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.6323</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>-15.8075</v>
+        <v>-15.7625</v>
       </c>
     </row>
     <row r="79">
@@ -5647,10 +5647,10 @@
         <v>0.35</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.6412</v>
+        <v>-0.6388</v>
       </c>
       <c r="J79" t="n">
-        <v>-16.03</v>
+        <v>-15.97</v>
       </c>
     </row>
     <row r="80">
@@ -5687,10 +5687,10 @@
         <v>1.61</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8655</v>
+        <v>0.8308</v>
       </c>
       <c r="J80" t="n">
-        <v>21.6375</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="81">
@@ -5727,10 +5727,10 @@
         <v>1.33</v>
       </c>
       <c r="I81" t="n">
-        <v>0.5201</v>
+        <v>0.5125</v>
       </c>
       <c r="J81" t="n">
-        <v>13.0025</v>
+        <v>12.8125</v>
       </c>
     </row>
     <row r="82">
@@ -5767,10 +5767,10 @@
         <v>0.96</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.2279</v>
+        <v>-0.213</v>
       </c>
       <c r="J82" t="n">
-        <v>-3.8743</v>
+        <v>-3.621</v>
       </c>
     </row>
     <row r="83">
@@ -5807,10 +5807,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2935</v>
+        <v>-0.2754</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.9895</v>
+        <v>-4.6818</v>
       </c>
     </row>
     <row r="84">
@@ -5847,10 +5847,10 @@
         <v>0.92</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3552</v>
+        <v>-0.3331</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.0384</v>
+        <v>-5.6627</v>
       </c>
     </row>
     <row r="85">
@@ -5887,10 +5887,10 @@
         <v>1.84</v>
       </c>
       <c r="I85" t="n">
-        <v>1.5485</v>
+        <v>1.5374</v>
       </c>
       <c r="J85" t="n">
-        <v>26.3245</v>
+        <v>26.1358</v>
       </c>
     </row>
     <row r="86">
@@ -5927,10 +5927,10 @@
         <v>1.56</v>
       </c>
       <c r="I86" t="n">
-        <v>1.2067</v>
+        <v>1.1761</v>
       </c>
       <c r="J86" t="n">
-        <v>20.5139</v>
+        <v>19.9937</v>
       </c>
     </row>
     <row r="87">
@@ -5967,10 +5967,10 @@
         <v>1.53</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9331</v>
+        <v>0.8918</v>
       </c>
       <c r="J87" t="n">
-        <v>15.8627</v>
+        <v>15.1606</v>
       </c>
     </row>
     <row r="88">
@@ -6007,10 +6007,10 @@
         <v>1.37</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6829</v>
+        <v>0.6659</v>
       </c>
       <c r="J88" t="n">
-        <v>11.6093</v>
+        <v>11.3203</v>
       </c>
     </row>
     <row r="89">
@@ -6047,10 +6047,10 @@
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0148</v>
+        <v>-0.0114</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.2516</v>
+        <v>-0.1938</v>
       </c>
     </row>
     <row r="90">
@@ -6087,10 +6087,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0667</v>
+        <v>0.082</v>
       </c>
       <c r="J90" t="n">
-        <v>1.1339</v>
+        <v>1.394</v>
       </c>
     </row>
     <row r="91">
@@ -6127,10 +6127,10 @@
         <v>0.87</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1841</v>
+        <v>-0.1936</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.1297</v>
+        <v>-3.2912</v>
       </c>
     </row>
     <row r="92">
@@ -6167,10 +6167,10 @@
         <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0011</v>
+        <v>0.0007</v>
       </c>
       <c r="J92" t="n">
-        <v>0.0198</v>
+        <v>0.0126</v>
       </c>
     </row>
     <row r="93">
@@ -6207,10 +6207,10 @@
         <v>0.4</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.5771</v>
+        <v>-1.4088</v>
       </c>
       <c r="J93" t="n">
-        <v>-28.3878</v>
+        <v>-25.3584</v>
       </c>
     </row>
     <row r="94">
@@ -6247,10 +6247,10 @@
         <v>0.12</v>
       </c>
       <c r="I94" t="n">
-        <v>-2.1996</v>
+        <v>-1.9262</v>
       </c>
       <c r="J94" t="n">
-        <v>-39.5928</v>
+        <v>-34.6716</v>
       </c>
     </row>
     <row r="95">
@@ -6287,10 +6287,10 @@
         <v>2.01</v>
       </c>
       <c r="I95" t="n">
-        <v>1.8338</v>
+        <v>1.8623</v>
       </c>
       <c r="J95" t="n">
-        <v>33.0084</v>
+        <v>33.5214</v>
       </c>
     </row>
     <row r="96">
@@ -6327,10 +6327,10 @@
         <v>1.43</v>
       </c>
       <c r="I96" t="n">
-        <v>1.113</v>
+        <v>1.0611</v>
       </c>
       <c r="J96" t="n">
-        <v>20.034</v>
+        <v>19.0998</v>
       </c>
     </row>
     <row r="97">
@@ -6367,10 +6367,10 @@
         <v>1.39</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7117</v>
+        <v>0.6926</v>
       </c>
       <c r="J97" t="n">
-        <v>12.8106</v>
+        <v>12.4668</v>
       </c>
     </row>
     <row r="98">
@@ -6407,10 +6407,10 @@
         <v>1.37</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6798</v>
+        <v>0.6636</v>
       </c>
       <c r="J98" t="n">
-        <v>12.2364</v>
+        <v>11.9448</v>
       </c>
     </row>
     <row r="99">
@@ -6447,10 +6447,10 @@
         <v>0.83</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.227</v>
+        <v>-0.2366</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.086</v>
+        <v>-4.2588</v>
       </c>
     </row>
     <row r="100">
@@ -6487,10 +6487,10 @@
         <v>1.18</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3645</v>
+        <v>0.3724</v>
       </c>
       <c r="J100" t="n">
-        <v>6.561</v>
+        <v>6.7032</v>
       </c>
     </row>
     <row r="101">
@@ -6527,10 +6527,10 @@
         <v>1.09</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1982</v>
+        <v>0.2129</v>
       </c>
       <c r="J101" t="n">
-        <v>3.5676</v>
+        <v>3.8322</v>
       </c>
     </row>
     <row r="102">
@@ -6567,10 +6567,10 @@
         <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0225</v>
+        <v>0.0162</v>
       </c>
       <c r="J102" t="n">
-        <v>0.54</v>
+        <v>0.3888</v>
       </c>
     </row>
     <row r="103">
@@ -6607,10 +6607,10 @@
         <v>0.92</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.102</v>
+        <v>-0.1163</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.448</v>
+        <v>-2.7912</v>
       </c>
     </row>
     <row r="104">
@@ -6647,10 +6647,10 @@
         <v>0.66</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3613</v>
+        <v>-0.3742</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.671200000000001</v>
+        <v>-8.9808</v>
       </c>
     </row>
     <row r="105">
@@ -6687,10 +6687,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0532</v>
+        <v>-0.0649</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.2768</v>
+        <v>-1.5576</v>
       </c>
     </row>
     <row r="106">
@@ -6727,10 +6727,10 @@
         <v>0.93</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.1042</v>
       </c>
       <c r="J106" t="n">
-        <v>-2.1696</v>
+        <v>-2.5008</v>
       </c>
     </row>
     <row r="107">
@@ -6767,10 +6767,10 @@
         <v>0.61</v>
       </c>
       <c r="I107" t="n">
-        <v>-1.0954</v>
+        <v>-0.9997</v>
       </c>
       <c r="J107" t="n">
-        <v>-26.2896</v>
+        <v>-23.9928</v>
       </c>
     </row>
     <row r="108">
@@ -6807,10 +6807,10 @@
         <v>0.59</v>
       </c>
       <c r="I108" t="n">
-        <v>-1.1428</v>
+        <v>-1.0404</v>
       </c>
       <c r="J108" t="n">
-        <v>-27.4272</v>
+        <v>-24.9696</v>
       </c>
     </row>
     <row r="109">
@@ -6847,10 +6847,10 @@
         <v>0.52</v>
       </c>
       <c r="I109" t="n">
-        <v>-1.3067</v>
+        <v>-1.18</v>
       </c>
       <c r="J109" t="n">
-        <v>-31.3608</v>
+        <v>-28.32</v>
       </c>
     </row>
     <row r="110">
@@ -6887,10 +6887,10 @@
         <v>1.73</v>
       </c>
       <c r="I110" t="n">
-        <v>1.2316</v>
+        <v>1.3306</v>
       </c>
       <c r="J110" t="n">
-        <v>29.5584</v>
+        <v>31.9344</v>
       </c>
     </row>
     <row r="111">
@@ -6927,10 +6927,10 @@
         <v>1.62</v>
       </c>
       <c r="I111" t="n">
-        <v>1.0873</v>
+        <v>1.1792</v>
       </c>
       <c r="J111" t="n">
-        <v>26.0952</v>
+        <v>28.3008</v>
       </c>
     </row>
     <row r="112">
@@ -6967,10 +6967,10 @@
         <v>1.41</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6017</v>
+        <v>0.672</v>
       </c>
       <c r="J112" t="n">
-        <v>16.2459</v>
+        <v>18.144</v>
       </c>
     </row>
     <row r="113">
@@ -7007,10 +7007,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2333</v>
+        <v>-0.2458</v>
       </c>
       <c r="J113" t="n">
-        <v>-6.2991</v>
+        <v>-6.6366</v>
       </c>
     </row>
     <row r="114">
@@ -7047,10 +7047,10 @@
         <v>0.62</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4148</v>
+        <v>-0.4227</v>
       </c>
       <c r="J114" t="n">
-        <v>-11.1996</v>
+        <v>-11.4129</v>
       </c>
     </row>
     <row r="115">
@@ -7087,10 +7087,10 @@
         <v>1.36</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5527</v>
+        <v>0.6167</v>
       </c>
       <c r="J115" t="n">
-        <v>14.9229</v>
+        <v>16.6509</v>
       </c>
     </row>
     <row r="116">
@@ -7127,10 +7127,10 @@
         <v>0.99</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0238</v>
+        <v>-0.0277</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.7479</v>
       </c>
     </row>
     <row r="117">
@@ -7167,10 +7167,10 @@
         <v>0.8</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.5883</v>
+        <v>-0.5645</v>
       </c>
       <c r="J117" t="n">
-        <v>-15.8841</v>
+        <v>-15.2415</v>
       </c>
     </row>
     <row r="118">
@@ -7207,10 +7207,10 @@
         <v>0.71</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.8163</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>-22.0401</v>
+        <v>-20.6442</v>
       </c>
     </row>
     <row r="119">
@@ -7247,10 +7247,10 @@
         <v>0.63</v>
       </c>
       <c r="I119" t="n">
-        <v>-1.0125</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>-27.3375</v>
+        <v>-25.218</v>
       </c>
     </row>
     <row r="120">
@@ -7287,10 +7287,10 @@
         <v>1.25</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6148</v>
+        <v>0.6642</v>
       </c>
       <c r="J120" t="n">
-        <v>16.5996</v>
+        <v>17.9334</v>
       </c>
     </row>
     <row r="121">
@@ -7327,10 +7327,10 @@
         <v>1.09</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3518</v>
+        <v>0.3463</v>
       </c>
       <c r="J121" t="n">
-        <v>9.4986</v>
+        <v>9.350099999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7367,10 +7367,10 @@
         <v>1.4</v>
       </c>
       <c r="I122" t="n">
-        <v>0.746</v>
+        <v>0.8239</v>
       </c>
       <c r="J122" t="n">
-        <v>30.586</v>
+        <v>33.7799</v>
       </c>
     </row>
     <row r="123">
@@ -7407,10 +7407,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3684</v>
+        <v>0.391</v>
       </c>
       <c r="J123" t="n">
-        <v>15.1044</v>
+        <v>16.031</v>
       </c>
     </row>
     <row r="124">
@@ -7447,10 +7447,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3342</v>
+        <v>0.3416</v>
       </c>
       <c r="J124" t="n">
-        <v>13.7022</v>
+        <v>14.0056</v>
       </c>
     </row>
     <row r="125">
@@ -7487,10 +7487,10 @@
         <v>1.09</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2824</v>
+        <v>0.2897</v>
       </c>
       <c r="J125" t="n">
-        <v>11.5784</v>
+        <v>11.8777</v>
       </c>
     </row>
     <row r="126">
@@ -7527,10 +7527,10 @@
         <v>1.09</v>
       </c>
       <c r="I126" t="n">
-        <v>0.2824</v>
+        <v>0.2897</v>
       </c>
       <c r="J126" t="n">
-        <v>11.5784</v>
+        <v>11.8777</v>
       </c>
     </row>
     <row r="127">
@@ -7567,10 +7567,10 @@
         <v>1.07</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1935</v>
+        <v>0.1987</v>
       </c>
       <c r="J127" t="n">
-        <v>7.9335</v>
+        <v>8.146699999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7607,10 +7607,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1713</v>
+        <v>0.177</v>
       </c>
       <c r="J128" t="n">
-        <v>7.0233</v>
+        <v>7.257</v>
       </c>
     </row>
     <row r="129">
@@ -7647,10 +7647,10 @@
         <v>1.02</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0737</v>
+        <v>0.0789</v>
       </c>
       <c r="J129" t="n">
-        <v>3.0217</v>
+        <v>3.2349</v>
       </c>
     </row>
     <row r="130">
@@ -7687,10 +7687,10 @@
         <v>0.88</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1516</v>
+        <v>-0.1658</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.2156</v>
+        <v>-6.7978</v>
       </c>
     </row>
     <row r="131">
@@ -7727,10 +7727,10 @@
         <v>0.77</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.264</v>
+        <v>-0.2781</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.824</v>
+        <v>-11.4021</v>
       </c>
     </row>
     <row r="132">
@@ -7767,10 +7767,10 @@
         <v>1.82</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1718</v>
+        <v>1.2952</v>
       </c>
       <c r="J132" t="n">
-        <v>21.0924</v>
+        <v>23.3136</v>
       </c>
     </row>
     <row r="133">
@@ -7807,10 +7807,10 @@
         <v>1.68</v>
       </c>
       <c r="I133" t="n">
-        <v>1.0159</v>
+        <v>1.129</v>
       </c>
       <c r="J133" t="n">
-        <v>18.2862</v>
+        <v>20.322</v>
       </c>
     </row>
     <row r="134">
@@ -7847,10 +7847,10 @@
         <v>1.62</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9489</v>
+        <v>1.057</v>
       </c>
       <c r="J134" t="n">
-        <v>17.0802</v>
+        <v>19.026</v>
       </c>
     </row>
     <row r="135">
@@ -7887,10 +7887,10 @@
         <v>1.46</v>
       </c>
       <c r="I135" t="n">
-        <v>0.7639</v>
+        <v>0.8562</v>
       </c>
       <c r="J135" t="n">
-        <v>13.7502</v>
+        <v>15.4116</v>
       </c>
     </row>
     <row r="136">
@@ -7927,10 +7927,10 @@
         <v>1.41</v>
       </c>
       <c r="I136" t="n">
-        <v>0.7022</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="J136" t="n">
-        <v>12.6396</v>
+        <v>14.1984</v>
       </c>
     </row>
     <row r="137">
@@ -7967,10 +7967,10 @@
         <v>0.79</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1325</v>
+        <v>-0.1711</v>
       </c>
       <c r="J137" t="n">
-        <v>-2.385</v>
+        <v>-3.0798</v>
       </c>
     </row>
     <row r="138">
@@ -8007,10 +8007,10 @@
         <v>0.68</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2616</v>
+        <v>-0.2931</v>
       </c>
       <c r="J138" t="n">
-        <v>-4.7088</v>
+        <v>-5.2758</v>
       </c>
     </row>
     <row r="139">
@@ -8047,10 +8047,10 @@
         <v>0.39</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.5476</v>
+        <v>-0.5598</v>
       </c>
       <c r="J139" t="n">
-        <v>-9.8568</v>
+        <v>-10.0764</v>
       </c>
     </row>
     <row r="140">
@@ -8087,10 +8087,10 @@
         <v>0.32</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.617</v>
+        <v>-0.6233</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.106</v>
+        <v>-11.2194</v>
       </c>
     </row>
     <row r="141">
@@ -8127,10 +8127,10 @@
         <v>0.29</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6472</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.6496</v>
+        <v>-11.7126</v>
       </c>
     </row>
     <row r="142">
@@ -8167,10 +8167,10 @@
         <v>1.34</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5727</v>
+        <v>0.6312</v>
       </c>
       <c r="J142" t="n">
-        <v>16.0356</v>
+        <v>17.6736</v>
       </c>
     </row>
     <row r="143">
@@ -8207,10 +8207,10 @@
         <v>0.99</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.016</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.238</v>
+        <v>-0.448</v>
       </c>
     </row>
     <row r="144">
@@ -8247,10 +8247,10 @@
         <v>0.82</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2056</v>
+        <v>-0.2221</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.7568</v>
+        <v>-6.2188</v>
       </c>
     </row>
     <row r="145">
@@ -8287,10 +8287,10 @@
         <v>0.74</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2845</v>
+        <v>-0.2998</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.966</v>
+        <v>-8.394399999999999</v>
       </c>
     </row>
     <row r="146">
@@ -8327,10 +8327,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4536</v>
+        <v>-0.4625</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.7008</v>
+        <v>-12.95</v>
       </c>
     </row>
     <row r="147">
@@ -8367,10 +8367,10 @@
         <v>1.64</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0523</v>
+        <v>1.1523</v>
       </c>
       <c r="J147" t="n">
-        <v>29.4644</v>
+        <v>32.2644</v>
       </c>
     </row>
     <row r="148">
@@ -8407,10 +8407,10 @@
         <v>1.33</v>
       </c>
       <c r="I148" t="n">
-        <v>0.65</v>
+        <v>0.7198</v>
       </c>
       <c r="J148" t="n">
-        <v>18.2</v>
+        <v>20.1544</v>
       </c>
     </row>
     <row r="149">
@@ -8447,10 +8447,10 @@
         <v>1.05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1587</v>
+        <v>0.1739</v>
       </c>
       <c r="J149" t="n">
-        <v>4.4436</v>
+        <v>4.8692</v>
       </c>
     </row>
     <row r="150">
@@ -8487,10 +8487,10 @@
         <v>0.93</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3073</v>
+        <v>-0.2925</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.6044</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="151">
@@ -8527,10 +8527,10 @@
         <v>0.92</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3378</v>
+        <v>-0.3209</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.458399999999999</v>
+        <v>-8.985200000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8567,10 +8567,10 @@
         <v>1.38</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4326</v>
+        <v>0.4901</v>
       </c>
       <c r="J152" t="n">
-        <v>12.978</v>
+        <v>14.703</v>
       </c>
     </row>
     <row r="153">
@@ -8607,10 +8607,10 @@
         <v>1.29</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3707</v>
+        <v>0.4083</v>
       </c>
       <c r="J153" t="n">
-        <v>11.121</v>
+        <v>12.249</v>
       </c>
     </row>
     <row r="154">
@@ -8647,10 +8647,10 @@
         <v>1.18</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2624</v>
+        <v>0.2788</v>
       </c>
       <c r="J154" t="n">
-        <v>7.872</v>
+        <v>8.364000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -8687,10 +8687,10 @@
         <v>0.95</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0906</v>
+        <v>-0.0975</v>
       </c>
       <c r="J155" t="n">
-        <v>-2.718</v>
+        <v>-2.925</v>
       </c>
     </row>
     <row r="156">
@@ -8727,10 +8727,10 @@
         <v>0.91</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1383</v>
+        <v>-0.1473</v>
       </c>
       <c r="J156" t="n">
-        <v>-4.149</v>
+        <v>-4.419</v>
       </c>
     </row>
     <row r="157">
@@ -8767,10 +8767,10 @@
         <v>1.16</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2947</v>
+        <v>0.2973</v>
       </c>
       <c r="J157" t="n">
-        <v>8.840999999999999</v>
+        <v>8.919</v>
       </c>
     </row>
     <row r="158">
@@ -8807,10 +8807,10 @@
         <v>1.04</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1002</v>
+        <v>0.106</v>
       </c>
       <c r="J158" t="n">
-        <v>3.006</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="159">
@@ -8847,10 +8847,10 @@
         <v>0.91</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1164</v>
+        <v>-0.1303</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.492</v>
+        <v>-3.909</v>
       </c>
     </row>
     <row r="160">
@@ -8887,10 +8887,10 @@
         <v>0.79</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2413</v>
+        <v>-0.2563</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.239</v>
+        <v>-7.689</v>
       </c>
     </row>
     <row r="161">
@@ -8927,10 +8927,10 @@
         <v>0.78</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2512</v>
+        <v>-0.2661</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.536</v>
+        <v>-7.983</v>
       </c>
     </row>
     <row r="162">
@@ -8967,10 +8967,10 @@
         <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2163</v>
+        <v>0.2206</v>
       </c>
       <c r="J162" t="n">
-        <v>6.2727</v>
+        <v>6.3974</v>
       </c>
     </row>
     <row r="163">
@@ -9007,10 +9007,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0469</v>
+        <v>-0.0558</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.3601</v>
+        <v>-1.6182</v>
       </c>
     </row>
     <row r="164">
@@ -9047,10 +9047,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0599</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.7371</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="165">
@@ -9087,10 +9087,10 @@
         <v>0.91</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1183</v>
+        <v>-0.1318</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.4307</v>
+        <v>-3.8222</v>
       </c>
     </row>
     <row r="166">
@@ -9127,10 +9127,10 @@
         <v>0.86</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1724</v>
+        <v>-0.187</v>
       </c>
       <c r="J166" t="n">
-        <v>-4.9996</v>
+        <v>-5.423</v>
       </c>
     </row>
     <row r="167">
@@ -9167,10 +9167,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7651</v>
+        <v>0.8434</v>
       </c>
       <c r="J167" t="n">
-        <v>22.1879</v>
+        <v>24.4586</v>
       </c>
     </row>
     <row r="168">
@@ -9207,10 +9207,10 @@
         <v>1.36</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6979</v>
+        <v>0.7705</v>
       </c>
       <c r="J168" t="n">
-        <v>20.2391</v>
+        <v>22.3445</v>
       </c>
     </row>
     <row r="169">
@@ -9247,10 +9247,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0625</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="J169" t="n">
-        <v>1.8125</v>
+        <v>2.2678</v>
       </c>
     </row>
     <row r="170">
@@ -9287,10 +9287,10 @@
         <v>0.99</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0882</v>
+        <v>-0.0827</v>
       </c>
       <c r="J170" t="n">
-        <v>-2.5578</v>
+        <v>-2.3983</v>
       </c>
     </row>
     <row r="171">
@@ -9327,10 +9327,10 @@
         <v>0.92</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3289</v>
+        <v>-0.3147</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.5381</v>
+        <v>-9.126300000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9367,10 +9367,10 @@
         <v>1.13</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3801</v>
+        <v>0.4043</v>
       </c>
       <c r="J172" t="n">
-        <v>12.9234</v>
+        <v>13.7462</v>
       </c>
     </row>
     <row r="173">
@@ -9407,10 +9407,10 @@
         <v>1.07</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2441</v>
+        <v>0.2487</v>
       </c>
       <c r="J173" t="n">
-        <v>8.2994</v>
+        <v>8.4558</v>
       </c>
     </row>
     <row r="174">
@@ -9447,10 +9447,10 @@
         <v>0.96</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1811</v>
+        <v>-0.1803</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.1574</v>
+        <v>-6.1302</v>
       </c>
     </row>
     <row r="175">
@@ -9487,10 +9487,10 @@
         <v>1.15</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4116</v>
+        <v>0.448</v>
       </c>
       <c r="J175" t="n">
-        <v>13.9944</v>
+        <v>15.232</v>
       </c>
     </row>
     <row r="176">
@@ -9527,10 +9527,10 @@
         <v>1.01</v>
       </c>
       <c r="I176" t="n">
-        <v>0.0408</v>
+        <v>0.0502</v>
       </c>
       <c r="J176" t="n">
-        <v>1.3872</v>
+        <v>1.7068</v>
       </c>
     </row>
     <row r="177">
@@ -9567,10 +9567,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.2299</v>
+        <v>-0.2432</v>
       </c>
       <c r="J177" t="n">
-        <v>-7.8166</v>
+        <v>-8.268800000000001</v>
       </c>
     </row>
     <row r="178">
@@ -9607,10 +9607,10 @@
         <v>0.8</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2399</v>
+        <v>-0.2531</v>
       </c>
       <c r="J178" t="n">
-        <v>-8.156599999999999</v>
+        <v>-8.605399999999999</v>
       </c>
     </row>
     <row r="179">
@@ -9647,10 +9647,10 @@
         <v>0.74</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2989</v>
+        <v>-0.3111</v>
       </c>
       <c r="J179" t="n">
-        <v>-10.1626</v>
+        <v>-10.5774</v>
       </c>
     </row>
     <row r="180">
@@ -9687,10 +9687,10 @@
         <v>1.46</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6579</v>
+        <v>0.7336</v>
       </c>
       <c r="J180" t="n">
-        <v>22.3686</v>
+        <v>24.9424</v>
       </c>
     </row>
     <row r="181">
@@ -9727,10 +9727,10 @@
         <v>1.23</v>
       </c>
       <c r="I181" t="n">
-        <v>0.4263</v>
+        <v>0.4708</v>
       </c>
       <c r="J181" t="n">
-        <v>14.4942</v>
+        <v>16.0072</v>
       </c>
     </row>
     <row r="182">
@@ -9767,10 +9767,10 @@
         <v>1.09</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2782</v>
+        <v>0.2868</v>
       </c>
       <c r="J182" t="n">
-        <v>10.0152</v>
+        <v>10.3248</v>
       </c>
     </row>
     <row r="183">
@@ -9807,10 +9807,10 @@
         <v>1.09</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2782</v>
+        <v>0.2868</v>
       </c>
       <c r="J183" t="n">
-        <v>10.0152</v>
+        <v>10.3248</v>
       </c>
     </row>
     <row r="184">
@@ -9847,10 +9847,10 @@
         <v>1</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0441</v>
+        <v>-0.0304</v>
       </c>
       <c r="J184" t="n">
-        <v>-1.5876</v>
+        <v>-1.0944</v>
       </c>
     </row>
     <row r="185">
@@ -9887,10 +9887,10 @@
         <v>1.66</v>
       </c>
       <c r="I185" t="n">
-        <v>1.0748</v>
+        <v>1.1766</v>
       </c>
       <c r="J185" t="n">
-        <v>38.6928</v>
+        <v>42.3576</v>
       </c>
     </row>
     <row r="186">
@@ -9927,10 +9927,10 @@
         <v>1.07</v>
       </c>
       <c r="I186" t="n">
-        <v>0.2193</v>
+        <v>0.2317</v>
       </c>
       <c r="J186" t="n">
-        <v>7.8948</v>
+        <v>8.341200000000001</v>
       </c>
     </row>
     <row r="187">
@@ -9967,10 +9967,10 @@
         <v>0.95</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.7972</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="188">
@@ -10007,10 +10007,10 @@
         <v>0.78</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.261</v>
+        <v>-0.2737</v>
       </c>
       <c r="J188" t="n">
-        <v>-9.396000000000001</v>
+        <v>-9.853199999999999</v>
       </c>
     </row>
     <row r="189">
@@ -10047,10 +10047,10 @@
         <v>0.6</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.4311</v>
+        <v>-0.4387</v>
       </c>
       <c r="J189" t="n">
-        <v>-15.5196</v>
+        <v>-15.7932</v>
       </c>
     </row>
     <row r="190">
@@ -10087,10 +10087,10 @@
         <v>1.46</v>
       </c>
       <c r="I190" t="n">
-        <v>0.6552</v>
+        <v>0.731</v>
       </c>
       <c r="J190" t="n">
-        <v>23.5872</v>
+        <v>26.316</v>
       </c>
     </row>
     <row r="191">
@@ -10127,10 +10127,10 @@
         <v>1.3</v>
       </c>
       <c r="I191" t="n">
-        <v>0.4969</v>
+        <v>0.5523</v>
       </c>
       <c r="J191" t="n">
-        <v>17.8884</v>
+        <v>19.8828</v>
       </c>
     </row>
     <row r="192">
@@ -10167,10 +10167,10 @@
         <v>1.44</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0946</v>
+        <v>1.0467</v>
       </c>
       <c r="J192" t="n">
-        <v>27.365</v>
+        <v>26.1675</v>
       </c>
     </row>
     <row r="193">
@@ -10207,10 +10207,10 @@
         <v>1.08</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2702</v>
+        <v>0.2741</v>
       </c>
       <c r="J193" t="n">
-        <v>6.755</v>
+        <v>6.8525</v>
       </c>
     </row>
     <row r="194">
@@ -10247,10 +10247,10 @@
         <v>1.01</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0359</v>
+        <v>0.0468</v>
       </c>
       <c r="J194" t="n">
-        <v>0.8975</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="195">
@@ -10287,10 +10287,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2199</v>
+        <v>-0.2159</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.4975</v>
+        <v>-5.3975</v>
       </c>
     </row>
     <row r="196">
@@ -10327,10 +10327,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.252</v>
+        <v>-0.2464</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.3</v>
+        <v>-6.16</v>
       </c>
     </row>
     <row r="197">
@@ -10367,10 +10367,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6425</v>
+        <v>0.6191</v>
       </c>
       <c r="J197" t="n">
-        <v>16.0625</v>
+        <v>15.4775</v>
       </c>
     </row>
     <row r="198">
@@ -10407,10 +10407,10 @@
         <v>1.11</v>
       </c>
       <c r="I198" t="n">
-        <v>0.272</v>
+        <v>0.2758</v>
       </c>
       <c r="J198" t="n">
-        <v>6.8</v>
+        <v>6.895</v>
       </c>
     </row>
     <row r="199">
@@ -10447,10 +10447,10 @@
         <v>1.1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2516</v>
+        <v>0.2563</v>
       </c>
       <c r="J199" t="n">
-        <v>6.29</v>
+        <v>6.4075</v>
       </c>
     </row>
     <row r="200">
@@ -10487,10 +10487,10 @@
         <v>0.72</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3149</v>
+        <v>-0.3274</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.8725</v>
+        <v>-8.185</v>
       </c>
     </row>
     <row r="201">
@@ -10527,10 +10527,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3716</v>
+        <v>-0.3823</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.289999999999999</v>
+        <v>-9.557499999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10567,10 +10567,10 @@
         <v>1.25</v>
       </c>
       <c r="I202" t="n">
-        <v>0.433</v>
+        <v>0.4262</v>
       </c>
       <c r="J202" t="n">
-        <v>12.557</v>
+        <v>12.3598</v>
       </c>
     </row>
     <row r="203">
@@ -10607,10 +10607,10 @@
         <v>1.06</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1423</v>
+        <v>0.147</v>
       </c>
       <c r="J203" t="n">
-        <v>4.1267</v>
+        <v>4.263</v>
       </c>
     </row>
     <row r="204">
@@ -10647,10 +10647,10 @@
         <v>1.04</v>
       </c>
       <c r="I204" t="n">
-        <v>0.106</v>
+        <v>0.1104</v>
       </c>
       <c r="J204" t="n">
-        <v>3.074</v>
+        <v>3.2016</v>
       </c>
     </row>
     <row r="205">
@@ -10687,10 +10687,10 @@
         <v>0.63</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3914</v>
+        <v>-0.4027</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.3506</v>
+        <v>-11.6783</v>
       </c>
     </row>
     <row r="206">
@@ -10727,10 +10727,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4468</v>
+        <v>-0.4556</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.9572</v>
+        <v>-13.2124</v>
       </c>
     </row>
     <row r="207">
@@ -10767,10 +10767,10 @@
         <v>1.28</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3841</v>
+        <v>0.397</v>
       </c>
       <c r="J207" t="n">
-        <v>11.1389</v>
+        <v>11.513</v>
       </c>
     </row>
     <row r="208">
@@ -10807,10 +10807,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3117</v>
+        <v>0.3271</v>
       </c>
       <c r="J208" t="n">
-        <v>9.039300000000001</v>
+        <v>9.485900000000001</v>
       </c>
     </row>
     <row r="209">
@@ -10847,10 +10847,10 @@
         <v>1.21</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2994</v>
+        <v>0.3151</v>
       </c>
       <c r="J209" t="n">
-        <v>8.682600000000001</v>
+        <v>9.1379</v>
       </c>
     </row>
     <row r="210">
@@ -10887,10 +10887,10 @@
         <v>1.18</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2622</v>
+        <v>0.2787</v>
       </c>
       <c r="J210" t="n">
-        <v>7.6038</v>
+        <v>8.0823</v>
       </c>
     </row>
     <row r="211">
@@ -10927,10 +10927,10 @@
         <v>0.83</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2242</v>
+        <v>-0.2344</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.5018</v>
+        <v>-6.7976</v>
       </c>
     </row>
     <row r="212">
@@ -10967,10 +10967,10 @@
         <v>1.38</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9821</v>
+        <v>0.9218</v>
       </c>
       <c r="J212" t="n">
-        <v>27.4988</v>
+        <v>25.8104</v>
       </c>
     </row>
     <row r="213">
@@ -11007,10 +11007,10 @@
         <v>1.28</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7593</v>
+        <v>0.7205</v>
       </c>
       <c r="J213" t="n">
-        <v>21.2604</v>
+        <v>20.174</v>
       </c>
     </row>
     <row r="214">
@@ -11047,10 +11047,10 @@
         <v>1.14</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4195</v>
+        <v>0.4156</v>
       </c>
       <c r="J214" t="n">
-        <v>11.746</v>
+        <v>11.6368</v>
       </c>
     </row>
     <row r="215">
@@ -11087,10 +11087,10 @@
         <v>1.03</v>
       </c>
       <c r="I215" t="n">
-        <v>0.095</v>
+        <v>0.1115</v>
       </c>
       <c r="J215" t="n">
-        <v>2.66</v>
+        <v>3.122</v>
       </c>
     </row>
     <row r="216">
@@ -11127,10 +11127,10 @@
         <v>0.96</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2062</v>
+        <v>-0.1978</v>
       </c>
       <c r="J216" t="n">
-        <v>-5.7736</v>
+        <v>-5.5384</v>
       </c>
     </row>
     <row r="217">
@@ -11167,10 +11167,10 @@
         <v>1.09</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2523</v>
+        <v>0.252</v>
       </c>
       <c r="J217" t="n">
-        <v>7.0644</v>
+        <v>7.056</v>
       </c>
     </row>
     <row r="218">
@@ -11207,10 +11207,10 @@
         <v>1.04</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1386</v>
+        <v>0.1409</v>
       </c>
       <c r="J218" t="n">
-        <v>3.8808</v>
+        <v>3.9452</v>
       </c>
     </row>
     <row r="219">
@@ -11247,10 +11247,10 @@
         <v>0.9</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.125</v>
+        <v>-0.1398</v>
       </c>
       <c r="J219" t="n">
-        <v>-3.5</v>
+        <v>-3.9144</v>
       </c>
     </row>
     <row r="220">
@@ -11287,10 +11287,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2181</v>
+        <v>-0.234</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.1068</v>
+        <v>-6.552</v>
       </c>
     </row>
     <row r="221">
@@ -11327,10 +11327,10 @@
         <v>0.71</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3159</v>
+        <v>-0.33</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.8452</v>
+        <v>-9.24</v>
       </c>
     </row>
     <row r="222">
@@ -11367,10 +11367,10 @@
         <v>1.28</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5273</v>
       </c>
       <c r="J222" t="n">
-        <v>11.1237</v>
+        <v>11.0733</v>
       </c>
     </row>
     <row r="223">
@@ -11407,10 +11407,10 @@
         <v>1.25</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4801</v>
+        <v>0.4814</v>
       </c>
       <c r="J223" t="n">
-        <v>10.0821</v>
+        <v>10.1094</v>
       </c>
     </row>
     <row r="224">
@@ -11447,10 +11447,10 @@
         <v>1.2</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3965</v>
+        <v>0.4032</v>
       </c>
       <c r="J224" t="n">
-        <v>8.326499999999999</v>
+        <v>8.4672</v>
       </c>
     </row>
     <row r="225">
@@ -11487,10 +11487,10 @@
         <v>1.28</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5273</v>
       </c>
       <c r="J225" t="n">
-        <v>11.1237</v>
+        <v>11.0733</v>
       </c>
     </row>
     <row r="226">
@@ -11527,10 +11527,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1078</v>
+        <v>-0.1143</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.2638</v>
+        <v>-2.4003</v>
       </c>
     </row>
     <row r="227">
@@ -11567,10 +11567,10 @@
         <v>0.74</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.786</v>
+        <v>-0.7306</v>
       </c>
       <c r="J227" t="n">
-        <v>-16.506</v>
+        <v>-15.3426</v>
       </c>
     </row>
     <row r="228">
@@ -11607,10 +11607,10 @@
         <v>0.61</v>
       </c>
       <c r="I228" t="n">
-        <v>-1.1021</v>
+        <v>-1.0045</v>
       </c>
       <c r="J228" t="n">
-        <v>-23.1441</v>
+        <v>-21.0945</v>
       </c>
     </row>
     <row r="229">
@@ -11647,10 +11647,10 @@
         <v>0.46</v>
       </c>
       <c r="I229" t="n">
-        <v>-1.4504</v>
+        <v>-1.3009</v>
       </c>
       <c r="J229" t="n">
-        <v>-30.4584</v>
+        <v>-27.3189</v>
       </c>
     </row>
     <row r="230">
@@ -11687,10 +11687,10 @@
         <v>2.03</v>
       </c>
       <c r="I230" t="n">
-        <v>1.8338</v>
+        <v>1.8605</v>
       </c>
       <c r="J230" t="n">
-        <v>38.5098</v>
+        <v>39.0705</v>
       </c>
     </row>
     <row r="231">
@@ -11727,10 +11727,10 @@
         <v>1.36</v>
       </c>
       <c r="I231" t="n">
-        <v>0.9878</v>
+        <v>0.9192</v>
       </c>
       <c r="J231" t="n">
-        <v>20.7438</v>
+        <v>19.3032</v>
       </c>
     </row>
     <row r="232">
@@ -11767,10 +11767,10 @@
         <v>1.47</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8575</v>
+        <v>0.8205</v>
       </c>
       <c r="J232" t="n">
-        <v>20.58</v>
+        <v>19.692</v>
       </c>
     </row>
     <row r="233">
@@ -11807,10 +11807,10 @@
         <v>1.2</v>
       </c>
       <c r="I233" t="n">
-        <v>0.4093</v>
+        <v>0.4123</v>
       </c>
       <c r="J233" t="n">
-        <v>9.8232</v>
+        <v>9.895200000000001</v>
       </c>
     </row>
     <row r="234">
@@ -11847,10 +11847,10 @@
         <v>1.08</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1872</v>
+        <v>0.1998</v>
       </c>
       <c r="J234" t="n">
-        <v>4.4928</v>
+        <v>4.7952</v>
       </c>
     </row>
     <row r="235">
@@ -11887,10 +11887,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1352</v>
+        <v>-0.1448</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.2448</v>
+        <v>-3.4752</v>
       </c>
     </row>
     <row r="236">
@@ -11927,10 +11927,10 @@
         <v>0.9</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1464</v>
+        <v>-0.1564</v>
       </c>
       <c r="J236" t="n">
-        <v>-3.5136</v>
+        <v>-3.7536</v>
       </c>
     </row>
     <row r="237">
@@ -11967,10 +11967,10 @@
         <v>0.9</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.3632</v>
+        <v>-0.3519</v>
       </c>
       <c r="J237" t="n">
-        <v>-8.716799999999999</v>
+        <v>-8.445600000000001</v>
       </c>
     </row>
     <row r="238">
@@ -12007,10 +12007,10 @@
         <v>0.73</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.8137</v>
+        <v>-0.7544</v>
       </c>
       <c r="J238" t="n">
-        <v>-19.5288</v>
+        <v>-18.1056</v>
       </c>
     </row>
     <row r="239">
@@ -12047,10 +12047,10 @@
         <v>0.67</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.961</v>
+        <v>-0.8825</v>
       </c>
       <c r="J239" t="n">
-        <v>-23.064</v>
+        <v>-21.18</v>
       </c>
     </row>
     <row r="240">
@@ -12087,10 +12087,10 @@
         <v>1.58</v>
       </c>
       <c r="I240" t="n">
-        <v>1.2928</v>
+        <v>1.257</v>
       </c>
       <c r="J240" t="n">
-        <v>31.0272</v>
+        <v>30.168</v>
       </c>
     </row>
     <row r="241">
@@ -12127,10 +12127,10 @@
         <v>1.37</v>
       </c>
       <c r="I241" t="n">
-        <v>1.0022</v>
+        <v>0.9355</v>
       </c>
       <c r="J241" t="n">
-        <v>24.0528</v>
+        <v>22.452</v>
       </c>
     </row>
     <row r="242">
@@ -12167,10 +12167,10 @@
         <v>1.11</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2743</v>
+        <v>0.2774</v>
       </c>
       <c r="J242" t="n">
-        <v>7.6804</v>
+        <v>7.7672</v>
       </c>
     </row>
     <row r="243">
@@ -12207,10 +12207,10 @@
         <v>1.03</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0973</v>
+        <v>0.1039</v>
       </c>
       <c r="J243" t="n">
-        <v>2.7244</v>
+        <v>2.9092</v>
       </c>
     </row>
     <row r="244">
@@ -12247,10 +12247,10 @@
         <v>0.93</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.1093</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.7216</v>
+        <v>-3.0604</v>
       </c>
     </row>
     <row r="245">
@@ -12287,10 +12287,10 @@
         <v>0.9</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1312</v>
+        <v>-0.1446</v>
       </c>
       <c r="J245" t="n">
-        <v>-3.6736</v>
+        <v>-4.0488</v>
       </c>
     </row>
     <row r="246">
@@ -12327,10 +12327,10 @@
         <v>0.89</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1421</v>
+        <v>-0.1558</v>
       </c>
       <c r="J246" t="n">
-        <v>-3.9788</v>
+        <v>-4.3624</v>
       </c>
     </row>
     <row r="247">
@@ -12367,10 +12367,10 @@
         <v>1.28</v>
       </c>
       <c r="I247" t="n">
-        <v>0.592</v>
+        <v>0.6536</v>
       </c>
       <c r="J247" t="n">
-        <v>16.576</v>
+        <v>18.3008</v>
       </c>
     </row>
     <row r="248">
@@ -12407,10 +12407,10 @@
         <v>1.27</v>
       </c>
       <c r="I248" t="n">
-        <v>0.5779</v>
+        <v>0.638</v>
       </c>
       <c r="J248" t="n">
-        <v>16.1812</v>
+        <v>17.864</v>
       </c>
     </row>
     <row r="249">
@@ -12447,10 +12447,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4626</v>
+        <v>0.5095</v>
       </c>
       <c r="J249" t="n">
-        <v>12.9528</v>
+        <v>14.266</v>
       </c>
     </row>
     <row r="250">
@@ -12487,10 +12487,10 @@
         <v>1.12</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3573</v>
+        <v>0.3718</v>
       </c>
       <c r="J250" t="n">
-        <v>10.0044</v>
+        <v>10.4104</v>
       </c>
     </row>
     <row r="251">
@@ -12527,10 +12527,10 @@
         <v>0.74</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.8074</v>
+        <v>-0.7457</v>
       </c>
       <c r="J251" t="n">
-        <v>-22.6072</v>
+        <v>-20.8796</v>
       </c>
     </row>
     <row r="252">
@@ -12567,10 +12567,10 @@
         <v>1.3</v>
       </c>
       <c r="I252" t="n">
-        <v>0.487</v>
+        <v>0.5432</v>
       </c>
       <c r="J252" t="n">
-        <v>14.61</v>
+        <v>16.296</v>
       </c>
     </row>
     <row r="253">
@@ -12607,10 +12607,10 @@
         <v>1.15</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3257</v>
+        <v>0.3338</v>
       </c>
       <c r="J253" t="n">
-        <v>9.771000000000001</v>
+        <v>10.014</v>
       </c>
     </row>
     <row r="254">
@@ -12647,10 +12647,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0281</v>
+        <v>0.0366</v>
       </c>
       <c r="J254" t="n">
-        <v>0.843</v>
+        <v>1.098</v>
       </c>
     </row>
     <row r="255">
@@ -12687,10 +12687,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0953</v>
+        <v>-0.1045</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.859</v>
+        <v>-3.135</v>
       </c>
     </row>
     <row r="256">
@@ -12727,10 +12727,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.0953</v>
+        <v>-0.1045</v>
       </c>
       <c r="J256" t="n">
-        <v>-2.859</v>
+        <v>-3.135</v>
       </c>
     </row>
     <row r="257">
@@ -12767,10 +12767,10 @@
         <v>1.46</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8909</v>
+        <v>0.9677</v>
       </c>
       <c r="J257" t="n">
-        <v>26.727</v>
+        <v>29.031</v>
       </c>
     </row>
     <row r="258">
@@ -12807,10 +12807,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.5122</v>
+        <v>0.5566</v>
       </c>
       <c r="J258" t="n">
-        <v>15.366</v>
+        <v>16.698</v>
       </c>
     </row>
     <row r="259">
@@ -12847,10 +12847,10 @@
         <v>1.03</v>
       </c>
       <c r="I259" t="n">
-        <v>0.139</v>
+        <v>0.1416</v>
       </c>
       <c r="J259" t="n">
-        <v>4.17</v>
+        <v>4.248</v>
       </c>
     </row>
     <row r="260">
@@ -12887,10 +12887,10 @@
         <v>0.63</v>
       </c>
       <c r="I260" t="n">
-        <v>-1.0348</v>
+        <v>-0.9496</v>
       </c>
       <c r="J260" t="n">
-        <v>-31.044</v>
+        <v>-28.488</v>
       </c>
     </row>
     <row r="261">
@@ -12927,10 +12927,10 @@
         <v>0.52</v>
       </c>
       <c r="I261" t="n">
-        <v>-1.2953</v>
+        <v>-1.172</v>
       </c>
       <c r="J261" t="n">
-        <v>-38.859</v>
+        <v>-35.16</v>
       </c>
     </row>
     <row r="262">
@@ -12967,10 +12967,10 @@
         <v>1.02</v>
       </c>
       <c r="I262" t="n">
-        <v>0.1268</v>
+        <v>0.1146</v>
       </c>
       <c r="J262" t="n">
-        <v>2.6628</v>
+        <v>2.4066</v>
       </c>
     </row>
     <row r="263">
@@ -13007,10 +13007,10 @@
         <v>0.84</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1636</v>
+        <v>-0.1852</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.4356</v>
+        <v>-3.8892</v>
       </c>
     </row>
     <row r="264">
@@ -13047,10 +13047,10 @@
         <v>0.77</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2359</v>
+        <v>-0.2564</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.9539</v>
+        <v>-5.3844</v>
       </c>
     </row>
     <row r="265">
@@ -13087,10 +13087,10 @@
         <v>0.52</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4685</v>
+        <v>-0.48</v>
       </c>
       <c r="J265" t="n">
-        <v>-9.8385</v>
+        <v>-10.08</v>
       </c>
     </row>
     <row r="266">
@@ -13127,10 +13127,10 @@
         <v>0.49</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4965</v>
+        <v>-0.5062</v>
       </c>
       <c r="J266" t="n">
-        <v>-10.4265</v>
+        <v>-10.6302</v>
       </c>
     </row>
     <row r="267">
@@ -13167,10 +13167,10 @@
         <v>1.66</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5853</v>
+        <v>0.6744</v>
       </c>
       <c r="J267" t="n">
-        <v>12.2913</v>
+        <v>14.1624</v>
       </c>
     </row>
     <row r="268">
@@ -13207,10 +13207,10 @@
         <v>1.61</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5553</v>
+        <v>0.6394</v>
       </c>
       <c r="J268" t="n">
-        <v>11.6613</v>
+        <v>13.4274</v>
       </c>
     </row>
     <row r="269">
@@ -13247,10 +13247,10 @@
         <v>1.36</v>
       </c>
       <c r="I269" t="n">
-        <v>0.4018</v>
+        <v>0.4572</v>
       </c>
       <c r="J269" t="n">
-        <v>8.437799999999999</v>
+        <v>9.6012</v>
       </c>
     </row>
     <row r="270">
@@ -13287,10 +13287,10 @@
         <v>1.2</v>
       </c>
       <c r="I270" t="n">
-        <v>0.2652</v>
+        <v>0.2867</v>
       </c>
       <c r="J270" t="n">
-        <v>5.5692</v>
+        <v>6.0207</v>
       </c>
     </row>
     <row r="271">
@@ -13327,10 +13327,10 @@
         <v>1</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.0337</v>
+        <v>-0.0262</v>
       </c>
       <c r="J271" t="n">
-        <v>-0.7077</v>
+        <v>-0.5502</v>
       </c>
     </row>
     <row r="272">
@@ -13367,10 +13367,10 @@
         <v>1.54</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9857</v>
+        <v>1.0711</v>
       </c>
       <c r="J272" t="n">
-        <v>35.4852</v>
+        <v>38.5596</v>
       </c>
     </row>
     <row r="273">
@@ -13407,10 +13407,10 @@
         <v>1.13</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3923</v>
+        <v>0.4179</v>
       </c>
       <c r="J273" t="n">
-        <v>14.1228</v>
+        <v>15.0444</v>
       </c>
     </row>
     <row r="274">
@@ -13447,10 +13447,10 @@
         <v>0.93</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2605</v>
+        <v>-0.2599</v>
       </c>
       <c r="J274" t="n">
-        <v>-9.378</v>
+        <v>-9.356400000000001</v>
       </c>
     </row>
     <row r="275">
@@ -13487,10 +13487,10 @@
         <v>0.77</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.699</v>
+        <v>-0.6562</v>
       </c>
       <c r="J275" t="n">
-        <v>-25.164</v>
+        <v>-23.6232</v>
       </c>
     </row>
     <row r="276">
@@ -13527,10 +13527,10 @@
         <v>0.64</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.0204</v>
+        <v>-0.9358</v>
       </c>
       <c r="J276" t="n">
-        <v>-36.7344</v>
+        <v>-33.6888</v>
       </c>
     </row>
     <row r="277">
@@ -13567,10 +13567,10 @@
         <v>1.36</v>
       </c>
       <c r="I277" t="n">
-        <v>0.544</v>
+        <v>0.6087</v>
       </c>
       <c r="J277" t="n">
-        <v>19.584</v>
+        <v>21.9132</v>
       </c>
     </row>
     <row r="278">
@@ -13607,10 +13607,10 @@
         <v>1.29</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4748</v>
+        <v>0.5298</v>
       </c>
       <c r="J278" t="n">
-        <v>17.0928</v>
+        <v>19.0728</v>
       </c>
     </row>
     <row r="279">
@@ -13647,10 +13647,10 @@
         <v>1.1</v>
       </c>
       <c r="I279" t="n">
-        <v>0.2304</v>
+        <v>0.241</v>
       </c>
       <c r="J279" t="n">
-        <v>8.2944</v>
+        <v>8.676</v>
       </c>
     </row>
     <row r="280">
@@ -13687,10 +13687,10 @@
         <v>0.86</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1864</v>
+        <v>-0.1979</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.7104</v>
+        <v>-7.1244</v>
       </c>
     </row>
     <row r="281">
@@ -13727,10 +13727,10 @@
         <v>0.79</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2579</v>
+        <v>-0.2693</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.2844</v>
+        <v>-9.694800000000001</v>
       </c>
     </row>
     <row r="282">
@@ -13767,10 +13767,10 @@
         <v>1.78</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1949</v>
+        <v>1.3076</v>
       </c>
       <c r="J282" t="n">
-        <v>32.2623</v>
+        <v>35.3052</v>
       </c>
     </row>
     <row r="283">
@@ -13807,10 +13807,10 @@
         <v>1.52</v>
       </c>
       <c r="I283" t="n">
-        <v>0.8772</v>
+        <v>0.9701</v>
       </c>
       <c r="J283" t="n">
-        <v>23.6844</v>
+        <v>26.1927</v>
       </c>
     </row>
     <row r="284">
@@ -13847,10 +13847,10 @@
         <v>1.19</v>
       </c>
       <c r="I284" t="n">
-        <v>0.4456</v>
+        <v>0.4949</v>
       </c>
       <c r="J284" t="n">
-        <v>12.0312</v>
+        <v>13.3623</v>
       </c>
     </row>
     <row r="285">
@@ -13887,10 +13887,10 @@
         <v>1.01</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.0108</v>
+        <v>0.0143</v>
       </c>
       <c r="J285" t="n">
-        <v>-0.2916</v>
+        <v>0.3861</v>
       </c>
     </row>
     <row r="286">
@@ -13927,10 +13927,10 @@
         <v>0.85</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5596</v>
+        <v>-0.5188</v>
       </c>
       <c r="J286" t="n">
-        <v>-15.1092</v>
+        <v>-14.0076</v>
       </c>
     </row>
     <row r="287">
@@ -13967,10 +13967,10 @@
         <v>1.1</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3012</v>
+        <v>0.2927</v>
       </c>
       <c r="J287" t="n">
-        <v>8.132400000000001</v>
+        <v>7.9029</v>
       </c>
     </row>
     <row r="288">
@@ -14007,10 +14007,10 @@
         <v>1</v>
       </c>
       <c r="I288" t="n">
-        <v>0.0398</v>
+        <v>0.0288</v>
       </c>
       <c r="J288" t="n">
-        <v>1.0746</v>
+        <v>0.7776</v>
       </c>
     </row>
     <row r="289">
@@ -14047,10 +14047,10 @@
         <v>0.83</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1903</v>
+        <v>-0.2081</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.1381</v>
+        <v>-5.6187</v>
       </c>
     </row>
     <row r="290">
@@ -14087,10 +14087,10 @@
         <v>0.73</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2877</v>
+        <v>-0.3043</v>
       </c>
       <c r="J290" t="n">
-        <v>-7.7679</v>
+        <v>-8.216100000000001</v>
       </c>
     </row>
     <row r="291">
@@ -14127,10 +14127,10 @@
         <v>0.55</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4569</v>
+        <v>-0.4665</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.3363</v>
+        <v>-12.5955</v>
       </c>
     </row>
     <row r="292">
@@ -14167,10 +14167,10 @@
         <v>0.96</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.0408</v>
+        <v>-0.0552</v>
       </c>
       <c r="J292" t="n">
-        <v>-1.224</v>
+        <v>-1.656</v>
       </c>
     </row>
     <row r="293">
@@ -14207,10 +14207,10 @@
         <v>0.95</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.0541</v>
+        <v>-0.0693</v>
       </c>
       <c r="J293" t="n">
-        <v>-1.623</v>
+        <v>-2.079</v>
       </c>
     </row>
     <row r="294">
@@ -14247,10 +14247,10 @@
         <v>0.85</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1687</v>
+        <v>-0.1867</v>
       </c>
       <c r="J294" t="n">
-        <v>-5.061</v>
+        <v>-5.601</v>
       </c>
     </row>
     <row r="295">
@@ -14287,10 +14287,10 @@
         <v>0.68</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3324</v>
+        <v>-0.3481</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.972</v>
+        <v>-10.443</v>
       </c>
     </row>
     <row r="296">
@@ -14327,10 +14327,10 @@
         <v>0.66</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3513</v>
+        <v>-0.3663</v>
       </c>
       <c r="J296" t="n">
-        <v>-10.539</v>
+        <v>-10.989</v>
       </c>
     </row>
     <row r="297">
@@ -14367,10 +14367,10 @@
         <v>0.75</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.2794</v>
+        <v>-0.294</v>
       </c>
       <c r="J297" t="n">
-        <v>-8.382</v>
+        <v>-8.82</v>
       </c>
     </row>
     <row r="298">
@@ -14407,10 +14407,10 @@
         <v>1.32</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4244</v>
+        <v>0.473</v>
       </c>
       <c r="J298" t="n">
-        <v>12.732</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="299">
@@ -14447,10 +14447,10 @@
         <v>1.1</v>
       </c>
       <c r="I299" t="n">
-        <v>0.1908</v>
+        <v>0.1993</v>
       </c>
       <c r="J299" t="n">
-        <v>5.724</v>
+        <v>5.979</v>
       </c>
     </row>
     <row r="300">
@@ -14487,10 +14487,10 @@
         <v>0.74</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2891</v>
+        <v>-0.3034</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.673</v>
+        <v>-9.102</v>
       </c>
     </row>
     <row r="301">
@@ -14527,10 +14527,10 @@
         <v>0.72</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3084</v>
+        <v>-0.3222</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.252000000000001</v>
+        <v>-9.666</v>
       </c>
     </row>
     <row r="302">
@@ -14567,10 +14567,10 @@
         <v>0.85</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.4565</v>
+        <v>-0.4467</v>
       </c>
       <c r="J302" t="n">
-        <v>-12.782</v>
+        <v>-12.5076</v>
       </c>
     </row>
     <row r="303">
@@ -14607,10 +14607,10 @@
         <v>1.13</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4224</v>
+        <v>0.4492</v>
       </c>
       <c r="J303" t="n">
-        <v>11.8272</v>
+        <v>12.5776</v>
       </c>
     </row>
     <row r="304">
@@ -14647,10 +14647,10 @@
         <v>0.9</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3222</v>
+        <v>-0.3237</v>
       </c>
       <c r="J304" t="n">
-        <v>-9.021599999999999</v>
+        <v>-9.063599999999999</v>
       </c>
     </row>
     <row r="305">
@@ -14687,10 +14687,10 @@
         <v>0.86</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4298</v>
+        <v>-0.4226</v>
       </c>
       <c r="J305" t="n">
-        <v>-12.0344</v>
+        <v>-11.8328</v>
       </c>
     </row>
     <row r="306">
@@ -14727,10 +14727,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.7657</v>
+        <v>-0.7206</v>
       </c>
       <c r="J306" t="n">
-        <v>-21.4396</v>
+        <v>-20.1768</v>
       </c>
     </row>
     <row r="307">
@@ -14767,10 +14767,10 @@
         <v>0.82</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.2026</v>
+        <v>-0.2198</v>
       </c>
       <c r="J307" t="n">
-        <v>-5.6728</v>
+        <v>-6.1544</v>
       </c>
     </row>
     <row r="308">
@@ -14807,10 +14807,10 @@
         <v>1.2</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4283</v>
+        <v>0.4648</v>
       </c>
       <c r="J308" t="n">
-        <v>11.9924</v>
+        <v>13.0144</v>
       </c>
     </row>
     <row r="309">
@@ -14847,10 +14847,10 @@
         <v>0.83</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1926</v>
+        <v>-0.2098</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.3928</v>
+        <v>-5.8744</v>
       </c>
     </row>
     <row r="310">
@@ -14887,10 +14887,10 @@
         <v>0.82</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2026</v>
+        <v>-0.2198</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.6728</v>
+        <v>-6.1544</v>
       </c>
     </row>
     <row r="311">
@@ -14927,10 +14927,10 @@
         <v>0.65</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3668</v>
+        <v>-0.3801</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.2704</v>
+        <v>-10.6428</v>
       </c>
     </row>
     <row r="312">
@@ -14967,10 +14967,10 @@
         <v>0.71</v>
       </c>
       <c r="I312" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.7129</v>
       </c>
       <c r="J312" t="n">
-        <v>-22.242</v>
+        <v>-21.387</v>
       </c>
     </row>
     <row r="313">
@@ -15007,10 +15007,10 @@
         <v>0.92</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1438</v>
+        <v>-0.1858</v>
       </c>
       <c r="J313" t="n">
-        <v>-4.314</v>
+        <v>-5.574</v>
       </c>
     </row>
     <row r="314">
@@ -15047,10 +15047,10 @@
         <v>0.61</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.977</v>
+        <v>-0.9166</v>
       </c>
       <c r="J314" t="n">
-        <v>-29.31</v>
+        <v>-27.498</v>
       </c>
     </row>
     <row r="315">
@@ -15087,10 +15087,10 @@
         <v>0.58</v>
       </c>
       <c r="I315" t="n">
-        <v>-1.0495</v>
+        <v>-0.9782999999999999</v>
       </c>
       <c r="J315" t="n">
-        <v>-31.485</v>
+        <v>-29.349</v>
       </c>
     </row>
     <row r="316">
@@ -15127,10 +15127,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I316" t="n">
-        <v>-1.0981</v>
+        <v>-1.0194</v>
       </c>
       <c r="J316" t="n">
-        <v>-32.943</v>
+        <v>-30.582</v>
       </c>
     </row>
     <row r="317">
@@ -15167,10 +15167,10 @@
         <v>0.89</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.1395</v>
+        <v>-0.1538</v>
       </c>
       <c r="J317" t="n">
-        <v>-4.185</v>
+        <v>-4.614</v>
       </c>
     </row>
     <row r="318">
@@ -15207,10 +15207,10 @@
         <v>1.19</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3954</v>
+        <v>0.4279</v>
       </c>
       <c r="J318" t="n">
-        <v>11.862</v>
+        <v>12.837</v>
       </c>
     </row>
     <row r="319">
@@ -15247,10 +15247,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0833</v>
+        <v>-0.0954</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.499</v>
+        <v>-2.862</v>
       </c>
     </row>
     <row r="320">
@@ -15287,10 +15287,10 @@
         <v>0.89</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1395</v>
+        <v>-0.1538</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.185</v>
+        <v>-4.614</v>
       </c>
     </row>
     <row r="321">
@@ -15327,10 +15327,10 @@
         <v>0.83</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2025</v>
+        <v>-0.2174</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.075</v>
+        <v>-6.522</v>
       </c>
     </row>
     <row r="322">
@@ -15367,10 +15367,10 @@
         <v>1.04</v>
       </c>
       <c r="I322" t="n">
-        <v>0.1332</v>
+        <v>0.1475</v>
       </c>
       <c r="J322" t="n">
-        <v>3.0636</v>
+        <v>3.3925</v>
       </c>
     </row>
     <row r="323">
@@ -15407,10 +15407,10 @@
         <v>0.63</v>
       </c>
       <c r="I323" t="n">
-        <v>-1.0795</v>
+        <v>-0.9813</v>
       </c>
       <c r="J323" t="n">
-        <v>-24.8285</v>
+        <v>-22.5699</v>
       </c>
     </row>
     <row r="324">
@@ -15447,10 +15447,10 @@
         <v>0.53</v>
       </c>
       <c r="I324" t="n">
-        <v>-1.3116</v>
+        <v>-1.1802</v>
       </c>
       <c r="J324" t="n">
-        <v>-30.1668</v>
+        <v>-27.1446</v>
       </c>
     </row>
     <row r="325">
@@ -15487,10 +15487,10 @@
         <v>1.94</v>
       </c>
       <c r="I325" t="n">
-        <v>1.4336</v>
+        <v>1.5499</v>
       </c>
       <c r="J325" t="n">
-        <v>32.9728</v>
+        <v>35.6477</v>
       </c>
     </row>
     <row r="326">
@@ -15527,10 +15527,10 @@
         <v>1.58</v>
       </c>
       <c r="I326" t="n">
-        <v>0.9857</v>
+        <v>1.0801</v>
       </c>
       <c r="J326" t="n">
-        <v>22.6711</v>
+        <v>24.8423</v>
       </c>
     </row>
     <row r="327">
@@ -15567,10 +15567,10 @@
         <v>1.74</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8658</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="J327" t="n">
-        <v>19.9134</v>
+        <v>22.3629</v>
       </c>
     </row>
     <row r="328">
@@ -15607,10 +15607,10 @@
         <v>1.29</v>
       </c>
       <c r="I328" t="n">
-        <v>0.4581</v>
+        <v>0.5145</v>
       </c>
       <c r="J328" t="n">
-        <v>10.5363</v>
+        <v>11.8335</v>
       </c>
     </row>
     <row r="329">
@@ -15647,10 +15647,10 @@
         <v>0.98</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0555</v>
+        <v>-0.0578</v>
       </c>
       <c r="J329" t="n">
-        <v>-1.2765</v>
+        <v>-1.3294</v>
       </c>
     </row>
     <row r="330">
@@ -15687,10 +15687,10 @@
         <v>1</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.0185</v>
+        <v>-0.0143</v>
       </c>
       <c r="J330" t="n">
-        <v>-0.4255</v>
+        <v>-0.3289</v>
       </c>
     </row>
     <row r="331">
@@ -15727,10 +15727,10 @@
         <v>0.98</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.0555</v>
+        <v>-0.0578</v>
       </c>
       <c r="J331" t="n">
-        <v>-1.2765</v>
+        <v>-1.3294</v>
       </c>
     </row>
     <row r="332">
@@ -15767,10 +15767,10 @@
         <v>0.98</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.1235</v>
+        <v>-0.1201</v>
       </c>
       <c r="J332" t="n">
-        <v>-2.964</v>
+        <v>-2.8824</v>
       </c>
     </row>
     <row r="333">
@@ -15807,10 +15807,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I333" t="n">
-        <v>-1.2374</v>
+        <v>-1.1176</v>
       </c>
       <c r="J333" t="n">
-        <v>-29.6976</v>
+        <v>-26.8224</v>
       </c>
     </row>
     <row r="334">
@@ -15847,10 +15847,10 @@
         <v>0.54</v>
       </c>
       <c r="I334" t="n">
-        <v>-1.2835</v>
+        <v>-1.157</v>
       </c>
       <c r="J334" t="n">
-        <v>-30.804</v>
+        <v>-27.768</v>
       </c>
     </row>
     <row r="335">
@@ -15887,10 +15887,10 @@
         <v>1.87</v>
       </c>
       <c r="I335" t="n">
-        <v>1.3595</v>
+        <v>1.4712</v>
       </c>
       <c r="J335" t="n">
-        <v>32.628</v>
+        <v>35.3088</v>
       </c>
     </row>
     <row r="336">
@@ -15927,10 +15927,10 @@
         <v>1.64</v>
       </c>
       <c r="I336" t="n">
-        <v>1.0711</v>
+        <v>1.169</v>
       </c>
       <c r="J336" t="n">
-        <v>25.7064</v>
+        <v>28.056</v>
       </c>
     </row>
     <row r="337">
@@ -15967,10 +15967,10 @@
         <v>1.32</v>
       </c>
       <c r="I337" t="n">
-        <v>0.4991</v>
+        <v>0.5588</v>
       </c>
       <c r="J337" t="n">
-        <v>11.9784</v>
+        <v>13.4112</v>
       </c>
     </row>
     <row r="338">
@@ -16007,10 +16007,10 @@
         <v>1.29</v>
       </c>
       <c r="I338" t="n">
-        <v>0.4696</v>
+        <v>0.525</v>
       </c>
       <c r="J338" t="n">
-        <v>11.2704</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="339">
@@ -16047,10 +16047,10 @@
         <v>1.16</v>
       </c>
       <c r="I339" t="n">
-        <v>0.3336</v>
+        <v>0.3451</v>
       </c>
       <c r="J339" t="n">
-        <v>8.006399999999999</v>
+        <v>8.282400000000001</v>
       </c>
     </row>
     <row r="340">
@@ -16087,10 +16087,10 @@
         <v>0.91</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.1352</v>
+        <v>-0.1448</v>
       </c>
       <c r="J340" t="n">
-        <v>-3.2448</v>
+        <v>-3.4752</v>
       </c>
     </row>
     <row r="341">
@@ -16127,10 +16127,10 @@
         <v>0.88</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.1684</v>
+        <v>-0.1789</v>
       </c>
       <c r="J341" t="n">
-        <v>-4.0416</v>
+        <v>-4.2936</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5209/event_5209_evp_summary.xlsx
+++ b/database/event/5209/event_5209_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.666700000000001</v>
+        <v>8.605499999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4296</v>
+        <v>3.4054</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3211</v>
+        <v>3.3144</v>
       </c>
       <c r="E2" t="n">
-        <v>8.666700000000001</v>
+        <v>8.605499999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7904</v>
+        <v>2.7943</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8763</v>
+        <v>5.8111</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3823</v>
+        <v>3.4537</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5589</v>
+        <v>3.6407</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8763</v>
+        <v>5.8111</v>
       </c>
       <c r="K2" t="n">
         <v>78</v>
@@ -529,7 +529,7 @@
         <v>218</v>
       </c>
       <c r="M2" t="n">
-        <v>9.4352</v>
+        <v>9.451799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>296</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.1864</v>
+        <v>3.9656</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6566</v>
+        <v>1.5693</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2815</v>
+        <v>1.2007</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1864</v>
+        <v>3.9656</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5833</v>
+        <v>2.5208</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6031</v>
+        <v>1.4448</v>
       </c>
       <c r="H3" t="n">
-        <v>2.929</v>
+        <v>2.8268</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0819</v>
+        <v>2.9799</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6031</v>
+        <v>1.4448</v>
       </c>
       <c r="K3" t="n">
         <v>116</v>
@@ -575,7 +575,7 @@
         <v>197</v>
       </c>
       <c r="M3" t="n">
-        <v>4.685</v>
+        <v>4.424700000000001</v>
       </c>
       <c r="N3" t="n">
         <v>313</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.7004</v>
+        <v>3.6305</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4643</v>
+        <v>1.4367</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0603</v>
+        <v>1.0481</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7004</v>
+        <v>3.6305</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9683</v>
+        <v>0.9732</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7321</v>
+        <v>2.6573</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9683</v>
+        <v>0.9732</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9683</v>
+        <v>0.9732</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7321</v>
+        <v>2.6573</v>
       </c>
       <c r="K4" t="n">
         <v>50</v>
@@ -621,7 +621,7 @@
         <v>206</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7004</v>
+        <v>3.6305</v>
       </c>
       <c r="N4" t="n">
         <v>256</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1358</v>
+        <v>2.9971</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2409</v>
+        <v>1.186</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8033</v>
+        <v>0.7595</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1358</v>
+        <v>2.9971</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5844</v>
+        <v>1.4643</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5514</v>
+        <v>1.5328</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5844</v>
+        <v>1.4643</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5844</v>
+        <v>1.4643</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5514</v>
+        <v>1.5328</v>
       </c>
       <c r="K5" t="n">
         <v>35</v>
@@ -667,7 +667,7 @@
         <v>83</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1358</v>
+        <v>2.9971</v>
       </c>
       <c r="N5" t="n">
         <v>118</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.9511</v>
+        <v>2.9857</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1678</v>
+        <v>1.1815</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7192</v>
+        <v>0.7543</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9511</v>
+        <v>2.9857</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2925</v>
+        <v>-0.2681</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2436</v>
+        <v>3.2538</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2925</v>
+        <v>-0.2681</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3</v>
+        <v>-0.2753</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2436</v>
+        <v>3.2538</v>
       </c>
       <c r="K6" t="n">
         <v>85</v>
@@ -713,7 +713,7 @@
         <v>229</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9436</v>
+        <v>2.9785</v>
       </c>
       <c r="N6" t="n">
         <v>314</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5798</v>
+        <v>2.5204</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0209</v>
+        <v>0.9974</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5502</v>
+        <v>0.5424</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5798</v>
+        <v>2.5204</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4339</v>
+        <v>3.4123</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8541</v>
+        <v>-0.8919</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7907</v>
+        <v>4.8698</v>
       </c>
       <c r="I7" t="n">
-        <v>5.4406</v>
+        <v>5.5562</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8541</v>
+        <v>-0.8919</v>
       </c>
       <c r="K7" t="n">
         <v>151</v>
@@ -759,7 +759,7 @@
         <v>269</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5865</v>
+        <v>4.6643</v>
       </c>
       <c r="N7" t="n">
         <v>420</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5222</v>
+        <v>2.5086</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9981</v>
+        <v>0.9927</v>
       </c>
       <c r="D8" t="n">
-        <v>0.524</v>
+        <v>0.537</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5222</v>
+        <v>2.5086</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0603</v>
+        <v>0.6027</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4619</v>
+        <v>1.9059</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0603</v>
+        <v>0.6027</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1156</v>
+        <v>0.6027</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4619</v>
+        <v>1.9059</v>
       </c>
       <c r="K8" t="n">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5775</v>
+        <v>2.5086</v>
       </c>
       <c r="N8" t="n">
-        <v>166</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4631</v>
+        <v>2.4171</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9747</v>
+        <v>0.9565</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4971</v>
+        <v>0.4953</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4631</v>
+        <v>2.4171</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8504</v>
+        <v>2.825</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3873</v>
+        <v>-0.4079</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5138</v>
+        <v>3.5239</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7925</v>
+        <v>3.8141</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3873</v>
+        <v>-0.4079</v>
       </c>
       <c r="K9" t="n">
         <v>156</v>
@@ -851,7 +851,7 @@
         <v>190</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4052</v>
+        <v>3.4062</v>
       </c>
       <c r="N9" t="n">
         <v>346</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4343</v>
+        <v>2.3515</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9633</v>
+        <v>0.9305</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4839</v>
+        <v>0.4654</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4343</v>
+        <v>2.3515</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1752</v>
+        <v>1.0162</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2591</v>
+        <v>1.3353</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1752</v>
+        <v>1.0162</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1797</v>
+        <v>1.0712</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2591</v>
+        <v>1.3353</v>
       </c>
       <c r="K10" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L10" t="n">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4388</v>
+        <v>2.4065</v>
       </c>
       <c r="N10" t="n">
-        <v>249</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4205</v>
+        <v>2.2674</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9578</v>
+        <v>0.8973</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4777</v>
+        <v>0.4271</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4205</v>
+        <v>2.2674</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6659</v>
+        <v>0.0964</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7546</v>
+        <v>2.1709</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6659</v>
+        <v>0.0964</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6659</v>
+        <v>0.099</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7546</v>
+        <v>2.1709</v>
       </c>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="L11" t="n">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4205</v>
+        <v>2.2699</v>
       </c>
       <c r="N11" t="n">
-        <v>115</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7678</v>
+        <v>1.7635</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6996</v>
+        <v>0.6978</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1805</v>
+        <v>0.1976</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7678</v>
+        <v>1.7635</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8619</v>
+        <v>0.8702</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9059</v>
+        <v>0.8933</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8619</v>
+        <v>0.8702</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9069</v>
+        <v>0.9173</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9059</v>
+        <v>0.8933</v>
       </c>
       <c r="K12" t="n">
         <v>42</v>
@@ -989,7 +989,7 @@
         <v>218</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8128</v>
+        <v>1.8106</v>
       </c>
       <c r="N12" t="n">
         <v>260</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6454</v>
+        <v>1.5346</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6511</v>
+        <v>0.6073</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1248</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6454</v>
+        <v>1.5346</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0261</v>
+        <v>0.3883</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6715</v>
+        <v>1.1463</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0261</v>
+        <v>0.3883</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0275</v>
+        <v>0.4094</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6715</v>
+        <v>1.1463</v>
       </c>
       <c r="K13" t="n">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="L13" t="n">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="M13" t="n">
-        <v>1.644</v>
+        <v>1.5557</v>
       </c>
       <c r="N13" t="n">
-        <v>249</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5588</v>
+        <v>1.5166</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6168</v>
+        <v>0.6001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0854</v>
+        <v>0.0851</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5588</v>
+        <v>1.5166</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4013</v>
+        <v>-0.0961</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1575</v>
+        <v>1.6127</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4013</v>
+        <v>-0.0961</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4223</v>
+        <v>-0.1013</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1575</v>
+        <v>1.6127</v>
       </c>
       <c r="K14" t="n">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="L14" t="n">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5798</v>
+        <v>1.5114</v>
       </c>
       <c r="N14" t="n">
-        <v>137</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3747</v>
+        <v>1.3373</v>
       </c>
       <c r="C15" t="n">
-        <v>0.544</v>
+        <v>0.5292</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0016</v>
+        <v>0.0034</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3747</v>
+        <v>1.3373</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2968</v>
+        <v>1.2815</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0779</v>
+        <v>0.0558</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2968</v>
+        <v>1.2815</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3645</v>
+        <v>1.3509</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0779</v>
+        <v>0.0558</v>
       </c>
       <c r="K15" t="n">
         <v>82</v>
@@ -1127,7 +1127,7 @@
         <v>135</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4424</v>
+        <v>1.4067</v>
       </c>
       <c r="N15" t="n">
         <v>217</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3567</v>
+        <v>1.2579</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5369</v>
+        <v>0.4978</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0066</v>
+        <v>-0.0328</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3567</v>
+        <v>1.2579</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7199</v>
+        <v>1.6106</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3632</v>
+        <v>-0.3527</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7199</v>
+        <v>1.6106</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7642</v>
+        <v>1.6536</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3632</v>
+        <v>-0.3527</v>
       </c>
       <c r="K16" t="n">
         <v>94</v>
@@ -1173,7 +1173,7 @@
         <v>195</v>
       </c>
       <c r="M16" t="n">
-        <v>1.401</v>
+        <v>1.3009</v>
       </c>
       <c r="N16" t="n">
         <v>289</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2673</v>
+        <v>1.1002</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4354</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0473</v>
+        <v>-0.1046</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2673</v>
+        <v>1.1002</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8334</v>
+        <v>0.6798</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4339</v>
+        <v>0.4204</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8334</v>
+        <v>0.6798</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8549</v>
+        <v>0.6979</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4339</v>
+        <v>0.4204</v>
       </c>
       <c r="K17" t="n">
         <v>82</v>
@@ -1219,7 +1219,7 @@
         <v>58</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2888</v>
+        <v>1.1183</v>
       </c>
       <c r="N17" t="n">
         <v>140</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1273</v>
+        <v>0.9595</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4461</v>
+        <v>0.3797</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.111</v>
+        <v>-0.1687</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1273</v>
+        <v>0.9595</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1279</v>
+        <v>0.9699</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0104</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1279</v>
+        <v>0.9699</v>
       </c>
       <c r="I18" t="n">
-        <v>1.157</v>
+        <v>0.9958</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0104</v>
       </c>
       <c r="K18" t="n">
         <v>82</v>
@@ -1265,7 +1265,7 @@
         <v>58</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1564</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>140</v>
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.955</v>
+        <v>0.9286</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3779</v>
+        <v>0.3675</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1895</v>
+        <v>-0.1828</v>
       </c>
       <c r="E19" t="n">
-        <v>0.955</v>
+        <v>0.9286</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.955</v>
+        <v>0.9286</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.955</v>
+        <v>0.9286</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>230</v>
       </c>
       <c r="M19" t="n">
-        <v>0.955</v>
+        <v>0.9286</v>
       </c>
       <c r="N19" t="n">
         <v>230</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4435</v>
+        <v>0.3699</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1755</v>
+        <v>0.1464</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4223</v>
+        <v>-0.4373</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4435</v>
+        <v>0.3699</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4435</v>
+        <v>0.3699</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4435</v>
+        <v>0.3699</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4435</v>
+        <v>0.3699</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4435</v>
+        <v>0.3699</v>
       </c>
       <c r="N20" t="n">
         <v>97</v>
@@ -1366,139 +1366,139 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4245</v>
+        <v>0.3599</v>
       </c>
       <c r="C21" t="n">
-        <v>0.168</v>
+        <v>0.1424</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.431</v>
+        <v>-0.4418</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4245</v>
+        <v>0.3599</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2353</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1892</v>
+        <v>0.3599</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2353</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2414</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1892</v>
+        <v>0.3599</v>
       </c>
       <c r="K21" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4306</v>
+        <v>0.3599</v>
       </c>
       <c r="N21" t="n">
-        <v>140</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.378</v>
+        <v>0.3058</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1496</v>
+        <v>0.121</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4521</v>
+        <v>-0.4665</v>
       </c>
       <c r="E22" t="n">
-        <v>0.378</v>
+        <v>0.3058</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.1501</v>
       </c>
       <c r="G22" t="n">
-        <v>0.378</v>
+        <v>0.1557</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.1501</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.1541</v>
       </c>
       <c r="J22" t="n">
-        <v>0.378</v>
+        <v>0.1557</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="L22" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M22" t="n">
-        <v>0.378</v>
+        <v>0.3098</v>
       </c>
       <c r="N22" t="n">
-        <v>57</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2071</v>
+        <v>0.1382</v>
       </c>
       <c r="C23" t="n">
-        <v>0.082</v>
+        <v>0.0547</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5299</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2071</v>
+        <v>0.1382</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.3422</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2071</v>
+        <v>-0.204</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.3422</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.3422</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2071</v>
+        <v>-0.204</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L23" t="n">
-        <v>230</v>
+        <v>47</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2071</v>
+        <v>0.1382</v>
       </c>
       <c r="N23" t="n">
-        <v>230</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1957</v>
+        <v>0.1289</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0774</v>
+        <v>0.051</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5351</v>
+        <v>-0.5471</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1957</v>
+        <v>0.1289</v>
       </c>
       <c r="F24" t="n">
-        <v>0.777</v>
+        <v>0.7451</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5813</v>
+        <v>-0.6162</v>
       </c>
       <c r="H24" t="n">
-        <v>0.777</v>
+        <v>0.7451</v>
       </c>
       <c r="I24" t="n">
-        <v>0.797</v>
+        <v>0.765</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5813</v>
+        <v>-0.6162</v>
       </c>
       <c r="K24" t="n">
         <v>121</v>
@@ -1541,7 +1541,7 @@
         <v>239</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2157</v>
+        <v>0.1488</v>
       </c>
       <c r="N24" t="n">
         <v>360</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1722</v>
+        <v>0.0988</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0391</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5458</v>
+        <v>-0.5608</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1722</v>
+        <v>0.0988</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5685</v>
+        <v>0.4845</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3963</v>
+        <v>-0.3857</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5685</v>
+        <v>0.4845</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5831</v>
+        <v>0.4975</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3963</v>
+        <v>-0.3857</v>
       </c>
       <c r="K25" t="n">
         <v>102</v>
@@ -1587,7 +1587,7 @@
         <v>145</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1868</v>
+        <v>0.1118</v>
       </c>
       <c r="N25" t="n">
         <v>247</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1458</v>
+        <v>0.0963</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0577</v>
+        <v>0.0381</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5578</v>
+        <v>-0.5619</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1458</v>
+        <v>0.0963</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3825</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2367</v>
+        <v>0.0963</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3825</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3825</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2367</v>
+        <v>0.0963</v>
       </c>
       <c r="K26" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1458</v>
+        <v>0.0963</v>
       </c>
       <c r="N26" t="n">
-        <v>92</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27">
@@ -1646,22 +1646,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.144</v>
+        <v>-0.0205</v>
       </c>
       <c r="C27" t="n">
-        <v>0.057</v>
+        <v>-0.0081</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5587</v>
+        <v>-0.6151</v>
       </c>
       <c r="E27" t="n">
-        <v>0.144</v>
+        <v>-0.0205</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.144</v>
+        <v>-0.0205</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.144</v>
+        <v>-0.0205</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>230</v>
       </c>
       <c r="M27" t="n">
-        <v>0.144</v>
+        <v>-0.0205</v>
       </c>
       <c r="N27" t="n">
         <v>230</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0109</v>
+        <v>-0.0601</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0043</v>
+        <v>-0.0238</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6292</v>
+        <v>-0.6332</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0109</v>
+        <v>-0.0601</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1838</v>
+        <v>-0.2006</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1729</v>
+        <v>0.1405</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1838</v>
+        <v>-0.2006</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1885</v>
+        <v>-0.206</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1729</v>
+        <v>0.1405</v>
       </c>
       <c r="K28" t="n">
         <v>82</v>
@@ -1725,7 +1725,7 @@
         <v>58</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0156</v>
+        <v>-0.06549999999999997</v>
       </c>
       <c r="N28" t="n">
         <v>140</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5028</v>
+        <v>-0.4836</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.199</v>
+        <v>-0.1914</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8531</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5028</v>
+        <v>-0.4836</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.7621</v>
       </c>
       <c r="G29" t="n">
-        <v>0.285</v>
+        <v>0.2785</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.7621</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.8081</v>
+        <v>-0.7825</v>
       </c>
       <c r="J29" t="n">
-        <v>0.285</v>
+        <v>0.2785</v>
       </c>
       <c r="K29" t="n">
         <v>27</v>
@@ -1771,7 +1771,7 @@
         <v>155</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5231000000000001</v>
+        <v>-0.504</v>
       </c>
       <c r="N29" t="n">
         <v>182</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6005</v>
+        <v>-0.582</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2376</v>
+        <v>-0.2303</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8976</v>
+        <v>-0.8709</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6005</v>
+        <v>-0.582</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5948</v>
+        <v>0.5968</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.1953</v>
+        <v>-1.1788</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5948</v>
+        <v>0.5968</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6259</v>
+        <v>0.6291</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.1953</v>
+        <v>-1.1788</v>
       </c>
       <c r="K30" t="n">
         <v>82</v>
@@ -1817,7 +1817,7 @@
         <v>162</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5694</v>
+        <v>-0.5497000000000001</v>
       </c>
       <c r="N30" t="n">
         <v>244</v>
@@ -1826,231 +1826,231 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7447</v>
+        <v>-0.7956</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2947</v>
+        <v>-0.3148</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7447</v>
+        <v>-0.7956</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.4334</v>
+        <v>-0.779</v>
       </c>
       <c r="G31" t="n">
-        <v>1.6887</v>
+        <v>-0.0166</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.4334</v>
+        <v>-0.779</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.6264</v>
+        <v>-0.8212</v>
       </c>
       <c r="J31" t="n">
-        <v>1.6887</v>
+        <v>-0.0166</v>
       </c>
       <c r="K31" t="n">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="L31" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.9376999999999998</v>
+        <v>-0.8378</v>
       </c>
       <c r="N31" t="n">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.792</v>
+        <v>-0.8643</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3134</v>
+        <v>-0.342</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9847</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.792</v>
+        <v>-0.8643</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8552</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.06320000000000001</v>
+        <v>-0.8643</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8552</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8998</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.06320000000000001</v>
+        <v>-0.8643</v>
       </c>
       <c r="K32" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>159</v>
+        <v>230</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8366</v>
+        <v>-0.8643</v>
       </c>
       <c r="N32" t="n">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8072</v>
+        <v>-0.8888</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3194</v>
+        <v>-0.3517</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9917</v>
+        <v>-1.0107</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8072</v>
+        <v>-0.8888</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4714</v>
+        <v>-0.7783</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.2786</v>
+        <v>-0.1105</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4714</v>
+        <v>-0.7783</v>
       </c>
       <c r="I33" t="n">
-        <v>0.496</v>
+        <v>-0.7991</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.2786</v>
+        <v>-0.1105</v>
       </c>
       <c r="K33" t="n">
         <v>82</v>
       </c>
       <c r="L33" t="n">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7826</v>
+        <v>-0.9096000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>217</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9485</v>
+        <v>-0.9086</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3753</v>
+        <v>-0.3595</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.056</v>
+        <v>-1.0197</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9485</v>
+        <v>-0.9086</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8293</v>
+        <v>0.4016</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.1192</v>
+        <v>-1.3102</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8293</v>
+        <v>0.4016</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8507</v>
+        <v>0.4234</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.1192</v>
+        <v>-1.3102</v>
       </c>
       <c r="K34" t="n">
         <v>82</v>
       </c>
       <c r="L34" t="n">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9699</v>
+        <v>-0.8868</v>
       </c>
       <c r="N34" t="n">
-        <v>140</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-1.0111</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3756</v>
+        <v>-0.4001</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0563</v>
+        <v>-1.0664</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-1.0111</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-2.6915</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.9491000000000001</v>
+        <v>1.6804</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>-2.6915</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>-2.9131</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9491000000000001</v>
+        <v>1.6804</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L35" t="n">
-        <v>230</v>
+        <v>145</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-1.2327</v>
       </c>
       <c r="N35" t="n">
-        <v>230</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36">
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0892</v>
+        <v>-1.0331</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.431</v>
+        <v>-0.4088</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.12</v>
+        <v>-1.0764</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0892</v>
+        <v>-1.0331</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9718</v>
+        <v>-0.9378</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1174</v>
+        <v>-0.0953</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9718</v>
+        <v>-0.9378</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9968</v>
+        <v>-0.9629</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.1174</v>
+        <v>-0.0953</v>
       </c>
       <c r="K36" t="n">
         <v>45</v>
@@ -2093,7 +2093,7 @@
         <v>71</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1142</v>
+        <v>-1.0582</v>
       </c>
       <c r="N36" t="n">
         <v>116</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1917</v>
+        <v>-1.0988</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4716</v>
+        <v>-0.4348</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1667</v>
+        <v>-1.1063</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1917</v>
+        <v>-1.0988</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1774</v>
+        <v>-1.0871</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0143</v>
+        <v>-0.0117</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1774</v>
+        <v>-1.0871</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2389</v>
+        <v>-1.146</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.0143</v>
+        <v>-0.0117</v>
       </c>
       <c r="K37" t="n">
         <v>69</v>
@@ -2139,7 +2139,7 @@
         <v>23</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2532</v>
+        <v>-1.1577</v>
       </c>
       <c r="N37" t="n">
         <v>92</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4282</v>
+        <v>-1.3634</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5652</v>
+        <v>-0.5395</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2743</v>
+        <v>-1.2269</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4282</v>
+        <v>-1.3634</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.4282</v>
+        <v>-1.3634</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.4282</v>
+        <v>-1.3634</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>230</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4282</v>
+        <v>-1.3634</v>
       </c>
       <c r="N38" t="n">
         <v>230</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6806</v>
+        <v>-1.7111</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.665</v>
+        <v>-0.6771</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3892</v>
+        <v>-1.3853</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6806</v>
+        <v>-1.7111</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.2047</v>
+        <v>-2.224</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5241</v>
+        <v>0.5129</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.2047</v>
+        <v>-2.224</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.4409</v>
+        <v>-2.4714</v>
       </c>
       <c r="J39" t="n">
-        <v>0.5241</v>
+        <v>0.5129</v>
       </c>
       <c r="K39" t="n">
         <v>105</v>
@@ -2231,7 +2231,7 @@
         <v>145</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.9168</v>
+        <v>-1.9585</v>
       </c>
       <c r="N39" t="n">
         <v>250</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.2682</v>
+        <v>-2.3085</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8976</v>
+        <v>-0.9135</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6567</v>
+        <v>-1.6574</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.2682</v>
+        <v>-2.3085</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2682</v>
+        <v>-1.3085</v>
       </c>
       <c r="G40" t="n">
         <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2682</v>
+        <v>-1.3085</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3009</v>
+        <v>-1.3435</v>
       </c>
       <c r="J40" t="n">
         <v>-1</v>
@@ -2277,7 +2277,7 @@
         <v>47</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.3009</v>
+        <v>-2.3435</v>
       </c>
       <c r="N40" t="n">
         <v>68</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4795</v>
+        <v>-2.5172</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9812</v>
+        <v>-0.9961</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7529</v>
+        <v>-1.7525</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4795</v>
+        <v>-2.5172</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.0515</v>
+        <v>-2.0536</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.428</v>
+        <v>-0.4636</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.0515</v>
+        <v>-2.0536</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.1586</v>
+        <v>-2.1648</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.428</v>
+        <v>-0.4636</v>
       </c>
       <c r="K41" t="n">
         <v>50</v>
@@ -2323,7 +2323,7 @@
         <v>151</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.5866</v>
+        <v>-2.6284</v>
       </c>
       <c r="N41" t="n">
         <v>201</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.6716</v>
+        <v>-2.6397</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.0572</v>
+        <v>-1.0446</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.8404</v>
+        <v>-1.8083</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.6716</v>
+        <v>-2.6397</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.6716</v>
+        <v>-1.6397</v>
       </c>
       <c r="G42" t="n">
         <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.6716</v>
+        <v>-1.6397</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.7589</v>
+        <v>-1.7285</v>
       </c>
       <c r="J42" t="n">
         <v>-1</v>
@@ -2369,7 +2369,7 @@
         <v>47</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.7589</v>
+        <v>-2.7285</v>
       </c>
       <c r="N42" t="n">
         <v>92</v>
@@ -2378,93 +2378,93 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-2.7363</v>
+        <v>-2.7167</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.0828</v>
+        <v>-1.075</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.8698</v>
+        <v>-1.8434</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.7363</v>
+        <v>-2.7167</v>
       </c>
       <c r="F43" t="n">
-        <v>-3.0587</v>
+        <v>-3.3725</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3224</v>
+        <v>0.6558</v>
       </c>
       <c r="H43" t="n">
-        <v>-3.0587</v>
+        <v>-3.3725</v>
       </c>
       <c r="I43" t="n">
-        <v>-3.2184</v>
+        <v>-3.7477</v>
       </c>
       <c r="J43" t="n">
-        <v>0.3224</v>
+        <v>0.6558</v>
       </c>
       <c r="K43" t="n">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="L43" t="n">
-        <v>300</v>
+        <v>145</v>
       </c>
       <c r="M43" t="n">
-        <v>-2.896</v>
+        <v>-3.0919</v>
       </c>
       <c r="N43" t="n">
-        <v>350</v>
+        <v>274</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-2.7696</v>
+        <v>-2.9668</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.096</v>
+        <v>-1.174</v>
       </c>
       <c r="D44" t="n">
-        <v>-1.885</v>
+        <v>-1.9573</v>
       </c>
       <c r="E44" t="n">
-        <v>-2.7696</v>
+        <v>-2.9668</v>
       </c>
       <c r="F44" t="n">
-        <v>-3.4263</v>
+        <v>-3.2386</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6567</v>
+        <v>0.2718</v>
       </c>
       <c r="H44" t="n">
-        <v>-3.4263</v>
+        <v>-3.2386</v>
       </c>
       <c r="I44" t="n">
-        <v>-3.7934</v>
+        <v>-3.414</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6567</v>
+        <v>0.2718</v>
       </c>
       <c r="K44" t="n">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="L44" t="n">
-        <v>145</v>
+        <v>300</v>
       </c>
       <c r="M44" t="n">
-        <v>-3.1367</v>
+        <v>-3.1422</v>
       </c>
       <c r="N44" t="n">
-        <v>274</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -2567,10 +2567,10 @@
         <v>0.7</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.819</v>
+        <v>-0.7965</v>
       </c>
       <c r="J2" t="n">
-        <v>-16.38</v>
+        <v>-15.93</v>
       </c>
     </row>
     <row r="3">
@@ -2607,10 +2607,10 @@
         <v>0.61</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0063</v>
+        <v>-1.0046</v>
       </c>
       <c r="J3" t="n">
-        <v>-20.126</v>
+        <v>-20.092</v>
       </c>
     </row>
     <row r="4">
@@ -2647,10 +2647,10 @@
         <v>0.42</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3788</v>
+        <v>-1.4357</v>
       </c>
       <c r="J4" t="n">
-        <v>-27.576</v>
+        <v>-28.714</v>
       </c>
     </row>
     <row r="5">
@@ -2687,10 +2687,10 @@
         <v>2.12</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J5" t="n">
-        <v>36.906</v>
+        <v>39.644</v>
       </c>
     </row>
     <row r="6">
@@ -2727,10 +2727,10 @@
         <v>1.4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9969</v>
+        <v>0.99</v>
       </c>
       <c r="J6" t="n">
-        <v>19.938</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="7">
@@ -2767,10 +2767,10 @@
         <v>1.36</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6716</v>
+        <v>0.6128</v>
       </c>
       <c r="J7" t="n">
-        <v>13.432</v>
+        <v>12.256</v>
       </c>
     </row>
     <row r="8">
@@ -2807,10 +2807,10 @@
         <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3687</v>
+        <v>0.3147</v>
       </c>
       <c r="J8" t="n">
-        <v>7.374</v>
+        <v>6.294</v>
       </c>
     </row>
     <row r="9">
@@ -2847,10 +2847,10 @@
         <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1528</v>
+        <v>-0.1327</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.056</v>
+        <v>-2.654</v>
       </c>
     </row>
     <row r="10">
@@ -2887,10 +2887,10 @@
         <v>1.15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3338</v>
+        <v>0.2821</v>
       </c>
       <c r="J10" t="n">
-        <v>6.676</v>
+        <v>5.642</v>
       </c>
     </row>
     <row r="11">
@@ -2927,10 +2927,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2973</v>
+        <v>-0.2797</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.946</v>
+        <v>-5.594</v>
       </c>
     </row>
     <row r="12">
@@ -2967,10 +2967,10 @@
         <v>0.55</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4573</v>
+        <v>-0.451</v>
       </c>
       <c r="J12" t="n">
-        <v>-13.719</v>
+        <v>-13.53</v>
       </c>
     </row>
     <row r="13">
@@ -3007,10 +3007,10 @@
         <v>0.4</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.5987</v>
       </c>
       <c r="J13" t="n">
-        <v>-17.616</v>
+        <v>-17.961</v>
       </c>
     </row>
     <row r="14">
@@ -3047,10 +3047,10 @@
         <v>0.39</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5957</v>
+        <v>-0.6086</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.871</v>
+        <v>-18.258</v>
       </c>
     </row>
     <row r="15">
@@ -3087,10 +3087,10 @@
         <v>1.39</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6667</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>20.001</v>
+        <v>22.002</v>
       </c>
     </row>
     <row r="16">
@@ -3127,10 +3127,10 @@
         <v>1.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1858</v>
+        <v>0.177</v>
       </c>
       <c r="J16" t="n">
-        <v>5.574</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="17">
@@ -3167,10 +3167,10 @@
         <v>0.62</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4003</v>
+        <v>-0.3888</v>
       </c>
       <c r="J17" t="n">
-        <v>-12.009</v>
+        <v>-11.664</v>
       </c>
     </row>
     <row r="18">
@@ -3207,10 +3207,10 @@
         <v>0.59</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.427</v>
+        <v>-0.4179</v>
       </c>
       <c r="J18" t="n">
-        <v>-12.81</v>
+        <v>-12.537</v>
       </c>
     </row>
     <row r="19">
@@ -3247,10 +3247,10 @@
         <v>0.41</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5828</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-17.484</v>
+        <v>-17.829</v>
       </c>
     </row>
     <row r="20">
@@ -3287,10 +3287,10 @@
         <v>1.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3716</v>
+        <v>0.3178</v>
       </c>
       <c r="J20" t="n">
-        <v>11.148</v>
+        <v>9.534000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3327,10 +3327,10 @@
         <v>1.19</v>
       </c>
       <c r="I21" t="n">
-        <v>0.358</v>
+        <v>0.3048</v>
       </c>
       <c r="J21" t="n">
-        <v>10.74</v>
+        <v>9.144</v>
       </c>
     </row>
     <row r="22">
@@ -3367,10 +3367,10 @@
         <v>0.75</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6917</v>
+        <v>-0.6577</v>
       </c>
       <c r="J22" t="n">
-        <v>-14.5257</v>
+        <v>-13.8117</v>
       </c>
     </row>
     <row r="23">
@@ -3407,10 +3407,10 @@
         <v>0.61</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9892</v>
+        <v>-0.9828</v>
       </c>
       <c r="J23" t="n">
-        <v>-20.7732</v>
+        <v>-20.6388</v>
       </c>
     </row>
     <row r="24">
@@ -3447,10 +3447,10 @@
         <v>0.34</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5182</v>
+        <v>-1.5995</v>
       </c>
       <c r="J24" t="n">
-        <v>-31.8822</v>
+        <v>-33.5895</v>
       </c>
     </row>
     <row r="25">
@@ -3487,10 +3487,10 @@
         <v>1.59</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4138</v>
+        <v>1.4687</v>
       </c>
       <c r="J25" t="n">
-        <v>29.6898</v>
+        <v>30.8427</v>
       </c>
     </row>
     <row r="26">
@@ -3527,10 +3527,10 @@
         <v>1.51</v>
       </c>
       <c r="I26" t="n">
-        <v>1.258</v>
+        <v>1.2966</v>
       </c>
       <c r="J26" t="n">
-        <v>26.418</v>
+        <v>27.2286</v>
       </c>
     </row>
     <row r="27">
@@ -3567,10 +3567,10 @@
         <v>1.25</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5293</v>
+        <v>0.4712</v>
       </c>
       <c r="J27" t="n">
-        <v>11.1153</v>
+        <v>9.895200000000001</v>
       </c>
     </row>
     <row r="28">
@@ -3607,10 +3607,10 @@
         <v>0.95</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.7451</v>
+        <v>-1.4406</v>
       </c>
     </row>
     <row r="29">
@@ -3647,10 +3647,10 @@
         <v>0.88</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1654</v>
+        <v>-0.1457</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.4734</v>
+        <v>-3.0597</v>
       </c>
     </row>
     <row r="30">
@@ -3687,10 +3687,10 @@
         <v>0.85</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1975</v>
+        <v>-0.1771</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.1475</v>
+        <v>-3.7191</v>
       </c>
     </row>
     <row r="31">
@@ -3727,10 +3727,10 @@
         <v>0.85</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1975</v>
+        <v>-0.1771</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.1475</v>
+        <v>-3.7191</v>
       </c>
     </row>
     <row r="32">
@@ -3767,10 +3767,10 @@
         <v>1.01</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0419</v>
+        <v>0.0288</v>
       </c>
       <c r="J32" t="n">
-        <v>1.257</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="33">
@@ -3807,10 +3807,10 @@
         <v>0.86</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1927</v>
+        <v>-0.172</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.781</v>
+        <v>-5.16</v>
       </c>
     </row>
     <row r="34">
@@ -3847,10 +3847,10 @@
         <v>0.82</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2342</v>
+        <v>-0.2139</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.026</v>
+        <v>-6.417</v>
       </c>
     </row>
     <row r="35">
@@ -3887,10 +3887,10 @@
         <v>1.35</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6694</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>20.082</v>
+        <v>18.342</v>
       </c>
     </row>
     <row r="36">
@@ -3927,10 +3927,10 @@
         <v>1.06</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1673</v>
+        <v>0.131</v>
       </c>
       <c r="J36" t="n">
-        <v>5.019</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="37">
@@ -3967,10 +3967,10 @@
         <v>0.54</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0996</v>
+        <v>-1.1039</v>
       </c>
       <c r="J37" t="n">
-        <v>-32.988</v>
+        <v>-33.117</v>
       </c>
     </row>
     <row r="38">
@@ -4007,10 +4007,10 @@
         <v>0.48</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2204</v>
+        <v>-1.2423</v>
       </c>
       <c r="J38" t="n">
-        <v>-36.612</v>
+        <v>-37.269</v>
       </c>
     </row>
     <row r="39">
@@ -4047,10 +4047,10 @@
         <v>0.36</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4572</v>
+        <v>-1.5212</v>
       </c>
       <c r="J39" t="n">
-        <v>-43.716</v>
+        <v>-45.636</v>
       </c>
     </row>
     <row r="40">
@@ -4087,10 +4087,10 @@
         <v>1.4</v>
       </c>
       <c r="I40" t="n">
-        <v>1.0941</v>
+        <v>1.1295</v>
       </c>
       <c r="J40" t="n">
-        <v>32.823</v>
+        <v>33.885</v>
       </c>
     </row>
     <row r="41">
@@ -4127,10 +4127,10 @@
         <v>1.3</v>
       </c>
       <c r="I41" t="n">
-        <v>0.904</v>
+        <v>0.9094</v>
       </c>
       <c r="J41" t="n">
-        <v>27.12</v>
+        <v>27.282</v>
       </c>
     </row>
     <row r="42">
@@ -4167,10 +4167,10 @@
         <v>0.98</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0302</v>
+        <v>-0.0229</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.6644</v>
+        <v>-0.5038</v>
       </c>
     </row>
     <row r="43">
@@ -4207,10 +4207,10 @@
         <v>0.86</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1793</v>
+        <v>-0.1612</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.9446</v>
+        <v>-3.5464</v>
       </c>
     </row>
     <row r="44">
@@ -4247,10 +4247,10 @@
         <v>0.63</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3977</v>
+        <v>-0.3861</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.7494</v>
+        <v>-8.494199999999999</v>
       </c>
     </row>
     <row r="45">
@@ -4287,10 +4287,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1008</v>
+        <v>-0.0866</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.2176</v>
+        <v>-1.9052</v>
       </c>
     </row>
     <row r="46">
@@ -4327,10 +4327,10 @@
         <v>0.9</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1364</v>
+        <v>-0.1202</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.0008</v>
+        <v>-2.6444</v>
       </c>
     </row>
     <row r="47">
@@ -4367,10 +4367,10 @@
         <v>0.82</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.5442</v>
+        <v>-0.5032</v>
       </c>
       <c r="J47" t="n">
-        <v>-11.9724</v>
+        <v>-11.0704</v>
       </c>
     </row>
     <row r="48">
@@ -4407,10 +4407,10 @@
         <v>0.67</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.8759</v>
+        <v>-0.8582</v>
       </c>
       <c r="J48" t="n">
-        <v>-19.2698</v>
+        <v>-18.8804</v>
       </c>
     </row>
     <row r="49">
@@ -4447,10 +4447,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.101</v>
+        <v>-1.1111</v>
       </c>
       <c r="J49" t="n">
-        <v>-24.222</v>
+        <v>-24.4442</v>
       </c>
     </row>
     <row r="50">
@@ -4487,10 +4487,10 @@
         <v>1.59</v>
       </c>
       <c r="I50" t="n">
-        <v>1.2837</v>
+        <v>1.3117</v>
       </c>
       <c r="J50" t="n">
-        <v>28.2414</v>
+        <v>28.8574</v>
       </c>
     </row>
     <row r="51">
@@ -4527,10 +4527,10 @@
         <v>1.44</v>
       </c>
       <c r="I51" t="n">
-        <v>1.068</v>
+        <v>1.08</v>
       </c>
       <c r="J51" t="n">
-        <v>23.496</v>
+        <v>23.76</v>
       </c>
     </row>
     <row r="52">
@@ -4567,10 +4567,10 @@
         <v>0.68</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.8081</v>
+        <v>-0.7825</v>
       </c>
       <c r="J52" t="n">
-        <v>-21.8187</v>
+        <v>-21.1275</v>
       </c>
     </row>
     <row r="53">
@@ -4607,10 +4607,10 @@
         <v>0.57</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.0374</v>
+        <v>-1.0338</v>
       </c>
       <c r="J53" t="n">
-        <v>-28.0098</v>
+        <v>-27.9126</v>
       </c>
     </row>
     <row r="54">
@@ -4647,10 +4647,10 @@
         <v>0.26</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.6499</v>
+        <v>-1.7551</v>
       </c>
       <c r="J54" t="n">
-        <v>-44.5473</v>
+        <v>-47.3877</v>
       </c>
     </row>
     <row r="55">
@@ -4687,10 +4687,10 @@
         <v>1.37</v>
       </c>
       <c r="I55" t="n">
-        <v>1.0468</v>
+        <v>1.0774</v>
       </c>
       <c r="J55" t="n">
-        <v>28.2636</v>
+        <v>29.0898</v>
       </c>
     </row>
     <row r="56">
@@ -4727,10 +4727,10 @@
         <v>1.18</v>
       </c>
       <c r="I56" t="n">
-        <v>0.6217</v>
+        <v>0.5966</v>
       </c>
       <c r="J56" t="n">
-        <v>16.7859</v>
+        <v>16.1082</v>
       </c>
     </row>
     <row r="57">
@@ -4767,10 +4767,10 @@
         <v>0.92</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.13</v>
+        <v>-0.1108</v>
       </c>
       <c r="J57" t="n">
-        <v>-3.51</v>
+        <v>-2.9916</v>
       </c>
     </row>
     <row r="58">
@@ -4807,10 +4807,10 @@
         <v>0.89</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1648</v>
+        <v>-0.1445</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.4496</v>
+        <v>-3.9015</v>
       </c>
     </row>
     <row r="59">
@@ -4847,10 +4847,10 @@
         <v>0.5</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5281</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>-14.2587</v>
+        <v>-14.4396</v>
       </c>
     </row>
     <row r="60">
@@ -4887,10 +4887,10 @@
         <v>1.82</v>
       </c>
       <c r="I60" t="n">
-        <v>1.2282</v>
+        <v>1.2207</v>
       </c>
       <c r="J60" t="n">
-        <v>33.1614</v>
+        <v>32.9589</v>
       </c>
     </row>
     <row r="61">
@@ -4927,10 +4927,10 @@
         <v>1.25</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4997</v>
+        <v>0.4407</v>
       </c>
       <c r="J61" t="n">
-        <v>13.4919</v>
+        <v>11.8989</v>
       </c>
     </row>
     <row r="62">
@@ -4967,10 +4967,10 @@
         <v>0.74</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.7029</v>
+        <v>-0.6695</v>
       </c>
       <c r="J62" t="n">
-        <v>-16.1667</v>
+        <v>-15.3985</v>
       </c>
     </row>
     <row r="63">
@@ -5007,10 +5007,10 @@
         <v>0.54</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.1212</v>
+        <v>-1.131</v>
       </c>
       <c r="J63" t="n">
-        <v>-25.7876</v>
+        <v>-26.013</v>
       </c>
     </row>
     <row r="64">
@@ -5047,10 +5047,10 @@
         <v>0.31</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.5685</v>
+        <v>-1.6589</v>
       </c>
       <c r="J64" t="n">
-        <v>-36.0755</v>
+        <v>-38.1547</v>
       </c>
     </row>
     <row r="65">
@@ -5087,10 +5087,10 @@
         <v>1.63</v>
       </c>
       <c r="I65" t="n">
-        <v>1.3889</v>
+        <v>1.4393</v>
       </c>
       <c r="J65" t="n">
-        <v>31.9447</v>
+        <v>33.1039</v>
       </c>
     </row>
     <row r="66">
@@ -5127,10 +5127,10 @@
         <v>1.34</v>
       </c>
       <c r="I66" t="n">
-        <v>0.9339</v>
+        <v>0.93</v>
       </c>
       <c r="J66" t="n">
-        <v>21.4797</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="67">
@@ -5167,10 +5167,10 @@
         <v>1.21</v>
       </c>
       <c r="I67" t="n">
-        <v>0.433</v>
+        <v>0.3761</v>
       </c>
       <c r="J67" t="n">
-        <v>9.959</v>
+        <v>8.6503</v>
       </c>
     </row>
     <row r="68">
@@ -5207,10 +5207,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3829</v>
+        <v>0.3285</v>
       </c>
       <c r="J68" t="n">
-        <v>8.806699999999999</v>
+        <v>7.5555</v>
       </c>
     </row>
     <row r="69">
@@ -5247,10 +5247,10 @@
         <v>1.06</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1611</v>
+        <v>0.1279</v>
       </c>
       <c r="J69" t="n">
-        <v>3.7053</v>
+        <v>2.9417</v>
       </c>
     </row>
     <row r="70">
@@ -5287,10 +5287,10 @@
         <v>1.18</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3829</v>
+        <v>0.3285</v>
       </c>
       <c r="J70" t="n">
-        <v>8.806699999999999</v>
+        <v>7.5555</v>
       </c>
     </row>
     <row r="71">
@@ -5327,10 +5327,10 @@
         <v>0.8</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2599</v>
+        <v>-0.2407</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.9777</v>
+        <v>-5.5361</v>
       </c>
     </row>
     <row r="72">
@@ -5367,10 +5367,10 @@
         <v>1.02</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0626</v>
+        <v>0.0499</v>
       </c>
       <c r="J72" t="n">
-        <v>1.565</v>
+        <v>1.2475</v>
       </c>
     </row>
     <row r="73">
@@ -5407,10 +5407,10 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0041</v>
+        <v>0.0026</v>
       </c>
       <c r="J73" t="n">
-        <v>0.1025</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="74">
@@ -5447,10 +5447,10 @@
         <v>0.71</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3342</v>
+        <v>-0.3182</v>
       </c>
       <c r="J74" t="n">
-        <v>-8.355</v>
+        <v>-7.955</v>
       </c>
     </row>
     <row r="75">
@@ -5487,10 +5487,10 @@
         <v>1.14</v>
       </c>
       <c r="I75" t="n">
-        <v>0.265</v>
+        <v>0.2507</v>
       </c>
       <c r="J75" t="n">
-        <v>6.625</v>
+        <v>6.2675</v>
       </c>
     </row>
     <row r="76">
@@ -5527,10 +5527,10 @@
         <v>0.9</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1431</v>
+        <v>-0.1242</v>
       </c>
       <c r="J76" t="n">
-        <v>-3.5775</v>
+        <v>-3.105</v>
       </c>
     </row>
     <row r="77">
@@ -5567,10 +5567,10 @@
         <v>0.72</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.317</v>
+        <v>-0.2998</v>
       </c>
       <c r="J77" t="n">
-        <v>-7.925</v>
+        <v>-7.495</v>
       </c>
     </row>
     <row r="78">
@@ -5607,10 +5607,10 @@
         <v>0.36</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6515</v>
       </c>
       <c r="J78" t="n">
-        <v>-15.7625</v>
+        <v>-16.2875</v>
       </c>
     </row>
     <row r="79">
@@ -5647,10 +5647,10 @@
         <v>0.35</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.6388</v>
+        <v>-0.6613</v>
       </c>
       <c r="J79" t="n">
-        <v>-15.97</v>
+        <v>-16.5325</v>
       </c>
     </row>
     <row r="80">
@@ -5687,10 +5687,10 @@
         <v>1.61</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8308</v>
+        <v>0.7826</v>
       </c>
       <c r="J80" t="n">
-        <v>20.77</v>
+        <v>19.565</v>
       </c>
     </row>
     <row r="81">
@@ -5727,10 +5727,10 @@
         <v>1.33</v>
       </c>
       <c r="I81" t="n">
-        <v>0.5125</v>
+        <v>0.4508</v>
       </c>
       <c r="J81" t="n">
-        <v>12.8125</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="82">
@@ -5767,10 +5767,10 @@
         <v>0.96</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.213</v>
+        <v>-0.1793</v>
       </c>
       <c r="J82" t="n">
-        <v>-3.621</v>
+        <v>-3.0481</v>
       </c>
     </row>
     <row r="83">
@@ -5807,10 +5807,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2754</v>
+        <v>-0.2379</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.6818</v>
+        <v>-4.0443</v>
       </c>
     </row>
     <row r="84">
@@ -5847,10 +5847,10 @@
         <v>0.92</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3331</v>
+        <v>-0.2938</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.6627</v>
+        <v>-4.9946</v>
       </c>
     </row>
     <row r="85">
@@ -5887,10 +5887,10 @@
         <v>1.84</v>
       </c>
       <c r="I85" t="n">
-        <v>1.5374</v>
+        <v>1.5752</v>
       </c>
       <c r="J85" t="n">
-        <v>26.1358</v>
+        <v>26.7784</v>
       </c>
     </row>
     <row r="86">
@@ -5927,10 +5927,10 @@
         <v>1.56</v>
       </c>
       <c r="I86" t="n">
-        <v>1.1761</v>
+        <v>1.1901</v>
       </c>
       <c r="J86" t="n">
-        <v>19.9937</v>
+        <v>20.2317</v>
       </c>
     </row>
     <row r="87">
@@ -5967,10 +5967,10 @@
         <v>1.53</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8918</v>
+        <v>0.8405</v>
       </c>
       <c r="J87" t="n">
-        <v>15.1606</v>
+        <v>14.2885</v>
       </c>
     </row>
     <row r="88">
@@ -6007,10 +6007,10 @@
         <v>1.37</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6659</v>
+        <v>0.6069</v>
       </c>
       <c r="J88" t="n">
-        <v>11.3203</v>
+        <v>10.3173</v>
       </c>
     </row>
     <row r="89">
@@ -6047,10 +6047,10 @@
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0114</v>
+        <v>-0.0089</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.1938</v>
+        <v>-0.1513</v>
       </c>
     </row>
     <row r="90">
@@ -6087,10 +6087,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.082</v>
+        <v>0.0619</v>
       </c>
       <c r="J90" t="n">
-        <v>1.394</v>
+        <v>1.0523</v>
       </c>
     </row>
     <row r="91">
@@ -6127,10 +6127,10 @@
         <v>0.87</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1936</v>
+        <v>-0.1736</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.2912</v>
+        <v>-2.9512</v>
       </c>
     </row>
     <row r="92">
@@ -6167,10 +6167,10 @@
         <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0007</v>
+        <v>0.0003</v>
       </c>
       <c r="J92" t="n">
-        <v>0.0126</v>
+        <v>0.0054</v>
       </c>
     </row>
     <row r="93">
@@ -6207,10 +6207,10 @@
         <v>0.4</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.4088</v>
+        <v>-1.4695</v>
       </c>
       <c r="J93" t="n">
-        <v>-25.3584</v>
+        <v>-26.451</v>
       </c>
     </row>
     <row r="94">
@@ -6247,10 +6247,10 @@
         <v>0.12</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.9262</v>
+        <v>-2.1042</v>
       </c>
       <c r="J94" t="n">
-        <v>-34.6716</v>
+        <v>-37.8756</v>
       </c>
     </row>
     <row r="95">
@@ -6287,10 +6287,10 @@
         <v>2.01</v>
       </c>
       <c r="I95" t="n">
-        <v>1.8623</v>
+        <v>1.9712</v>
       </c>
       <c r="J95" t="n">
-        <v>33.5214</v>
+        <v>35.4816</v>
       </c>
     </row>
     <row r="96">
@@ -6327,10 +6327,10 @@
         <v>1.43</v>
       </c>
       <c r="I96" t="n">
-        <v>1.0611</v>
+        <v>1.0735</v>
       </c>
       <c r="J96" t="n">
-        <v>19.0998</v>
+        <v>19.323</v>
       </c>
     </row>
     <row r="97">
@@ -6367,10 +6367,10 @@
         <v>1.39</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6926</v>
+        <v>0.634</v>
       </c>
       <c r="J97" t="n">
-        <v>12.4668</v>
+        <v>11.412</v>
       </c>
     </row>
     <row r="98">
@@ -6407,10 +6407,10 @@
         <v>1.37</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6636</v>
+        <v>0.6047</v>
       </c>
       <c r="J98" t="n">
-        <v>11.9448</v>
+        <v>10.8846</v>
       </c>
     </row>
     <row r="99">
@@ -6447,10 +6447,10 @@
         <v>0.83</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2366</v>
+        <v>-0.2173</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.2588</v>
+        <v>-3.9114</v>
       </c>
     </row>
     <row r="100">
@@ -6487,10 +6487,10 @@
         <v>1.18</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3724</v>
+        <v>0.3215</v>
       </c>
       <c r="J100" t="n">
-        <v>6.7032</v>
+        <v>5.787</v>
       </c>
     </row>
     <row r="101">
@@ -6527,10 +6527,10 @@
         <v>1.09</v>
       </c>
       <c r="I101" t="n">
-        <v>0.2129</v>
+        <v>0.1755</v>
       </c>
       <c r="J101" t="n">
-        <v>3.8322</v>
+        <v>3.159</v>
       </c>
     </row>
     <row r="102">
@@ -6567,10 +6567,10 @@
         <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0162</v>
+        <v>0.0114</v>
       </c>
       <c r="J102" t="n">
-        <v>0.3888</v>
+        <v>0.2736</v>
       </c>
     </row>
     <row r="103">
@@ -6607,10 +6607,10 @@
         <v>0.92</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1163</v>
+        <v>-0.1004</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.7912</v>
+        <v>-2.4096</v>
       </c>
     </row>
     <row r="104">
@@ -6647,10 +6647,10 @@
         <v>0.66</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3742</v>
+        <v>-0.3607</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.9808</v>
+        <v>-8.6568</v>
       </c>
     </row>
     <row r="105">
@@ -6687,10 +6687,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0649</v>
+        <v>-0.0534</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.5576</v>
+        <v>-1.2816</v>
       </c>
     </row>
     <row r="106">
@@ -6727,10 +6727,10 @@
         <v>0.93</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1042</v>
+        <v>-0.0892</v>
       </c>
       <c r="J106" t="n">
-        <v>-2.5008</v>
+        <v>-2.1408</v>
       </c>
     </row>
     <row r="107">
@@ -6767,10 +6767,10 @@
         <v>0.61</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.9997</v>
+        <v>-0.9961</v>
       </c>
       <c r="J107" t="n">
-        <v>-23.9928</v>
+        <v>-23.9064</v>
       </c>
     </row>
     <row r="108">
@@ -6807,10 +6807,10 @@
         <v>0.59</v>
       </c>
       <c r="I108" t="n">
-        <v>-1.0404</v>
+        <v>-1.042</v>
       </c>
       <c r="J108" t="n">
-        <v>-24.9696</v>
+        <v>-25.008</v>
       </c>
     </row>
     <row r="109">
@@ -6847,10 +6847,10 @@
         <v>0.52</v>
       </c>
       <c r="I109" t="n">
-        <v>-1.18</v>
+        <v>-1.2018</v>
       </c>
       <c r="J109" t="n">
-        <v>-28.32</v>
+        <v>-28.8432</v>
       </c>
     </row>
     <row r="110">
@@ -6887,10 +6887,10 @@
         <v>1.73</v>
       </c>
       <c r="I110" t="n">
-        <v>1.3306</v>
+        <v>1.3528</v>
       </c>
       <c r="J110" t="n">
-        <v>31.9344</v>
+        <v>32.4672</v>
       </c>
     </row>
     <row r="111">
@@ -6927,10 +6927,10 @@
         <v>1.62</v>
       </c>
       <c r="I111" t="n">
-        <v>1.1792</v>
+        <v>1.1855</v>
       </c>
       <c r="J111" t="n">
-        <v>28.3008</v>
+        <v>28.452</v>
       </c>
     </row>
     <row r="112">
@@ -6967,10 +6967,10 @@
         <v>1.41</v>
       </c>
       <c r="I112" t="n">
-        <v>0.672</v>
+        <v>0.6399</v>
       </c>
       <c r="J112" t="n">
-        <v>18.144</v>
+        <v>17.2773</v>
       </c>
     </row>
     <row r="113">
@@ -7007,10 +7007,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2458</v>
+        <v>-0.2259</v>
       </c>
       <c r="J113" t="n">
-        <v>-6.6366</v>
+        <v>-6.0993</v>
       </c>
     </row>
     <row r="114">
@@ -7047,10 +7047,10 @@
         <v>0.62</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4227</v>
+        <v>-0.4153</v>
       </c>
       <c r="J114" t="n">
-        <v>-11.4129</v>
+        <v>-11.2131</v>
       </c>
     </row>
     <row r="115">
@@ -7087,10 +7087,10 @@
         <v>1.36</v>
       </c>
       <c r="I115" t="n">
-        <v>0.6167</v>
+        <v>0.5874</v>
       </c>
       <c r="J115" t="n">
-        <v>16.6509</v>
+        <v>15.8598</v>
       </c>
     </row>
     <row r="116">
@@ -7127,10 +7127,10 @@
         <v>0.99</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0277</v>
+        <v>-0.0196</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.7479</v>
+        <v>-0.5292</v>
       </c>
     </row>
     <row r="117">
@@ -7167,10 +7167,10 @@
         <v>0.8</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.5645</v>
+        <v>-0.5254</v>
       </c>
       <c r="J117" t="n">
-        <v>-15.2415</v>
+        <v>-14.1858</v>
       </c>
     </row>
     <row r="118">
@@ -7207,10 +7207,10 @@
         <v>0.71</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.7353</v>
       </c>
       <c r="J118" t="n">
-        <v>-20.6442</v>
+        <v>-19.8531</v>
       </c>
     </row>
     <row r="119">
@@ -7247,10 +7247,10 @@
         <v>0.63</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>-25.218</v>
+        <v>-24.8373</v>
       </c>
     </row>
     <row r="120">
@@ -7287,10 +7287,10 @@
         <v>1.25</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6642</v>
+        <v>0.6538</v>
       </c>
       <c r="J120" t="n">
-        <v>17.9334</v>
+        <v>17.6526</v>
       </c>
     </row>
     <row r="121">
@@ -7327,10 +7327,10 @@
         <v>1.09</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3463</v>
+        <v>0.3048</v>
       </c>
       <c r="J121" t="n">
-        <v>9.350099999999999</v>
+        <v>8.2296</v>
       </c>
     </row>
     <row r="122">
@@ -7367,10 +7367,10 @@
         <v>1.4</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8239</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>33.7799</v>
+        <v>33.128</v>
       </c>
     </row>
     <row r="123">
@@ -7407,10 +7407,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.391</v>
+        <v>0.3553</v>
       </c>
       <c r="J123" t="n">
-        <v>16.031</v>
+        <v>14.5673</v>
       </c>
     </row>
     <row r="124">
@@ -7447,10 +7447,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3416</v>
+        <v>0.3069</v>
       </c>
       <c r="J124" t="n">
-        <v>14.0056</v>
+        <v>12.5829</v>
       </c>
     </row>
     <row r="125">
@@ -7487,10 +7487,10 @@
         <v>1.09</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2897</v>
+        <v>0.2567</v>
       </c>
       <c r="J125" t="n">
-        <v>11.8777</v>
+        <v>10.5247</v>
       </c>
     </row>
     <row r="126">
@@ -7527,10 +7527,10 @@
         <v>1.09</v>
       </c>
       <c r="I126" t="n">
-        <v>0.2897</v>
+        <v>0.2567</v>
       </c>
       <c r="J126" t="n">
-        <v>11.8777</v>
+        <v>10.5247</v>
       </c>
     </row>
     <row r="127">
@@ -7567,10 +7567,10 @@
         <v>1.07</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1987</v>
+        <v>0.1574</v>
       </c>
       <c r="J127" t="n">
-        <v>8.146699999999999</v>
+        <v>6.4534</v>
       </c>
     </row>
     <row r="128">
@@ -7607,10 +7607,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.177</v>
+        <v>0.1383</v>
       </c>
       <c r="J128" t="n">
-        <v>7.257</v>
+        <v>5.6703</v>
       </c>
     </row>
     <row r="129">
@@ -7647,10 +7647,10 @@
         <v>1.02</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0789</v>
+        <v>0.056</v>
       </c>
       <c r="J129" t="n">
-        <v>3.2349</v>
+        <v>2.296</v>
       </c>
     </row>
     <row r="130">
@@ -7687,10 +7687,10 @@
         <v>0.88</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1658</v>
+        <v>-0.1459</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.7978</v>
+        <v>-5.9819</v>
       </c>
     </row>
     <row r="131">
@@ -7727,10 +7727,10 @@
         <v>0.77</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2781</v>
+        <v>-0.259</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.4021</v>
+        <v>-10.619</v>
       </c>
     </row>
     <row r="132">
@@ -7767,10 +7767,10 @@
         <v>1.82</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2952</v>
+        <v>1.2995</v>
       </c>
       <c r="J132" t="n">
-        <v>23.3136</v>
+        <v>23.391</v>
       </c>
     </row>
     <row r="133">
@@ -7807,10 +7807,10 @@
         <v>1.68</v>
       </c>
       <c r="I133" t="n">
-        <v>1.129</v>
+        <v>1.1271</v>
       </c>
       <c r="J133" t="n">
-        <v>20.322</v>
+        <v>20.2878</v>
       </c>
     </row>
     <row r="134">
@@ -7847,10 +7847,10 @@
         <v>1.62</v>
       </c>
       <c r="I134" t="n">
-        <v>1.057</v>
+        <v>1.0536</v>
       </c>
       <c r="J134" t="n">
-        <v>19.026</v>
+        <v>18.9648</v>
       </c>
     </row>
     <row r="135">
@@ -7887,10 +7887,10 @@
         <v>1.46</v>
       </c>
       <c r="I135" t="n">
-        <v>0.8562</v>
+        <v>0.8514</v>
       </c>
       <c r="J135" t="n">
-        <v>15.4116</v>
+        <v>15.3252</v>
       </c>
     </row>
     <row r="136">
@@ -7927,10 +7927,10 @@
         <v>1.41</v>
       </c>
       <c r="I136" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.7841</v>
       </c>
       <c r="J136" t="n">
-        <v>14.1984</v>
+        <v>14.1138</v>
       </c>
     </row>
     <row r="137">
@@ -7967,10 +7967,10 @@
         <v>0.79</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1711</v>
+        <v>-0.1425</v>
       </c>
       <c r="J137" t="n">
-        <v>-3.0798</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="138">
@@ -8007,10 +8007,10 @@
         <v>0.68</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2931</v>
+        <v>-0.2795</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.2758</v>
+        <v>-5.031</v>
       </c>
     </row>
     <row r="139">
@@ -8047,10 +8047,10 @@
         <v>0.39</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.5598</v>
+        <v>-0.5651</v>
       </c>
       <c r="J139" t="n">
-        <v>-10.0764</v>
+        <v>-10.1718</v>
       </c>
     </row>
     <row r="140">
@@ -8087,10 +8087,10 @@
         <v>0.32</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6233</v>
+        <v>-0.6371</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.2194</v>
+        <v>-11.4678</v>
       </c>
     </row>
     <row r="141">
@@ -8127,10 +8127,10 @@
         <v>0.29</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.6692</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.7126</v>
+        <v>-12.0456</v>
       </c>
     </row>
     <row r="142">
@@ -8167,10 +8167,10 @@
         <v>1.34</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6312</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>17.6736</v>
+        <v>16.9792</v>
       </c>
     </row>
     <row r="143">
@@ -8207,10 +8207,10 @@
         <v>0.99</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.016</v>
+        <v>-0.0114</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.448</v>
+        <v>-0.3192</v>
       </c>
     </row>
     <row r="144">
@@ -8247,10 +8247,10 @@
         <v>0.82</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2221</v>
+        <v>-0.2025</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.2188</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="145">
@@ -8287,10 +8287,10 @@
         <v>0.74</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2998</v>
+        <v>-0.2818</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.394399999999999</v>
+        <v>-7.8904</v>
       </c>
     </row>
     <row r="146">
@@ -8327,10 +8327,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4625</v>
+        <v>-0.4579</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.95</v>
+        <v>-12.8212</v>
       </c>
     </row>
     <row r="147">
@@ -8367,10 +8367,10 @@
         <v>1.64</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1523</v>
+        <v>1.1479</v>
       </c>
       <c r="J147" t="n">
-        <v>32.2644</v>
+        <v>32.1412</v>
       </c>
     </row>
     <row r="148">
@@ -8407,10 +8407,10 @@
         <v>1.33</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7198</v>
+        <v>0.7049</v>
       </c>
       <c r="J148" t="n">
-        <v>20.1544</v>
+        <v>19.7372</v>
       </c>
     </row>
     <row r="149">
@@ -8447,10 +8447,10 @@
         <v>1.05</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1739</v>
+        <v>0.1474</v>
       </c>
       <c r="J149" t="n">
-        <v>4.8692</v>
+        <v>4.1272</v>
       </c>
     </row>
     <row r="150">
@@ -8487,10 +8487,10 @@
         <v>0.93</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2925</v>
+        <v>-0.2527</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.19</v>
+        <v>-7.0756</v>
       </c>
     </row>
     <row r="151">
@@ -8527,10 +8527,10 @@
         <v>0.92</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3209</v>
+        <v>-0.2802</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.985200000000001</v>
+        <v>-7.8456</v>
       </c>
     </row>
     <row r="152">
@@ -8567,10 +8567,10 @@
         <v>1.38</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4901</v>
+        <v>0.4396</v>
       </c>
       <c r="J152" t="n">
-        <v>14.703</v>
+        <v>13.188</v>
       </c>
     </row>
     <row r="153">
@@ -8607,10 +8607,10 @@
         <v>1.29</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4083</v>
+        <v>0.3452</v>
       </c>
       <c r="J153" t="n">
-        <v>12.249</v>
+        <v>10.356</v>
       </c>
     </row>
     <row r="154">
@@ -8647,10 +8647,10 @@
         <v>1.18</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2788</v>
+        <v>0.2271</v>
       </c>
       <c r="J154" t="n">
-        <v>8.364000000000001</v>
+        <v>6.813</v>
       </c>
     </row>
     <row r="155">
@@ -8687,10 +8687,10 @@
         <v>0.95</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0975</v>
+        <v>-0.0805</v>
       </c>
       <c r="J155" t="n">
-        <v>-2.925</v>
+        <v>-2.415</v>
       </c>
     </row>
     <row r="156">
@@ -8727,10 +8727,10 @@
         <v>0.91</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1473</v>
+        <v>-0.1277</v>
       </c>
       <c r="J156" t="n">
-        <v>-4.419</v>
+        <v>-3.831</v>
       </c>
     </row>
     <row r="157">
@@ -8767,10 +8767,10 @@
         <v>1.16</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2973</v>
+        <v>0.2855</v>
       </c>
       <c r="J157" t="n">
-        <v>8.919</v>
+        <v>8.565</v>
       </c>
     </row>
     <row r="158">
@@ -8807,10 +8807,10 @@
         <v>1.04</v>
       </c>
       <c r="I158" t="n">
-        <v>0.106</v>
+        <v>0.09</v>
       </c>
       <c r="J158" t="n">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="159">
@@ -8847,10 +8847,10 @@
         <v>0.91</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1303</v>
+        <v>-0.1124</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.909</v>
+        <v>-3.372</v>
       </c>
     </row>
     <row r="160">
@@ -8887,10 +8887,10 @@
         <v>0.79</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2563</v>
+        <v>-0.2366</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.689</v>
+        <v>-7.098</v>
       </c>
     </row>
     <row r="161">
@@ -8927,10 +8927,10 @@
         <v>0.78</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2661</v>
+        <v>-0.2466</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.983</v>
+        <v>-7.398</v>
       </c>
     </row>
     <row r="162">
@@ -8967,10 +8967,10 @@
         <v>1.08</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2206</v>
+        <v>0.1769</v>
       </c>
       <c r="J162" t="n">
-        <v>6.3974</v>
+        <v>5.1301</v>
       </c>
     </row>
     <row r="163">
@@ -9007,10 +9007,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0558</v>
+        <v>-0.0445</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.6182</v>
+        <v>-1.2905</v>
       </c>
     </row>
     <row r="164">
@@ -9047,10 +9047,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.03</v>
+        <v>-1.6472</v>
       </c>
     </row>
     <row r="165">
@@ -9087,10 +9087,10 @@
         <v>0.91</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1318</v>
+        <v>-0.1134</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.8222</v>
+        <v>-3.2886</v>
       </c>
     </row>
     <row r="166">
@@ -9127,10 +9127,10 @@
         <v>0.86</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.187</v>
+        <v>-0.1667</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.423</v>
+        <v>-4.8343</v>
       </c>
     </row>
     <row r="167">
@@ -9167,10 +9167,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8434</v>
+        <v>0.8276</v>
       </c>
       <c r="J167" t="n">
-        <v>24.4586</v>
+        <v>24.0004</v>
       </c>
     </row>
     <row r="168">
@@ -9207,10 +9207,10 @@
         <v>1.36</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7705</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>22.3445</v>
+        <v>21.8805</v>
       </c>
     </row>
     <row r="169">
@@ -9247,10 +9247,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0614</v>
       </c>
       <c r="J169" t="n">
-        <v>2.2678</v>
+        <v>1.7806</v>
       </c>
     </row>
     <row r="170">
@@ -9287,10 +9287,10 @@
         <v>0.99</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0827</v>
+        <v>-0.0619</v>
       </c>
       <c r="J170" t="n">
-        <v>-2.3983</v>
+        <v>-1.7951</v>
       </c>
     </row>
     <row r="171">
@@ -9327,10 +9327,10 @@
         <v>0.92</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3147</v>
+        <v>-0.2736</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.126300000000001</v>
+        <v>-7.9344</v>
       </c>
     </row>
     <row r="172">
@@ -9367,10 +9367,10 @@
         <v>1.13</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4043</v>
+        <v>0.3634</v>
       </c>
       <c r="J172" t="n">
-        <v>13.7462</v>
+        <v>12.3556</v>
       </c>
     </row>
     <row r="173">
@@ -9407,10 +9407,10 @@
         <v>1.07</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2487</v>
+        <v>0.2137</v>
       </c>
       <c r="J173" t="n">
-        <v>8.4558</v>
+        <v>7.2658</v>
       </c>
     </row>
     <row r="174">
@@ -9447,10 +9447,10 @@
         <v>0.96</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1803</v>
+        <v>-0.1465</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.1302</v>
+        <v>-4.981</v>
       </c>
     </row>
     <row r="175">
@@ -9487,10 +9487,10 @@
         <v>1.15</v>
       </c>
       <c r="I175" t="n">
-        <v>0.448</v>
+        <v>0.4117</v>
       </c>
       <c r="J175" t="n">
-        <v>15.232</v>
+        <v>13.9978</v>
       </c>
     </row>
     <row r="176">
@@ -9527,10 +9527,10 @@
         <v>1.01</v>
       </c>
       <c r="I176" t="n">
-        <v>0.0502</v>
+        <v>0.0378</v>
       </c>
       <c r="J176" t="n">
-        <v>1.7068</v>
+        <v>1.2852</v>
       </c>
     </row>
     <row r="177">
@@ -9567,10 +9567,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.2432</v>
+        <v>-0.2231</v>
       </c>
       <c r="J177" t="n">
-        <v>-8.268800000000001</v>
+        <v>-7.5854</v>
       </c>
     </row>
     <row r="178">
@@ -9607,10 +9607,10 @@
         <v>0.8</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2531</v>
+        <v>-0.2333</v>
       </c>
       <c r="J178" t="n">
-        <v>-8.605399999999999</v>
+        <v>-7.9322</v>
       </c>
     </row>
     <row r="179">
@@ -9647,10 +9647,10 @@
         <v>0.74</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3111</v>
+        <v>-0.2939</v>
       </c>
       <c r="J179" t="n">
-        <v>-10.5774</v>
+        <v>-9.992599999999999</v>
       </c>
     </row>
     <row r="180">
@@ -9687,10 +9687,10 @@
         <v>1.46</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7336</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="J180" t="n">
-        <v>24.9424</v>
+        <v>23.8034</v>
       </c>
     </row>
     <row r="181">
@@ -9727,10 +9727,10 @@
         <v>1.23</v>
       </c>
       <c r="I181" t="n">
-        <v>0.4708</v>
+        <v>0.4234</v>
       </c>
       <c r="J181" t="n">
-        <v>16.0072</v>
+        <v>14.3956</v>
       </c>
     </row>
     <row r="182">
@@ -9767,10 +9767,10 @@
         <v>1.09</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2868</v>
+        <v>0.2543</v>
       </c>
       <c r="J182" t="n">
-        <v>10.3248</v>
+        <v>9.1548</v>
       </c>
     </row>
     <row r="183">
@@ -9807,10 +9807,10 @@
         <v>1.09</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2868</v>
+        <v>0.2543</v>
       </c>
       <c r="J183" t="n">
-        <v>10.3248</v>
+        <v>9.1548</v>
       </c>
     </row>
     <row r="184">
@@ -9847,10 +9847,10 @@
         <v>1</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0304</v>
+        <v>-0.0248</v>
       </c>
       <c r="J184" t="n">
-        <v>-1.0944</v>
+        <v>-0.8928</v>
       </c>
     </row>
     <row r="185">
@@ -9887,10 +9887,10 @@
         <v>1.66</v>
       </c>
       <c r="I185" t="n">
-        <v>1.1766</v>
+        <v>1.1735</v>
       </c>
       <c r="J185" t="n">
-        <v>42.3576</v>
+        <v>42.246</v>
       </c>
     </row>
     <row r="186">
@@ -9927,10 +9927,10 @@
         <v>1.07</v>
       </c>
       <c r="I186" t="n">
-        <v>0.2317</v>
+        <v>0.2016</v>
       </c>
       <c r="J186" t="n">
-        <v>8.341200000000001</v>
+        <v>7.2576</v>
       </c>
     </row>
     <row r="187">
@@ -9967,10 +9967,10 @@
         <v>0.95</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>-3.15</v>
+        <v>-2.5704</v>
       </c>
     </row>
     <row r="188">
@@ -10007,10 +10007,10 @@
         <v>0.78</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2737</v>
+        <v>-0.2546</v>
       </c>
       <c r="J188" t="n">
-        <v>-9.853199999999999</v>
+        <v>-9.1656</v>
       </c>
     </row>
     <row r="189">
@@ -10047,10 +10047,10 @@
         <v>0.6</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.4387</v>
+        <v>-0.4328</v>
       </c>
       <c r="J189" t="n">
-        <v>-15.7932</v>
+        <v>-15.5808</v>
       </c>
     </row>
     <row r="190">
@@ -10087,10 +10087,10 @@
         <v>1.46</v>
       </c>
       <c r="I190" t="n">
-        <v>0.731</v>
+        <v>0.6973</v>
       </c>
       <c r="J190" t="n">
-        <v>26.316</v>
+        <v>25.1028</v>
       </c>
     </row>
     <row r="191">
@@ -10127,10 +10127,10 @@
         <v>1.3</v>
       </c>
       <c r="I191" t="n">
-        <v>0.5523</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="J191" t="n">
-        <v>19.8828</v>
+        <v>18.9252</v>
       </c>
     </row>
     <row r="192">
@@ -10167,10 +10167,10 @@
         <v>1.44</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0467</v>
+        <v>1.0527</v>
       </c>
       <c r="J192" t="n">
-        <v>26.1675</v>
+        <v>26.3175</v>
       </c>
     </row>
     <row r="193">
@@ -10207,10 +10207,10 @@
         <v>1.08</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2741</v>
+        <v>0.2385</v>
       </c>
       <c r="J193" t="n">
-        <v>6.8525</v>
+        <v>5.9625</v>
       </c>
     </row>
     <row r="194">
@@ -10247,10 +10247,10 @@
         <v>1.01</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0468</v>
+        <v>0.0351</v>
       </c>
       <c r="J194" t="n">
-        <v>1.17</v>
+        <v>0.8774999999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10287,10 +10287,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2159</v>
+        <v>-0.1791</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.3975</v>
+        <v>-4.4775</v>
       </c>
     </row>
     <row r="196">
@@ -10327,10 +10327,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2464</v>
+        <v>-0.2076</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.16</v>
+        <v>-5.19</v>
       </c>
     </row>
     <row r="197">
@@ -10367,10 +10367,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6191</v>
+        <v>0.5611</v>
       </c>
       <c r="J197" t="n">
-        <v>15.4775</v>
+        <v>14.0275</v>
       </c>
     </row>
     <row r="198">
@@ -10407,10 +10407,10 @@
         <v>1.11</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2758</v>
+        <v>0.227</v>
       </c>
       <c r="J198" t="n">
-        <v>6.895</v>
+        <v>5.675</v>
       </c>
     </row>
     <row r="199">
@@ -10447,10 +10447,10 @@
         <v>1.1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2563</v>
+        <v>0.2091</v>
       </c>
       <c r="J199" t="n">
-        <v>6.4075</v>
+        <v>5.2275</v>
       </c>
     </row>
     <row r="200">
@@ -10487,10 +10487,10 @@
         <v>0.72</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3274</v>
+        <v>-0.311</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.185</v>
+        <v>-7.775</v>
       </c>
     </row>
     <row r="201">
@@ -10527,10 +10527,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3823</v>
+        <v>-0.3702</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.557499999999999</v>
+        <v>-9.255000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10567,10 +10567,10 @@
         <v>1.25</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4262</v>
+        <v>0.429</v>
       </c>
       <c r="J202" t="n">
-        <v>12.3598</v>
+        <v>12.441</v>
       </c>
     </row>
     <row r="203">
@@ -10607,10 +10607,10 @@
         <v>1.06</v>
       </c>
       <c r="I203" t="n">
-        <v>0.147</v>
+        <v>0.1299</v>
       </c>
       <c r="J203" t="n">
-        <v>4.263</v>
+        <v>3.7671</v>
       </c>
     </row>
     <row r="204">
@@ -10647,10 +10647,10 @@
         <v>1.04</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1104</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="J204" t="n">
-        <v>3.2016</v>
+        <v>2.7347</v>
       </c>
     </row>
     <row r="205">
@@ -10687,10 +10687,10 @@
         <v>0.63</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4027</v>
+        <v>-0.3919</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.6783</v>
+        <v>-11.3651</v>
       </c>
     </row>
     <row r="206">
@@ -10727,10 +10727,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4556</v>
+        <v>-0.4504</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.2124</v>
+        <v>-13.0616</v>
       </c>
     </row>
     <row r="207">
@@ -10767,10 +10767,10 @@
         <v>1.28</v>
       </c>
       <c r="I207" t="n">
-        <v>0.397</v>
+        <v>0.3344</v>
       </c>
       <c r="J207" t="n">
-        <v>11.513</v>
+        <v>9.6976</v>
       </c>
     </row>
     <row r="208">
@@ -10807,10 +10807,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3271</v>
+        <v>0.2703</v>
       </c>
       <c r="J208" t="n">
-        <v>9.485900000000001</v>
+        <v>7.8387</v>
       </c>
     </row>
     <row r="209">
@@ -10847,10 +10847,10 @@
         <v>1.21</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3151</v>
+        <v>0.2596</v>
       </c>
       <c r="J209" t="n">
-        <v>9.1379</v>
+        <v>7.5284</v>
       </c>
     </row>
     <row r="210">
@@ -10887,10 +10887,10 @@
         <v>1.18</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2787</v>
+        <v>0.227</v>
       </c>
       <c r="J210" t="n">
-        <v>8.0823</v>
+        <v>6.583</v>
       </c>
     </row>
     <row r="211">
@@ -10927,10 +10927,10 @@
         <v>0.83</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2344</v>
+        <v>-0.2148</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.7976</v>
+        <v>-6.2292</v>
       </c>
     </row>
     <row r="212">
@@ -10967,10 +10967,10 @@
         <v>1.38</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9218</v>
+        <v>0.9062</v>
       </c>
       <c r="J212" t="n">
-        <v>25.8104</v>
+        <v>25.3736</v>
       </c>
     </row>
     <row r="213">
@@ -11007,10 +11007,10 @@
         <v>1.28</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7205</v>
+        <v>0.6901</v>
       </c>
       <c r="J213" t="n">
-        <v>20.174</v>
+        <v>19.3228</v>
       </c>
     </row>
     <row r="214">
@@ -11047,10 +11047,10 @@
         <v>1.14</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4156</v>
+        <v>0.3792</v>
       </c>
       <c r="J214" t="n">
-        <v>11.6368</v>
+        <v>10.6176</v>
       </c>
     </row>
     <row r="215">
@@ -11087,10 +11087,10 @@
         <v>1.03</v>
       </c>
       <c r="I215" t="n">
-        <v>0.1115</v>
+        <v>0.0906</v>
       </c>
       <c r="J215" t="n">
-        <v>3.122</v>
+        <v>2.5368</v>
       </c>
     </row>
     <row r="216">
@@ -11127,10 +11127,10 @@
         <v>0.96</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1978</v>
+        <v>-0.1632</v>
       </c>
       <c r="J216" t="n">
-        <v>-5.5384</v>
+        <v>-4.5696</v>
       </c>
     </row>
     <row r="217">
@@ -11167,10 +11167,10 @@
         <v>1.09</v>
       </c>
       <c r="I217" t="n">
-        <v>0.252</v>
+        <v>0.2055</v>
       </c>
       <c r="J217" t="n">
-        <v>7.056</v>
+        <v>5.754</v>
       </c>
     </row>
     <row r="218">
@@ -11207,10 +11207,10 @@
         <v>1.04</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1409</v>
+        <v>0.1072</v>
       </c>
       <c r="J218" t="n">
-        <v>3.9452</v>
+        <v>3.0016</v>
       </c>
     </row>
     <row r="219">
@@ -11247,10 +11247,10 @@
         <v>0.9</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1398</v>
+        <v>-0.122</v>
       </c>
       <c r="J219" t="n">
-        <v>-3.9144</v>
+        <v>-3.416</v>
       </c>
     </row>
     <row r="220">
@@ -11287,10 +11287,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.234</v>
+        <v>-0.2141</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.552</v>
+        <v>-5.9948</v>
       </c>
     </row>
     <row r="221">
@@ -11327,10 +11327,10 @@
         <v>0.71</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.33</v>
+        <v>-0.3135</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.24</v>
+        <v>-8.778</v>
       </c>
     </row>
     <row r="222">
@@ -11367,10 +11367,10 @@
         <v>1.28</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5273</v>
+        <v>0.4698</v>
       </c>
       <c r="J222" t="n">
-        <v>11.0733</v>
+        <v>9.8658</v>
       </c>
     </row>
     <row r="223">
@@ -11407,10 +11407,10 @@
         <v>1.25</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4814</v>
+        <v>0.4254</v>
       </c>
       <c r="J223" t="n">
-        <v>10.1094</v>
+        <v>8.933400000000001</v>
       </c>
     </row>
     <row r="224">
@@ -11447,10 +11447,10 @@
         <v>1.2</v>
       </c>
       <c r="I224" t="n">
-        <v>0.4032</v>
+        <v>0.351</v>
       </c>
       <c r="J224" t="n">
-        <v>8.4672</v>
+        <v>7.371</v>
       </c>
     </row>
     <row r="225">
@@ -11487,10 +11487,10 @@
         <v>1.28</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5273</v>
+        <v>0.4698</v>
       </c>
       <c r="J225" t="n">
-        <v>11.0733</v>
+        <v>9.8658</v>
       </c>
     </row>
     <row r="226">
@@ -11527,10 +11527,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1143</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.4003</v>
+        <v>-2.0286</v>
       </c>
     </row>
     <row r="227">
@@ -11567,10 +11567,10 @@
         <v>0.74</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.7306</v>
+        <v>-0.7003</v>
       </c>
       <c r="J227" t="n">
-        <v>-15.3426</v>
+        <v>-14.7063</v>
       </c>
     </row>
     <row r="228">
@@ -11607,10 +11607,10 @@
         <v>0.61</v>
       </c>
       <c r="I228" t="n">
-        <v>-1.0045</v>
+        <v>-1.0023</v>
       </c>
       <c r="J228" t="n">
-        <v>-21.0945</v>
+        <v>-21.0483</v>
       </c>
     </row>
     <row r="229">
@@ -11647,10 +11647,10 @@
         <v>0.46</v>
       </c>
       <c r="I229" t="n">
-        <v>-1.3009</v>
+        <v>-1.3435</v>
       </c>
       <c r="J229" t="n">
-        <v>-27.3189</v>
+        <v>-28.2135</v>
       </c>
     </row>
     <row r="230">
@@ -11687,10 +11687,10 @@
         <v>2.03</v>
       </c>
       <c r="I230" t="n">
-        <v>1.8605</v>
+        <v>1.9604</v>
       </c>
       <c r="J230" t="n">
-        <v>39.0705</v>
+        <v>41.1684</v>
       </c>
     </row>
     <row r="231">
@@ -11727,10 +11727,10 @@
         <v>1.36</v>
       </c>
       <c r="I231" t="n">
-        <v>0.9192</v>
+        <v>0.9045</v>
       </c>
       <c r="J231" t="n">
-        <v>19.3032</v>
+        <v>18.9945</v>
       </c>
     </row>
     <row r="232">
@@ -11767,10 +11767,10 @@
         <v>1.47</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8205</v>
+        <v>0.7662</v>
       </c>
       <c r="J232" t="n">
-        <v>19.692</v>
+        <v>18.3888</v>
       </c>
     </row>
     <row r="233">
@@ -11807,10 +11807,10 @@
         <v>1.2</v>
       </c>
       <c r="I233" t="n">
-        <v>0.4123</v>
+        <v>0.357</v>
       </c>
       <c r="J233" t="n">
-        <v>9.895200000000001</v>
+        <v>8.568</v>
       </c>
     </row>
     <row r="234">
@@ -11847,10 +11847,10 @@
         <v>1.08</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1998</v>
+        <v>0.1624</v>
       </c>
       <c r="J234" t="n">
-        <v>4.7952</v>
+        <v>3.8976</v>
       </c>
     </row>
     <row r="235">
@@ -11887,10 +11887,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1448</v>
+        <v>-0.1252</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.4752</v>
+        <v>-3.0048</v>
       </c>
     </row>
     <row r="236">
@@ -11927,10 +11927,10 @@
         <v>0.9</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1564</v>
+        <v>-0.1364</v>
       </c>
       <c r="J236" t="n">
-        <v>-3.7536</v>
+        <v>-3.2736</v>
       </c>
     </row>
     <row r="237">
@@ -11967,10 +11967,10 @@
         <v>0.9</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.3519</v>
+        <v>-0.3093</v>
       </c>
       <c r="J237" t="n">
-        <v>-8.445600000000001</v>
+        <v>-7.4232</v>
       </c>
     </row>
     <row r="238">
@@ -12007,10 +12007,10 @@
         <v>0.73</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.7544</v>
+        <v>-0.7262</v>
       </c>
       <c r="J238" t="n">
-        <v>-18.1056</v>
+        <v>-17.4288</v>
       </c>
     </row>
     <row r="239">
@@ -12047,10 +12047,10 @@
         <v>0.67</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.8825</v>
+        <v>-0.8663</v>
       </c>
       <c r="J239" t="n">
-        <v>-21.18</v>
+        <v>-20.7912</v>
       </c>
     </row>
     <row r="240">
@@ -12087,10 +12087,10 @@
         <v>1.58</v>
       </c>
       <c r="I240" t="n">
-        <v>1.257</v>
+        <v>1.2806</v>
       </c>
       <c r="J240" t="n">
-        <v>30.168</v>
+        <v>30.7344</v>
       </c>
     </row>
     <row r="241">
@@ -12127,10 +12127,10 @@
         <v>1.37</v>
       </c>
       <c r="I241" t="n">
-        <v>0.9355</v>
+        <v>0.9226</v>
       </c>
       <c r="J241" t="n">
-        <v>22.452</v>
+        <v>22.1424</v>
       </c>
     </row>
     <row r="242">
@@ -12167,10 +12167,10 @@
         <v>1.11</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2774</v>
+        <v>0.2284</v>
       </c>
       <c r="J242" t="n">
-        <v>7.7672</v>
+        <v>6.3952</v>
       </c>
     </row>
     <row r="243">
@@ -12207,10 +12207,10 @@
         <v>1.03</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1039</v>
+        <v>0.0765</v>
       </c>
       <c r="J243" t="n">
-        <v>2.9092</v>
+        <v>2.142</v>
       </c>
     </row>
     <row r="244">
@@ -12247,10 +12247,10 @@
         <v>0.93</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1093</v>
+        <v>-0.0921</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.0604</v>
+        <v>-2.5788</v>
       </c>
     </row>
     <row r="245">
@@ -12287,10 +12287,10 @@
         <v>0.9</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1446</v>
+        <v>-0.1253</v>
       </c>
       <c r="J245" t="n">
-        <v>-4.0488</v>
+        <v>-3.5084</v>
       </c>
     </row>
     <row r="246">
@@ -12327,10 +12327,10 @@
         <v>0.89</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1558</v>
+        <v>-0.1361</v>
       </c>
       <c r="J246" t="n">
-        <v>-4.3624</v>
+        <v>-3.8108</v>
       </c>
     </row>
     <row r="247">
@@ -12367,10 +12367,10 @@
         <v>1.28</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6536</v>
+        <v>0.6394</v>
       </c>
       <c r="J247" t="n">
-        <v>18.3008</v>
+        <v>17.9032</v>
       </c>
     </row>
     <row r="248">
@@ -12407,10 +12407,10 @@
         <v>1.27</v>
       </c>
       <c r="I248" t="n">
-        <v>0.638</v>
+        <v>0.6244</v>
       </c>
       <c r="J248" t="n">
-        <v>17.864</v>
+        <v>17.4832</v>
       </c>
     </row>
     <row r="249">
@@ -12447,10 +12447,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.5095</v>
+        <v>0.4945</v>
       </c>
       <c r="J249" t="n">
-        <v>14.266</v>
+        <v>13.846</v>
       </c>
     </row>
     <row r="250">
@@ -12487,10 +12487,10 @@
         <v>1.12</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3718</v>
+        <v>0.3342</v>
       </c>
       <c r="J250" t="n">
-        <v>10.4104</v>
+        <v>9.3576</v>
       </c>
     </row>
     <row r="251">
@@ -12527,10 +12527,10 @@
         <v>0.74</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7457</v>
+        <v>-0.7183</v>
       </c>
       <c r="J251" t="n">
-        <v>-20.8796</v>
+        <v>-20.1124</v>
       </c>
     </row>
     <row r="252">
@@ -12567,10 +12567,10 @@
         <v>1.3</v>
       </c>
       <c r="I252" t="n">
-        <v>0.5432</v>
+        <v>0.5154</v>
       </c>
       <c r="J252" t="n">
-        <v>16.296</v>
+        <v>15.462</v>
       </c>
     </row>
     <row r="253">
@@ -12607,10 +12607,10 @@
         <v>1.15</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3338</v>
+        <v>0.2821</v>
       </c>
       <c r="J253" t="n">
-        <v>10.014</v>
+        <v>8.462999999999999</v>
       </c>
     </row>
     <row r="254">
@@ -12647,10 +12647,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0366</v>
+        <v>0.0256</v>
       </c>
       <c r="J254" t="n">
-        <v>1.098</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="255">
@@ -12687,10 +12687,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1045</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J255" t="n">
-        <v>-3.135</v>
+        <v>-2.607</v>
       </c>
     </row>
     <row r="256">
@@ -12727,10 +12727,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1045</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J256" t="n">
-        <v>-3.135</v>
+        <v>-2.607</v>
       </c>
     </row>
     <row r="257">
@@ -12767,10 +12767,10 @@
         <v>1.46</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9677</v>
+        <v>0.9618</v>
       </c>
       <c r="J257" t="n">
-        <v>29.031</v>
+        <v>28.854</v>
       </c>
     </row>
     <row r="258">
@@ -12807,10 +12807,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.5566</v>
+        <v>0.5455</v>
       </c>
       <c r="J258" t="n">
-        <v>16.698</v>
+        <v>16.365</v>
       </c>
     </row>
     <row r="259">
@@ -12847,10 +12847,10 @@
         <v>1.03</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1416</v>
+        <v>0.1121</v>
       </c>
       <c r="J259" t="n">
-        <v>4.248</v>
+        <v>3.363</v>
       </c>
     </row>
     <row r="260">
@@ -12887,10 +12887,10 @@
         <v>0.63</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.9496</v>
+        <v>-0.9388</v>
       </c>
       <c r="J260" t="n">
-        <v>-28.488</v>
+        <v>-28.164</v>
       </c>
     </row>
     <row r="261">
@@ -12927,10 +12927,10 @@
         <v>0.52</v>
       </c>
       <c r="I261" t="n">
-        <v>-1.172</v>
+        <v>-1.191</v>
       </c>
       <c r="J261" t="n">
-        <v>-35.16</v>
+        <v>-35.73</v>
       </c>
     </row>
     <row r="262">
@@ -12967,10 +12967,10 @@
         <v>1.02</v>
       </c>
       <c r="I262" t="n">
-        <v>0.1146</v>
+        <v>0.1098</v>
       </c>
       <c r="J262" t="n">
-        <v>2.4066</v>
+        <v>2.3058</v>
       </c>
     </row>
     <row r="263">
@@ -13007,10 +13007,10 @@
         <v>0.84</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1852</v>
+        <v>-0.1696</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.8892</v>
+        <v>-3.5616</v>
       </c>
     </row>
     <row r="264">
@@ -13047,10 +13047,10 @@
         <v>0.77</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2564</v>
+        <v>-0.2412</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.3844</v>
+        <v>-5.0652</v>
       </c>
     </row>
     <row r="265">
@@ -13087,10 +13087,10 @@
         <v>0.52</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.48</v>
+        <v>-0.4761</v>
       </c>
       <c r="J265" t="n">
-        <v>-10.08</v>
+        <v>-9.998100000000001</v>
       </c>
     </row>
     <row r="266">
@@ -13127,10 +13127,10 @@
         <v>0.49</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5062</v>
+        <v>-0.5054</v>
       </c>
       <c r="J266" t="n">
-        <v>-10.6302</v>
+        <v>-10.6134</v>
       </c>
     </row>
     <row r="267">
@@ -13167,10 +13167,10 @@
         <v>1.66</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6744</v>
+        <v>0.6309</v>
       </c>
       <c r="J267" t="n">
-        <v>14.1624</v>
+        <v>13.2489</v>
       </c>
     </row>
     <row r="268">
@@ -13207,10 +13207,10 @@
         <v>1.61</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6394</v>
+        <v>0.599</v>
       </c>
       <c r="J268" t="n">
-        <v>13.4274</v>
+        <v>12.579</v>
       </c>
     </row>
     <row r="269">
@@ -13247,10 +13247,10 @@
         <v>1.36</v>
       </c>
       <c r="I269" t="n">
-        <v>0.4572</v>
+        <v>0.4021</v>
       </c>
       <c r="J269" t="n">
-        <v>9.6012</v>
+        <v>8.444100000000001</v>
       </c>
     </row>
     <row r="270">
@@ -13287,10 +13287,10 @@
         <v>1.2</v>
       </c>
       <c r="I270" t="n">
-        <v>0.2867</v>
+        <v>0.2383</v>
       </c>
       <c r="J270" t="n">
-        <v>6.0207</v>
+        <v>5.0043</v>
       </c>
     </row>
     <row r="271">
@@ -13327,10 +13327,10 @@
         <v>1</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.0262</v>
+        <v>-0.0245</v>
       </c>
       <c r="J271" t="n">
-        <v>-0.5502</v>
+        <v>-0.5145</v>
       </c>
     </row>
     <row r="272">
@@ -13367,10 +13367,10 @@
         <v>1.54</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0711</v>
+        <v>1.0694</v>
       </c>
       <c r="J272" t="n">
-        <v>38.5596</v>
+        <v>38.4984</v>
       </c>
     </row>
     <row r="273">
@@ -13407,10 +13407,10 @@
         <v>1.13</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4179</v>
+        <v>0.3759</v>
       </c>
       <c r="J273" t="n">
-        <v>15.0444</v>
+        <v>13.5324</v>
       </c>
     </row>
     <row r="274">
@@ -13447,10 +13447,10 @@
         <v>0.93</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2599</v>
+        <v>-0.2213</v>
       </c>
       <c r="J274" t="n">
-        <v>-9.356400000000001</v>
+        <v>-7.9668</v>
       </c>
     </row>
     <row r="275">
@@ -13487,10 +13487,10 @@
         <v>0.77</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.6562</v>
+        <v>-0.6203</v>
       </c>
       <c r="J275" t="n">
-        <v>-23.6232</v>
+        <v>-22.3308</v>
       </c>
     </row>
     <row r="276">
@@ -13527,10 +13527,10 @@
         <v>0.64</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.9358</v>
+        <v>-0.9242</v>
       </c>
       <c r="J276" t="n">
-        <v>-33.6888</v>
+        <v>-33.2712</v>
       </c>
     </row>
     <row r="277">
@@ -13567,10 +13567,10 @@
         <v>1.36</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6087</v>
+        <v>0.5794</v>
       </c>
       <c r="J277" t="n">
-        <v>21.9132</v>
+        <v>20.8584</v>
       </c>
     </row>
     <row r="278">
@@ -13607,10 +13607,10 @@
         <v>1.29</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5298</v>
+        <v>0.4999</v>
       </c>
       <c r="J278" t="n">
-        <v>19.0728</v>
+        <v>17.9964</v>
       </c>
     </row>
     <row r="279">
@@ -13647,10 +13647,10 @@
         <v>1.1</v>
       </c>
       <c r="I279" t="n">
-        <v>0.241</v>
+        <v>0.1978</v>
       </c>
       <c r="J279" t="n">
-        <v>8.676</v>
+        <v>7.1208</v>
       </c>
     </row>
     <row r="280">
@@ -13687,10 +13687,10 @@
         <v>0.86</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1979</v>
+        <v>-0.1773</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.1244</v>
+        <v>-6.3828</v>
       </c>
     </row>
     <row r="281">
@@ -13727,10 +13727,10 @@
         <v>0.79</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2693</v>
+        <v>-0.2504</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.694800000000001</v>
+        <v>-9.0144</v>
       </c>
     </row>
     <row r="282">
@@ -13767,10 +13767,10 @@
         <v>1.78</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3076</v>
+        <v>1.3118</v>
       </c>
       <c r="J282" t="n">
-        <v>35.3052</v>
+        <v>35.4186</v>
       </c>
     </row>
     <row r="283">
@@ -13807,10 +13807,10 @@
         <v>1.52</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9701</v>
+        <v>0.9569</v>
       </c>
       <c r="J283" t="n">
-        <v>26.1927</v>
+        <v>25.8363</v>
       </c>
     </row>
     <row r="284">
@@ -13847,10 +13847,10 @@
         <v>1.19</v>
       </c>
       <c r="I284" t="n">
-        <v>0.4949</v>
+        <v>0.4827</v>
       </c>
       <c r="J284" t="n">
-        <v>13.3623</v>
+        <v>13.0329</v>
       </c>
     </row>
     <row r="285">
@@ -13887,10 +13887,10 @@
         <v>1.01</v>
       </c>
       <c r="I285" t="n">
-        <v>0.0143</v>
+        <v>0.004</v>
       </c>
       <c r="J285" t="n">
-        <v>0.3861</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="286">
@@ -13927,10 +13927,10 @@
         <v>0.85</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5188</v>
+        <v>-0.4818</v>
       </c>
       <c r="J286" t="n">
-        <v>-14.0076</v>
+        <v>-13.0086</v>
       </c>
     </row>
     <row r="287">
@@ -13967,10 +13967,10 @@
         <v>1.1</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2927</v>
+        <v>0.2457</v>
       </c>
       <c r="J287" t="n">
-        <v>7.9029</v>
+        <v>6.6339</v>
       </c>
     </row>
     <row r="288">
@@ -14007,10 +14007,10 @@
         <v>1</v>
       </c>
       <c r="I288" t="n">
-        <v>0.0288</v>
+        <v>0.023</v>
       </c>
       <c r="J288" t="n">
-        <v>0.7776</v>
+        <v>0.621</v>
       </c>
     </row>
     <row r="289">
@@ -14047,10 +14047,10 @@
         <v>0.83</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2081</v>
+        <v>-0.1897</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.6187</v>
+        <v>-5.1219</v>
       </c>
     </row>
     <row r="290">
@@ -14087,10 +14087,10 @@
         <v>0.73</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3043</v>
+        <v>-0.2868</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.216100000000001</v>
+        <v>-7.7436</v>
       </c>
     </row>
     <row r="291">
@@ -14127,10 +14127,10 @@
         <v>0.55</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4665</v>
+        <v>-0.4619</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.5955</v>
+        <v>-12.4713</v>
       </c>
     </row>
     <row r="292">
@@ -14167,10 +14167,10 @@
         <v>0.96</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.0552</v>
+        <v>-0.0446</v>
       </c>
       <c r="J292" t="n">
-        <v>-1.656</v>
+        <v>-1.338</v>
       </c>
     </row>
     <row r="293">
@@ -14207,10 +14207,10 @@
         <v>0.95</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.0693</v>
+        <v>-0.0575</v>
       </c>
       <c r="J293" t="n">
-        <v>-2.079</v>
+        <v>-1.725</v>
       </c>
     </row>
     <row r="294">
@@ -14247,10 +14247,10 @@
         <v>0.85</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1867</v>
+        <v>-0.1695</v>
       </c>
       <c r="J294" t="n">
-        <v>-5.601</v>
+        <v>-5.085</v>
       </c>
     </row>
     <row r="295">
@@ -14287,10 +14287,10 @@
         <v>0.68</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3481</v>
+        <v>-0.3329</v>
       </c>
       <c r="J295" t="n">
-        <v>-10.443</v>
+        <v>-9.987</v>
       </c>
     </row>
     <row r="296">
@@ -14327,10 +14327,10 @@
         <v>0.66</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3663</v>
+        <v>-0.3522</v>
       </c>
       <c r="J296" t="n">
-        <v>-10.989</v>
+        <v>-10.566</v>
       </c>
     </row>
     <row r="297">
@@ -14367,10 +14367,10 @@
         <v>0.75</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.294</v>
+        <v>-0.2756</v>
       </c>
       <c r="J297" t="n">
-        <v>-8.82</v>
+        <v>-8.268000000000001</v>
       </c>
     </row>
     <row r="298">
@@ -14407,10 +14407,10 @@
         <v>1.32</v>
       </c>
       <c r="I298" t="n">
-        <v>0.473</v>
+        <v>0.4209</v>
       </c>
       <c r="J298" t="n">
-        <v>14.19</v>
+        <v>12.627</v>
       </c>
     </row>
     <row r="299">
@@ -14447,10 +14447,10 @@
         <v>1.1</v>
       </c>
       <c r="I299" t="n">
-        <v>0.1993</v>
+        <v>0.1548</v>
       </c>
       <c r="J299" t="n">
-        <v>5.979</v>
+        <v>4.644</v>
       </c>
     </row>
     <row r="300">
@@ -14487,10 +14487,10 @@
         <v>0.74</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3034</v>
+        <v>-0.2855</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.102</v>
+        <v>-8.565</v>
       </c>
     </row>
     <row r="301">
@@ -14527,10 +14527,10 @@
         <v>0.72</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3222</v>
+        <v>-0.3053</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.666</v>
+        <v>-9.159000000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14567,10 +14567,10 @@
         <v>0.85</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.4467</v>
+        <v>-0.4067</v>
       </c>
       <c r="J302" t="n">
-        <v>-12.5076</v>
+        <v>-11.3876</v>
       </c>
     </row>
     <row r="303">
@@ -14607,10 +14607,10 @@
         <v>1.13</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4492</v>
+        <v>0.4136</v>
       </c>
       <c r="J303" t="n">
-        <v>12.5776</v>
+        <v>11.5808</v>
       </c>
     </row>
     <row r="304">
@@ -14647,10 +14647,10 @@
         <v>0.9</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3237</v>
+        <v>-0.287</v>
       </c>
       <c r="J304" t="n">
-        <v>-9.063599999999999</v>
+        <v>-8.036</v>
       </c>
     </row>
     <row r="305">
@@ -14687,10 +14687,10 @@
         <v>0.86</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4226</v>
+        <v>-0.3829</v>
       </c>
       <c r="J305" t="n">
-        <v>-11.8328</v>
+        <v>-10.7212</v>
       </c>
     </row>
     <row r="306">
@@ -14727,10 +14727,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.7206</v>
+        <v>-0.6884</v>
       </c>
       <c r="J306" t="n">
-        <v>-20.1768</v>
+        <v>-19.2752</v>
       </c>
     </row>
     <row r="307">
@@ -14767,10 +14767,10 @@
         <v>0.82</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.2198</v>
+        <v>-0.2006</v>
       </c>
       <c r="J307" t="n">
-        <v>-6.1544</v>
+        <v>-5.6168</v>
       </c>
     </row>
     <row r="308">
@@ -14807,10 +14807,10 @@
         <v>1.2</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4648</v>
+        <v>0.4206</v>
       </c>
       <c r="J308" t="n">
-        <v>13.0144</v>
+        <v>11.7768</v>
       </c>
     </row>
     <row r="309">
@@ -14847,10 +14847,10 @@
         <v>0.83</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2098</v>
+        <v>-0.1908</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.8744</v>
+        <v>-5.3424</v>
       </c>
     </row>
     <row r="310">
@@ -14887,10 +14887,10 @@
         <v>0.82</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2198</v>
+        <v>-0.2006</v>
       </c>
       <c r="J310" t="n">
-        <v>-6.1544</v>
+        <v>-5.6168</v>
       </c>
     </row>
     <row r="311">
@@ -14927,10 +14927,10 @@
         <v>0.65</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3801</v>
+        <v>-0.3671</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.6428</v>
+        <v>-10.2788</v>
       </c>
     </row>
     <row r="312">
@@ -14967,10 +14967,10 @@
         <v>0.71</v>
       </c>
       <c r="I312" t="n">
-        <v>-0.7129</v>
+        <v>-0.6916</v>
       </c>
       <c r="J312" t="n">
-        <v>-21.387</v>
+        <v>-20.748</v>
       </c>
     </row>
     <row r="313">
@@ -15007,10 +15007,10 @@
         <v>0.92</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1858</v>
+        <v>-0.1478</v>
       </c>
       <c r="J313" t="n">
-        <v>-5.574</v>
+        <v>-4.434</v>
       </c>
     </row>
     <row r="314">
@@ -15047,10 +15047,10 @@
         <v>0.61</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.9166</v>
+        <v>-0.903</v>
       </c>
       <c r="J314" t="n">
-        <v>-27.498</v>
+        <v>-27.09</v>
       </c>
     </row>
     <row r="315">
@@ -15087,10 +15087,10 @@
         <v>0.58</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.9782999999999999</v>
+        <v>-0.9692</v>
       </c>
       <c r="J315" t="n">
-        <v>-29.349</v>
+        <v>-29.076</v>
       </c>
     </row>
     <row r="316">
@@ -15127,10 +15127,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I316" t="n">
-        <v>-1.0194</v>
+        <v>-1.0139</v>
       </c>
       <c r="J316" t="n">
-        <v>-30.582</v>
+        <v>-30.417</v>
       </c>
     </row>
     <row r="317">
@@ -15167,10 +15167,10 @@
         <v>0.89</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.1538</v>
+        <v>-0.1345</v>
       </c>
       <c r="J317" t="n">
-        <v>-4.614</v>
+        <v>-4.035</v>
       </c>
     </row>
     <row r="318">
@@ -15207,10 +15207,10 @@
         <v>1.19</v>
       </c>
       <c r="I318" t="n">
-        <v>0.4279</v>
+        <v>0.3729</v>
       </c>
       <c r="J318" t="n">
-        <v>12.837</v>
+        <v>11.187</v>
       </c>
     </row>
     <row r="319">
@@ -15247,10 +15247,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0954</v>
+        <v>-0.0798</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.862</v>
+        <v>-2.394</v>
       </c>
     </row>
     <row r="320">
@@ -15287,10 +15287,10 @@
         <v>0.89</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1538</v>
+        <v>-0.1345</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.614</v>
+        <v>-4.035</v>
       </c>
     </row>
     <row r="321">
@@ -15327,10 +15327,10 @@
         <v>0.83</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2174</v>
+        <v>-0.1971</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.522</v>
+        <v>-5.913</v>
       </c>
     </row>
     <row r="322">
@@ -15367,10 +15367,10 @@
         <v>1.04</v>
       </c>
       <c r="I322" t="n">
-        <v>0.1475</v>
+        <v>0.1229</v>
       </c>
       <c r="J322" t="n">
-        <v>3.3925</v>
+        <v>2.8267</v>
       </c>
     </row>
     <row r="323">
@@ -15407,10 +15407,10 @@
         <v>0.63</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.9813</v>
+        <v>-0.9792</v>
       </c>
       <c r="J323" t="n">
-        <v>-22.5699</v>
+        <v>-22.5216</v>
       </c>
     </row>
     <row r="324">
@@ -15447,10 +15447,10 @@
         <v>0.53</v>
       </c>
       <c r="I324" t="n">
-        <v>-1.1802</v>
+        <v>-1.2062</v>
       </c>
       <c r="J324" t="n">
-        <v>-27.1446</v>
+        <v>-27.7426</v>
       </c>
     </row>
     <row r="325">
@@ -15487,10 +15487,10 @@
         <v>1.94</v>
       </c>
       <c r="I325" t="n">
-        <v>1.5499</v>
+        <v>1.5865</v>
       </c>
       <c r="J325" t="n">
-        <v>35.6477</v>
+        <v>36.4895</v>
       </c>
     </row>
     <row r="326">
@@ -15527,10 +15527,10 @@
         <v>1.58</v>
       </c>
       <c r="I326" t="n">
-        <v>1.0801</v>
+        <v>1.0721</v>
       </c>
       <c r="J326" t="n">
-        <v>24.8423</v>
+        <v>24.6583</v>
       </c>
     </row>
     <row r="327">
@@ -15567,10 +15567,10 @@
         <v>1.74</v>
       </c>
       <c r="I327" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9311</v>
       </c>
       <c r="J327" t="n">
-        <v>22.3629</v>
+        <v>21.4153</v>
       </c>
     </row>
     <row r="328">
@@ -15607,10 +15607,10 @@
         <v>1.29</v>
       </c>
       <c r="I328" t="n">
-        <v>0.5145</v>
+        <v>0.483</v>
       </c>
       <c r="J328" t="n">
-        <v>11.8335</v>
+        <v>11.109</v>
       </c>
     </row>
     <row r="329">
@@ -15647,10 +15647,10 @@
         <v>0.98</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0578</v>
+        <v>-0.0455</v>
       </c>
       <c r="J329" t="n">
-        <v>-1.3294</v>
+        <v>-1.0465</v>
       </c>
     </row>
     <row r="330">
@@ -15687,10 +15687,10 @@
         <v>1</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.0143</v>
+        <v>-0.0117</v>
       </c>
       <c r="J330" t="n">
-        <v>-0.3289</v>
+        <v>-0.2691</v>
       </c>
     </row>
     <row r="331">
@@ -15727,10 +15727,10 @@
         <v>0.98</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.0578</v>
+        <v>-0.0455</v>
       </c>
       <c r="J331" t="n">
-        <v>-1.3294</v>
+        <v>-1.0465</v>
       </c>
     </row>
     <row r="332">
@@ -15767,10 +15767,10 @@
         <v>0.98</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.1201</v>
+        <v>-0.093</v>
       </c>
       <c r="J332" t="n">
-        <v>-2.8824</v>
+        <v>-2.232</v>
       </c>
     </row>
     <row r="333">
@@ -15807,10 +15807,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I333" t="n">
-        <v>-1.1176</v>
+        <v>-1.1333</v>
       </c>
       <c r="J333" t="n">
-        <v>-26.8224</v>
+        <v>-27.1992</v>
       </c>
     </row>
     <row r="334">
@@ -15847,10 +15847,10 @@
         <v>0.54</v>
       </c>
       <c r="I334" t="n">
-        <v>-1.157</v>
+        <v>-1.1786</v>
       </c>
       <c r="J334" t="n">
-        <v>-27.768</v>
+        <v>-28.2864</v>
       </c>
     </row>
     <row r="335">
@@ -15887,10 +15887,10 @@
         <v>1.87</v>
       </c>
       <c r="I335" t="n">
-        <v>1.4712</v>
+        <v>1.5001</v>
       </c>
       <c r="J335" t="n">
-        <v>35.3088</v>
+        <v>36.0024</v>
       </c>
     </row>
     <row r="336">
@@ -15927,10 +15927,10 @@
         <v>1.64</v>
       </c>
       <c r="I336" t="n">
-        <v>1.169</v>
+        <v>1.1678</v>
       </c>
       <c r="J336" t="n">
-        <v>28.056</v>
+        <v>28.0272</v>
       </c>
     </row>
     <row r="337">
@@ -15967,10 +15967,10 @@
         <v>1.32</v>
       </c>
       <c r="I337" t="n">
-        <v>0.5588</v>
+        <v>0.5321</v>
       </c>
       <c r="J337" t="n">
-        <v>13.4112</v>
+        <v>12.7704</v>
       </c>
     </row>
     <row r="338">
@@ -16007,10 +16007,10 @@
         <v>1.29</v>
       </c>
       <c r="I338" t="n">
-        <v>0.525</v>
+        <v>0.4943</v>
       </c>
       <c r="J338" t="n">
-        <v>12.6</v>
+        <v>11.8632</v>
       </c>
     </row>
     <row r="339">
@@ -16047,10 +16047,10 @@
         <v>1.16</v>
       </c>
       <c r="I339" t="n">
-        <v>0.3451</v>
+        <v>0.2939</v>
       </c>
       <c r="J339" t="n">
-        <v>8.282400000000001</v>
+        <v>7.0536</v>
       </c>
     </row>
     <row r="340">
@@ -16087,10 +16087,10 @@
         <v>0.91</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.1448</v>
+        <v>-0.1252</v>
       </c>
       <c r="J340" t="n">
-        <v>-3.4752</v>
+        <v>-3.0048</v>
       </c>
     </row>
     <row r="341">
@@ -16127,10 +16127,10 @@
         <v>0.88</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.1789</v>
+        <v>-0.1585</v>
       </c>
       <c r="J341" t="n">
-        <v>-4.2936</v>
+        <v>-3.804</v>
       </c>
     </row>
   </sheetData>
